--- a/プロジェクト型演習_成果ドキュメント_一覧表示.xlsx
+++ b/プロジェクト型演習_成果ドキュメント_一覧表示.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER125\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\project-based-learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF959C97-1049-49C4-BFFA-F07F2C243BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37E68DC-B82D-4E99-94F7-0DE7B98FFBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1725" yWindow="885" windowWidth="18465" windowHeight="10515" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,6 @@
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -258,32 +257,11 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>login-servlet</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>①</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ユーザIDを入力する。</t>
-    <rPh sb="6" eb="8">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>submit</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>一覧表示画面</t>
-    <rPh sb="0" eb="4">
-      <t>イチランヒョウジ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -345,36 +323,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">基本フロー2：各項目内に該当するタスク情報が存在しなかった場合。
-1. 空白で表示する。
-</t>
-    <rPh sb="0" eb="2">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="7" eb="11">
-      <t>カクコウモクナイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ガイトウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>クウハク</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>ユーザがログイン状態であること。タスク一覧表示で必要な各表示項目に該当する情報がDBに保存されていること。</t>
     <rPh sb="8" eb="10">
       <t>ジョウタイ</t>
@@ -402,19 +350,6 @@
     </rPh>
     <rPh sb="46" eb="48">
       <t>ホゾン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>システムがタスク一覧を表形式で表示させる。</t>
-    <rPh sb="8" eb="10">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>ヒョウケイシキ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -463,6 +398,128 @@
       <t>ケイシキ</t>
     </rPh>
     <rPh sb="57" eb="59">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>メニュー画面へ遷移する。</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>menu-servlet</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク一覧表示画面</t>
+    <rPh sb="3" eb="7">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">基本フロー2：各項目内に該当するタスク情報が存在しなかった場合。
+1. 空欄で表示する。
+</t>
+    <rPh sb="0" eb="2">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>カクコウモクナイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>クウラン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク情報が存在する場合：タスク一覧表示画面へ遷移し、タスク一覧を表形式で表示させる。
+タスク情報が存在しない場合：タスク一覧表示画面へ遷移し、情報が存在しない項目内容は空欄で表示される。</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="18" eb="22">
+      <t>ヒョウジガメン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>ヒョウケイシキ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="61" eb="67">
+      <t>イチランヒョウジガメン</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>クウラン</t>
+    </rPh>
+    <rPh sb="88" eb="90">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -1439,7 +1496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1584,8 +1641,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1593,23 +1686,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1644,15 +1755,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1663,6 +1765,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1696,43 +1801,28 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1743,53 +1833,20 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1800,7 +1857,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1815,47 +1872,53 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1898,25 +1961,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -2017,13 +2061,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
@@ -2041,6 +2078,32 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4996,7 +5059,7 @@
           <a:pPr algn="l"/>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
-            <a:t>一覧表示</a:t>
+            <a:t>タスク一覧表示</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
         </a:p>
@@ -5220,57 +5283,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>338239</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>183697</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>183696</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>199620</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="16" name="直線コネクタ 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35681604-C3CF-1526-C65D-4BAC8049B875}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="9753335" y="1997110"/>
-          <a:ext cx="999448" cy="15923"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050"/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>274760</xdr:colOff>
       <xdr:row>11</xdr:row>
@@ -5320,143 +5332,6 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>285751</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>4525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>515770</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="23" name="直線コネクタ 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C1E02F9-9023-425F-837A-42A538AD3ED1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:cxnSpLocks/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9696451" y="2614375"/>
-          <a:ext cx="1973094" cy="5000"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050"/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>708163</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>238125</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>994328</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>242739</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="テキスト ボックス 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8826C4B3-0299-2AD8-9C21-9BD2FC513832}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8423413" y="2047875"/>
-          <a:ext cx="286165" cy="1071414"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>①</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>②</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>④</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -5589,7 +5464,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA498F99-F6C9-4CB9-9746-AAA03D333707}" name="テーブル1" displayName="テーブル1" ref="A1:F2" insertRow="1" totalsRowShown="0" headerRowDxfId="2" dataDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA498F99-F6C9-4CB9-9746-AAA03D333707}" name="テーブル1" displayName="テーブル1" ref="A1:F2" insertRow="1" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="A1:F2" xr:uid="{AA498F99-F6C9-4CB9-9746-AAA03D333707}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5599,10 +5474,10 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{A751ED3E-8687-49E8-AF06-7093CF569AD7}" name="タスク" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{2057FEB7-6810-4FA2-B76B-657FE8BA58DD}" name="カテゴリ" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{1D2F16BC-B599-4D57-8038-6B8E28F40C1C}" name="期限" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{11146246-3441-451A-894B-243A5EC6B1FE}" name="担当者情報" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{A751ED3E-8687-49E8-AF06-7093CF569AD7}" name="タスク" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{2057FEB7-6810-4FA2-B76B-657FE8BA58DD}" name="カテゴリ" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{1D2F16BC-B599-4D57-8038-6B8E28F40C1C}" name="期限" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{11146246-3441-451A-894B-243A5EC6B1FE}" name="担当者情報" dataDxfId="2"/>
     <tableColumn id="5" xr3:uid="{9692A1AA-C1FA-481F-9AB3-486A8613D028}" name="ステータス" dataDxfId="1"/>
     <tableColumn id="6" xr3:uid="{147F4C38-F038-4FEA-800F-DF90FA15194F}" name="メモ" dataDxfId="0"/>
   </tableColumns>
@@ -5817,85 +5692,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="103" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
+      <c r="M2" s="104"/>
+      <c r="N2" s="104"/>
+      <c r="O2" s="104"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="90"/>
+      <c r="M3" s="90"/>
+      <c r="N3" s="90"/>
+      <c r="O3" s="90"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="90"/>
+      <c r="N4" s="90"/>
+      <c r="O4" s="90"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="90"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="90"/>
+      <c r="K6" s="90"/>
+      <c r="L6" s="90"/>
+      <c r="M6" s="90"/>
+      <c r="N6" s="90"/>
+      <c r="O6" s="90"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -5915,46 +5790,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="55" t="s">
+      <c r="E8" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="52"/>
+      <c r="F8" s="90"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="90"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="90"/>
+      <c r="L8" s="90"/>
+      <c r="M8" s="90"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="48" t="s">
+      <c r="G13" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="50"/>
-      <c r="I13" s="56">
+      <c r="H13" s="62"/>
+      <c r="I13" s="106">
         <v>46230</v>
       </c>
-      <c r="J13" s="49"/>
-      <c r="K13" s="50"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="62"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="48"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="50"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="101"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="62"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="48"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="50"/>
+      <c r="G15" s="101"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="101"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="62"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -5963,13 +5838,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="51" t="s">
+      <c r="G17" s="102" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
+      <c r="H17" s="90"/>
+      <c r="I17" s="90"/>
+      <c r="J17" s="90"/>
+      <c r="K17" s="90"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -6983,19 +6858,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="87"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="65"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="65"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
@@ -7007,194 +6882,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="80" t="s">
+      <c r="A2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="97"/>
+      <c r="F2" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="84">
+      <c r="G2" s="97"/>
+      <c r="H2" s="100">
         <v>46231</v>
       </c>
-      <c r="I2" s="57" t="s">
-        <v>75</v>
+      <c r="I2" s="75" t="s">
+        <v>72</v>
       </c>
-      <c r="J2" s="60"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="61"/>
+      <c r="A3" s="89"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="76"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="62"/>
+      <c r="A4" s="92"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="66" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="84" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="85"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="61"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="70" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="64"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="60" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="61"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="64"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="61"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="70" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="64"/>
+    </row>
+    <row r="9" spans="1:10" ht="87.75" customHeight="1">
+      <c r="A9" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="62"/>
+      <c r="D9" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="67"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="68" t="s">
-        <v>9</v>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="64"/>
+    </row>
+    <row r="10" spans="1:10" ht="100.5" customHeight="1">
+      <c r="A10" s="72"/>
+      <c r="B10" s="74" t="s">
+        <v>14</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="69" t="s">
+      <c r="C10" s="62"/>
+      <c r="D10" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="70"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="68" t="s">
-        <v>10</v>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="64"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="73"/>
+      <c r="B11" s="74" t="s">
+        <v>15</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="69" t="s">
-        <v>66</v>
+      <c r="C11" s="62"/>
+      <c r="D11" s="70" t="s">
+        <v>67</v>
       </c>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="70"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="68" t="s">
-        <v>11</v>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="64"/>
+    </row>
+    <row r="12" spans="1:10" ht="34.5" customHeight="1">
+      <c r="A12" s="60" t="s">
+        <v>16</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="69" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="70"/>
-    </row>
-    <row r="9" spans="1:10" ht="87.75" customHeight="1">
-      <c r="A9" s="91" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="94" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="50"/>
-      <c r="D9" s="85" t="s">
+      <c r="B12" s="61"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="70"/>
-    </row>
-    <row r="10" spans="1:10" ht="100.5" customHeight="1">
-      <c r="A10" s="92"/>
-      <c r="B10" s="94" t="s">
-        <v>14</v>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="64"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A13" s="65" t="s">
+        <v>17</v>
       </c>
-      <c r="C10" s="50"/>
-      <c r="D10" s="85" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="70"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="93"/>
-      <c r="B11" s="94" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="50"/>
-      <c r="D11" s="69" t="s">
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="68" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="70"/>
-    </row>
-    <row r="12" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A12" s="68" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="85" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="70"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="86" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="87"/>
-      <c r="C13" s="88"/>
-      <c r="D13" s="89" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="87"/>
-      <c r="F13" s="87"/>
-      <c r="G13" s="87"/>
-      <c r="H13" s="87"/>
-      <c r="I13" s="87"/>
-      <c r="J13" s="90"/>
+      <c r="E13" s="139"/>
+      <c r="F13" s="139"/>
+      <c r="G13" s="139"/>
+      <c r="H13" s="139"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="140"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8185,6 +8060,18 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -8200,18 +8087,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -8230,19 +8105,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="87"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="65"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="65"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -8254,48 +8129,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="80" t="s">
+      <c r="A2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="97"/>
+      <c r="F2" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="84">
+      <c r="G2" s="97"/>
+      <c r="H2" s="100">
         <v>46230</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="60"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="61"/>
+      <c r="A3" s="89"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="76"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="62"/>
+      <c r="A4" s="92"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -9652,19 +9527,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="87"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="65"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="65"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -9676,48 +9551,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="80" t="s">
+      <c r="A2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="97"/>
+      <c r="F2" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="84">
+      <c r="G2" s="97"/>
+      <c r="H2" s="100">
         <v>46231</v>
       </c>
-      <c r="I2" s="57" t="s">
-        <v>75</v>
+      <c r="I2" s="75" t="s">
+        <v>72</v>
       </c>
-      <c r="J2" s="60"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="61"/>
+      <c r="A3" s="89"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="74"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="61"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="108"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="37"/>
@@ -11124,19 +10999,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="87"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="65"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="65"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -11148,81 +11023,81 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="80" t="s">
+      <c r="A2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="97"/>
+      <c r="F2" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="84">
+      <c r="G2" s="97"/>
+      <c r="H2" s="100">
         <v>46231</v>
       </c>
-      <c r="I2" s="57" t="s">
-        <v>75</v>
+      <c r="I2" s="75" t="s">
+        <v>72</v>
       </c>
-      <c r="J2" s="60"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="61"/>
+      <c r="A3" s="89"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="74"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="61"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="98" t="s">
+      <c r="A5" s="109" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="101" t="s">
-        <v>74</v>
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="115" t="s">
+        <v>87</v>
       </c>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="67"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="100" t="s">
+      <c r="A6" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="70"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="64"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="102"/>
+      <c r="A7" s="116"/>
       <c r="B7" s="117"/>
       <c r="C7" s="117"/>
       <c r="D7" s="117"/>
@@ -11306,32 +11181,32 @@
       <c r="J13" s="124"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="100" t="s">
+      <c r="A14" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="70"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="64"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="100" t="s">
+      <c r="A15" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="49"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="69" t="s">
-        <v>70</v>
+      <c r="B15" s="61"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="70" t="s">
+        <v>86</v>
       </c>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="50"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="62"/>
       <c r="I15" s="14" t="s">
         <v>25</v>
       </c>
@@ -11340,11 +11215,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="100" t="s">
+      <c r="A16" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="49"/>
-      <c r="C16" s="50"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="62"/>
       <c r="D16" s="14" t="s">
         <v>27</v>
       </c>
@@ -11357,107 +11232,107 @@
       <c r="G16" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="106" t="s">
+      <c r="H16" s="125" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="49"/>
-      <c r="J16" s="70"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="64"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="97" t="s">
-        <v>71</v>
+      <c r="A17" s="112" t="s">
+        <v>70</v>
       </c>
-      <c r="B17" s="137"/>
-      <c r="C17" s="138"/>
+      <c r="B17" s="113"/>
+      <c r="C17" s="114"/>
       <c r="D17" s="16" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F17" s="16" t="s">
         <v>67</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
-      <c r="H17" s="69" t="s">
-        <v>72</v>
+      <c r="H17" s="70" t="s">
+        <v>85</v>
       </c>
-      <c r="I17" s="49"/>
-      <c r="J17" s="70"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="64"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="97"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="50"/>
+      <c r="A18" s="112"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="62"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="64"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="97"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="50"/>
+      <c r="A19" s="112"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="62"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="70"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="64"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="97"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="50"/>
+      <c r="A20" s="112"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="62"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="64"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="97"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="50"/>
+      <c r="A21" s="112"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="62"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="70"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="64"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="97"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="50"/>
+      <c r="A22" s="112"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="62"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="64"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="99"/>
-      <c r="B23" s="87"/>
-      <c r="C23" s="88"/>
+      <c r="A23" s="110"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="67"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="89"/>
-      <c r="I23" s="87"/>
-      <c r="J23" s="90"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="66"/>
+      <c r="J23" s="69"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12438,11 +12313,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12459,16 +12339,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12483,48 +12358,48 @@
   <sheetFormatPr defaultColWidth="18.85546875" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="126" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="126" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="126" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="127" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" s="128" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="129"/>
-      <c r="B2" s="130"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="136"/>
+      <c r="A2" s="52"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="59"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="133"/>
-      <c r="B3" s="133"/>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="133"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="56"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="133"/>
-      <c r="B4" s="133"/>
-      <c r="C4" s="133"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="133"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="56"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8"/>
@@ -12546,182 +12421,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="79" t="s">
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="79" t="s">
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="79" t="s">
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="79" t="s">
+      <c r="P1" s="83"/>
+      <c r="Q1" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="65"/>
-      <c r="S1" s="79" t="s">
+      <c r="R1" s="83"/>
+      <c r="S1" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="67"/>
+      <c r="T1" s="85"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="81"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="104"/>
+      <c r="A2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="130"/>
+      <c r="M2" s="130"/>
+      <c r="N2" s="97"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="97"/>
+      <c r="Q2" s="96"/>
+      <c r="R2" s="97"/>
+      <c r="S2" s="96"/>
+      <c r="T2" s="131"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="82"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="82"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="82"/>
-      <c r="T3" s="105"/>
+      <c r="A3" s="89"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="90"/>
+      <c r="M3" s="90"/>
+      <c r="N3" s="91"/>
+      <c r="O3" s="98"/>
+      <c r="P3" s="91"/>
+      <c r="Q3" s="98"/>
+      <c r="R3" s="91"/>
+      <c r="S3" s="98"/>
+      <c r="T3" s="132"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="76"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="78"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
-      <c r="N4" s="78"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="78"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="78"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="115"/>
+      <c r="A4" s="92"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="93"/>
+      <c r="M4" s="93"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="94"/>
+      <c r="Q4" s="99"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="99"/>
+      <c r="T4" s="133"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="98" t="s">
+      <c r="A5" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="66" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="64"/>
-      <c r="O5" s="64"/>
-      <c r="P5" s="64"/>
-      <c r="Q5" s="64"/>
-      <c r="R5" s="64"/>
-      <c r="S5" s="64"/>
-      <c r="T5" s="67"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
+      <c r="L5" s="82"/>
+      <c r="M5" s="82"/>
+      <c r="N5" s="82"/>
+      <c r="O5" s="82"/>
+      <c r="P5" s="82"/>
+      <c r="Q5" s="82"/>
+      <c r="R5" s="82"/>
+      <c r="S5" s="82"/>
+      <c r="T5" s="85"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="100" t="s">
+      <c r="A6" s="111" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="69" t="s">
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="49"/>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49"/>
-      <c r="T6" s="70"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="64"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="100" t="s">
+      <c r="A7" s="111" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="69" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="49"/>
-      <c r="R7" s="49"/>
-      <c r="S7" s="49"/>
-      <c r="T7" s="70"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="61"/>
+      <c r="N7" s="61"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="61"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="61"/>
+      <c r="S7" s="61"/>
+      <c r="T7" s="64"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -12920,37 +12795,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="100" t="s">
+      <c r="A15" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="114" t="s">
+      <c r="B15" s="62"/>
+      <c r="C15" s="136" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="50"/>
-      <c r="E15" s="106" t="s">
+      <c r="D15" s="62"/>
+      <c r="E15" s="125" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="50"/>
-      <c r="G15" s="106" t="s">
+      <c r="F15" s="62"/>
+      <c r="G15" s="125" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="49"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="106" t="s">
+      <c r="H15" s="61"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="125" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="50"/>
-      <c r="L15" s="106" t="s">
+      <c r="K15" s="62"/>
+      <c r="L15" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="49"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="106" t="s">
+      <c r="M15" s="61"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="125" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="50"/>
+      <c r="P15" s="61"/>
+      <c r="Q15" s="62"/>
       <c r="R15" s="14" t="s">
         <v>49</v>
       </c>
@@ -12962,37 +12837,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="107">
+      <c r="A16" s="134">
         <v>1</v>
       </c>
-      <c r="B16" s="50"/>
-      <c r="C16" s="108" t="s">
+      <c r="B16" s="62"/>
+      <c r="C16" s="135" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="108" t="s">
+      <c r="D16" s="62"/>
+      <c r="E16" s="135" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="50"/>
-      <c r="G16" s="113" t="s">
+      <c r="F16" s="62"/>
+      <c r="G16" s="126" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="49"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="113" t="s">
+      <c r="H16" s="61"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="126" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="50"/>
-      <c r="L16" s="111" t="s">
+      <c r="K16" s="62"/>
+      <c r="L16" s="128" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="49"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="111" t="s">
+      <c r="M16" s="61"/>
+      <c r="N16" s="62"/>
+      <c r="O16" s="128" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="50"/>
+      <c r="P16" s="61"/>
+      <c r="Q16" s="62"/>
       <c r="R16" s="32"/>
       <c r="S16" s="32"/>
       <c r="T16" s="33"/>
@@ -13004,37 +12879,37 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="107">
+      <c r="A17" s="134">
         <v>2</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="108" t="s">
+      <c r="B17" s="62"/>
+      <c r="C17" s="135" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="50"/>
-      <c r="E17" s="108" t="s">
+      <c r="D17" s="62"/>
+      <c r="E17" s="135" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="50"/>
-      <c r="G17" s="113" t="s">
+      <c r="F17" s="62"/>
+      <c r="G17" s="126" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="49"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="113" t="s">
+      <c r="H17" s="61"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="126" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="50"/>
-      <c r="L17" s="111" t="s">
+      <c r="K17" s="62"/>
+      <c r="L17" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="49"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="111" t="s">
+      <c r="M17" s="61"/>
+      <c r="N17" s="62"/>
+      <c r="O17" s="128" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="49"/>
-      <c r="Q17" s="50"/>
+      <c r="P17" s="61"/>
+      <c r="Q17" s="62"/>
       <c r="R17" s="32"/>
       <c r="S17" s="32"/>
       <c r="T17" s="33"/>
@@ -13046,23 +12921,23 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="107"/>
-      <c r="B18" s="50"/>
-      <c r="C18" s="108"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="108"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="113"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="113"/>
-      <c r="K18" s="50"/>
-      <c r="L18" s="111"/>
-      <c r="M18" s="49"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="111"/>
-      <c r="P18" s="49"/>
-      <c r="Q18" s="50"/>
+      <c r="A18" s="134"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="126"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="126"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="128"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="62"/>
+      <c r="O18" s="128"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="62"/>
       <c r="R18" s="32"/>
       <c r="S18" s="32"/>
       <c r="T18" s="33"/>
@@ -13074,23 +12949,23 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="107"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="108"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="113"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="113"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="111"/>
-      <c r="M19" s="49"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="111"/>
-      <c r="P19" s="49"/>
-      <c r="Q19" s="50"/>
+      <c r="A19" s="134"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="135"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="135"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="126"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="126"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="128"/>
+      <c r="M19" s="61"/>
+      <c r="N19" s="62"/>
+      <c r="O19" s="128"/>
+      <c r="P19" s="61"/>
+      <c r="Q19" s="62"/>
       <c r="R19" s="32"/>
       <c r="S19" s="32"/>
       <c r="T19" s="33"/>
@@ -13102,23 +12977,23 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="107"/>
-      <c r="B20" s="50"/>
-      <c r="C20" s="108"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="108"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="113"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="113"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="111"/>
-      <c r="M20" s="49"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="111"/>
-      <c r="P20" s="49"/>
-      <c r="Q20" s="50"/>
+      <c r="A20" s="134"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="126"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="126"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="128"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="128"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="62"/>
       <c r="R20" s="32"/>
       <c r="S20" s="32"/>
       <c r="T20" s="33"/>
@@ -13130,23 +13005,23 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="107"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="108"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="113"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="111"/>
-      <c r="M21" s="49"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="49"/>
-      <c r="Q21" s="50"/>
+      <c r="A21" s="134"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="126"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="126"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="128"/>
+      <c r="M21" s="61"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="128"/>
+      <c r="P21" s="61"/>
+      <c r="Q21" s="62"/>
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="33"/>
@@ -13158,23 +13033,23 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="107"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="108"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="108"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="113"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="113"/>
-      <c r="K22" s="50"/>
-      <c r="L22" s="111"/>
-      <c r="M22" s="49"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="111"/>
-      <c r="P22" s="49"/>
-      <c r="Q22" s="50"/>
+      <c r="A22" s="134"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="135"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="126"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="126"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="128"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="128"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="62"/>
       <c r="R22" s="32"/>
       <c r="S22" s="32"/>
       <c r="T22" s="33"/>
@@ -13186,23 +13061,23 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="107"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="108"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="113"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="113"/>
-      <c r="K23" s="50"/>
-      <c r="L23" s="111"/>
-      <c r="M23" s="49"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="111"/>
-      <c r="P23" s="49"/>
-      <c r="Q23" s="50"/>
+      <c r="A23" s="134"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="135"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="135"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="126"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="126"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="128"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="62"/>
+      <c r="O23" s="128"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="62"/>
       <c r="R23" s="32"/>
       <c r="S23" s="32"/>
       <c r="T23" s="33"/>
@@ -13214,23 +13089,23 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="107"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="108"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="108"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="113"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="113"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="49"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="111"/>
-      <c r="P24" s="49"/>
-      <c r="Q24" s="50"/>
+      <c r="A24" s="134"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="135"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="126"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="126"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="128"/>
+      <c r="M24" s="61"/>
+      <c r="N24" s="62"/>
+      <c r="O24" s="128"/>
+      <c r="P24" s="61"/>
+      <c r="Q24" s="62"/>
       <c r="R24" s="32"/>
       <c r="S24" s="32"/>
       <c r="T24" s="33"/>
@@ -13242,23 +13117,23 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="107"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="108"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="113"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="113"/>
-      <c r="K25" s="50"/>
-      <c r="L25" s="111"/>
-      <c r="M25" s="49"/>
-      <c r="N25" s="50"/>
-      <c r="O25" s="111"/>
-      <c r="P25" s="49"/>
-      <c r="Q25" s="50"/>
+      <c r="A25" s="134"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="135"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="135"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="126"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="126"/>
+      <c r="K25" s="62"/>
+      <c r="L25" s="128"/>
+      <c r="M25" s="61"/>
+      <c r="N25" s="62"/>
+      <c r="O25" s="128"/>
+      <c r="P25" s="61"/>
+      <c r="Q25" s="62"/>
       <c r="R25" s="32"/>
       <c r="S25" s="32"/>
       <c r="T25" s="33"/>
@@ -13270,23 +13145,23 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="107"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="108"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="108"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="113"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="113"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="111"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="111"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="50"/>
+      <c r="A26" s="134"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="135"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="126"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="126"/>
+      <c r="K26" s="62"/>
+      <c r="L26" s="128"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="62"/>
+      <c r="O26" s="128"/>
+      <c r="P26" s="61"/>
+      <c r="Q26" s="62"/>
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
       <c r="T26" s="33"/>
@@ -13298,23 +13173,23 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="107"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="108"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="113"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="113"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="111"/>
-      <c r="M27" s="49"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="111"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="50"/>
+      <c r="A27" s="134"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="135"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="135"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="126"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="126"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="128"/>
+      <c r="M27" s="61"/>
+      <c r="N27" s="62"/>
+      <c r="O27" s="128"/>
+      <c r="P27" s="61"/>
+      <c r="Q27" s="62"/>
       <c r="R27" s="32"/>
       <c r="S27" s="32"/>
       <c r="T27" s="33"/>
@@ -13326,23 +13201,23 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="107"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="108"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="108"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="113"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="113"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="111"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="111"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="50"/>
+      <c r="A28" s="134"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="135"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="135"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="126"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="126"/>
+      <c r="K28" s="62"/>
+      <c r="L28" s="128"/>
+      <c r="M28" s="61"/>
+      <c r="N28" s="62"/>
+      <c r="O28" s="128"/>
+      <c r="P28" s="61"/>
+      <c r="Q28" s="62"/>
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="33"/>
@@ -13354,23 +13229,23 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="107"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="108"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="113"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="113"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="111"/>
-      <c r="M29" s="49"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="111"/>
-      <c r="P29" s="49"/>
-      <c r="Q29" s="50"/>
+      <c r="A29" s="134"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="135"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="135"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="126"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="126"/>
+      <c r="K29" s="62"/>
+      <c r="L29" s="128"/>
+      <c r="M29" s="61"/>
+      <c r="N29" s="62"/>
+      <c r="O29" s="128"/>
+      <c r="P29" s="61"/>
+      <c r="Q29" s="62"/>
       <c r="R29" s="32"/>
       <c r="S29" s="32"/>
       <c r="T29" s="33"/>
@@ -13382,23 +13257,23 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="107"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="108"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="108"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="113"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="113"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="111"/>
-      <c r="M30" s="49"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="111"/>
-      <c r="P30" s="49"/>
-      <c r="Q30" s="50"/>
+      <c r="A30" s="134"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="135"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="126"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="126"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="128"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="128"/>
+      <c r="P30" s="61"/>
+      <c r="Q30" s="62"/>
       <c r="R30" s="32"/>
       <c r="S30" s="32"/>
       <c r="T30" s="33"/>
@@ -13410,23 +13285,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="109"/>
-      <c r="B31" s="88"/>
-      <c r="C31" s="110"/>
-      <c r="D31" s="88"/>
-      <c r="E31" s="110"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="116"/>
-      <c r="H31" s="87"/>
-      <c r="I31" s="88"/>
-      <c r="J31" s="116"/>
-      <c r="K31" s="88"/>
-      <c r="L31" s="112"/>
-      <c r="M31" s="87"/>
-      <c r="N31" s="88"/>
-      <c r="O31" s="112"/>
-      <c r="P31" s="87"/>
-      <c r="Q31" s="88"/>
+      <c r="A31" s="137"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="138"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="138"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="127"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="127"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="129"/>
+      <c r="M31" s="66"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="129"/>
+      <c r="P31" s="66"/>
+      <c r="Q31" s="67"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -14424,62 +14299,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -14504,62 +14379,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/プロジェクト型演習_成果ドキュメント_一覧表示.xlsx
+++ b/プロジェクト型演習_成果ドキュメント_一覧表示.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\project-based-learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37E68DC-B82D-4E99-94F7-0DE7B98FFBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B849FB-58A8-4959-9C70-D6D99C489BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -18,15 +18,14 @@
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
     <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId6"/>
-    <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId7"/>
+    <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="84">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -272,36 +271,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>期限</t>
-    <rPh sb="0" eb="2">
-      <t>キゲン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>担当者情報</t>
-    <rPh sb="0" eb="5">
-      <t>タントウシャジョウホウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスク</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>カテゴリ</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ステータス</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>メモ</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>メニュー画面へ</t>
     <rPh sb="4" eb="6">
       <t>ガメン</t>
@@ -457,8 +426,8 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク情報が存在する場合：タスク一覧表示画面へ遷移し、タスク一覧を表形式で表示させる。
-タスク情報が存在しない場合：タスク一覧表示画面へ遷移し、情報が存在しない項目内容は空欄で表示される。</t>
+    <t>タスク情報が存在する場合：「タスク一覧表示画面」へ遷移し、タスク一覧を表形式で表示させる。
+タスク情報が存在しない場合：「タスク一覧表示画面」へ遷移し、情報が存在しない項目内容は空欄で表示される。</t>
     <rPh sb="3" eb="5">
       <t>ジョウホウ</t>
     </rPh>
@@ -468,58 +437,58 @@
     <rPh sb="10" eb="12">
       <t>バアイ</t>
     </rPh>
-    <rPh sb="16" eb="18">
+    <rPh sb="17" eb="19">
       <t>イチラン</t>
     </rPh>
-    <rPh sb="18" eb="22">
+    <rPh sb="19" eb="23">
       <t>ヒョウジガメン</t>
     </rPh>
-    <rPh sb="23" eb="25">
+    <rPh sb="25" eb="27">
       <t>センイ</t>
     </rPh>
-    <rPh sb="30" eb="32">
+    <rPh sb="32" eb="34">
       <t>イチラン</t>
     </rPh>
-    <rPh sb="33" eb="36">
+    <rPh sb="35" eb="38">
       <t>ヒョウケイシキ</t>
     </rPh>
-    <rPh sb="37" eb="39">
+    <rPh sb="39" eb="41">
       <t>ヒョウジ</t>
     </rPh>
-    <rPh sb="47" eb="49">
+    <rPh sb="49" eb="51">
       <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="50" eb="52">
+    <rPh sb="52" eb="54">
       <t>ソンザイ</t>
     </rPh>
-    <rPh sb="55" eb="57">
+    <rPh sb="57" eb="59">
       <t>バアイ</t>
     </rPh>
-    <rPh sb="61" eb="67">
+    <rPh sb="64" eb="70">
       <t>イチランヒョウジガメン</t>
     </rPh>
-    <rPh sb="68" eb="70">
+    <rPh sb="72" eb="74">
       <t>センイ</t>
     </rPh>
-    <rPh sb="72" eb="74">
+    <rPh sb="76" eb="78">
       <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="75" eb="77">
+    <rPh sb="79" eb="81">
       <t>ソンザイ</t>
     </rPh>
-    <rPh sb="80" eb="82">
+    <rPh sb="84" eb="86">
       <t>コウモク</t>
     </rPh>
-    <rPh sb="82" eb="84">
+    <rPh sb="86" eb="88">
       <t>ナイヨウ</t>
     </rPh>
-    <rPh sb="83" eb="84">
+    <rPh sb="87" eb="88">
       <t>カタチ</t>
     </rPh>
-    <rPh sb="85" eb="87">
+    <rPh sb="89" eb="91">
       <t>クウラン</t>
     </rPh>
-    <rPh sb="88" eb="90">
+    <rPh sb="92" eb="94">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -532,7 +501,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -595,43 +564,8 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="ＭＳ ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -644,14 +578,8 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="74">
+  <borders count="68">
     <border>
       <left/>
       <right/>
@@ -1422,81 +1350,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1641,107 +1499,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1750,90 +1524,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1844,6 +1546,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1875,17 +1580,152 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1899,213 +1739,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2863,15 +2504,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>125344</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>55218</xdr:rowOff>
+      <xdr:colOff>92872</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>115687</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1021522</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>69023</xdr:rowOff>
+      <xdr:colOff>998404</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>22950</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -2886,8 +2527,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="125344" y="3865218"/>
-          <a:ext cx="8596898" cy="4049822"/>
+          <a:off x="92872" y="2973187"/>
+          <a:ext cx="8610577" cy="5239562"/>
           <a:chOff x="9442174" y="4540527"/>
           <a:chExt cx="2671142" cy="4155109"/>
         </a:xfrm>
@@ -2988,16 +2629,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>992640</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>123436</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>664898</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>533</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>339743</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>135737</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>12001</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>12834</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -3012,8 +2653,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3123657" y="1350385"/>
-          <a:ext cx="2688925" cy="1949589"/>
+          <a:off x="5027688" y="1080600"/>
+          <a:ext cx="2689358" cy="1951319"/>
           <a:chOff x="1120775" y="3770428"/>
           <a:chExt cx="2701512" cy="1912822"/>
         </a:xfrm>
@@ -3203,7 +2844,7 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                 </a:rPr>
-                <a:t>LoginServlet</a:t>
+                <a:t>ViewServlet</a:t>
               </a:r>
               <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
                 <a:solidFill>
@@ -3254,7 +2895,7 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                 </a:rPr>
-                <a:t>+ LoginServlet()</a:t>
+                <a:t>+ ViewServlet()</a:t>
               </a:r>
             </a:p>
             <a:p>
@@ -3399,16 +3040,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1305</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>97691</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1025475</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>103901</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>881289</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>64328</xdr:rowOff>
+      <xdr:colOff>789088</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>118871</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -3423,8 +3064,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4360203" y="4392013"/>
-          <a:ext cx="4221806" cy="3034010"/>
+          <a:off x="4274180" y="3607740"/>
+          <a:ext cx="4219953" cy="3569836"/>
           <a:chOff x="320588" y="4493617"/>
           <a:chExt cx="4244135" cy="3112578"/>
         </a:xfrm>
@@ -3554,9 +3195,9 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="677202" y="6115772"/>
+            <a:off x="677202" y="6160856"/>
             <a:ext cx="3523190" cy="1322757"/>
-            <a:chOff x="514211" y="1346979"/>
+            <a:chOff x="514211" y="1390994"/>
             <a:chExt cx="2470840" cy="1291403"/>
           </a:xfrm>
         </xdr:grpSpPr>
@@ -3573,7 +3214,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="514292" y="1346979"/>
+              <a:off x="514292" y="1390994"/>
               <a:ext cx="2470759" cy="1291403"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3851,10 +3492,10 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="581606" y="4946625"/>
-            <a:ext cx="3710477" cy="713774"/>
-            <a:chOff x="568117" y="1521325"/>
-            <a:chExt cx="2269360" cy="699956"/>
+            <a:off x="578269" y="4983457"/>
+            <a:ext cx="3707701" cy="713774"/>
+            <a:chOff x="566076" y="1557444"/>
+            <a:chExt cx="2267662" cy="699956"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
@@ -3870,7 +3511,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="570527" y="1521325"/>
+              <a:off x="566076" y="1557444"/>
               <a:ext cx="2266950" cy="699956"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3912,7 +3553,7 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                 </a:rPr>
-                <a:t>UserDAO</a:t>
+                <a:t>taskDAO</a:t>
               </a:r>
             </a:p>
             <a:p>
@@ -3931,7 +3572,7 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                 </a:rPr>
-                <a:t>+ login(userId</a:t>
+                <a:t>+ selectAll()</a:t>
               </a:r>
               <a:r>
                 <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
@@ -3947,23 +3588,7 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                 </a:rPr>
-                <a:t>String)</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                </a:rPr>
-                <a:t>：</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                </a:rPr>
-                <a:t>UserBean</a:t>
+                <a:t>TaskBean</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -4017,15 +3642,12 @@
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
-            <xdr:cNvCxnSpPr>
-              <a:stCxn id="13" idx="1"/>
-              <a:endCxn id="13" idx="3"/>
-            </xdr:cNvCxnSpPr>
+            <xdr:cNvCxnSpPr/>
           </xdr:nvCxnSpPr>
           <xdr:spPr>
-            <a:xfrm>
-              <a:off x="570527" y="1871303"/>
-              <a:ext cx="2266950" cy="0"/>
+            <a:xfrm flipV="1">
+              <a:off x="577406" y="1858269"/>
+              <a:ext cx="2244221" cy="1"/>
             </a:xfrm>
             <a:prstGeom prst="line">
               <a:avLst/>
@@ -4058,15 +3680,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1735</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>70231</xdr:rowOff>
+      <xdr:colOff>57841</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>99869</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>816348</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>48661</xdr:rowOff>
+      <xdr:colOff>745933</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>153081</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -4081,10 +3703,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="340760" y="4364553"/>
-          <a:ext cx="3720546" cy="3368684"/>
-          <a:chOff x="4859129" y="4334564"/>
-          <a:chExt cx="3740979" cy="3454333"/>
+          <a:off x="398020" y="3603708"/>
+          <a:ext cx="3596618" cy="4416002"/>
+          <a:chOff x="4847659" y="3844680"/>
+          <a:chExt cx="3458537" cy="4142531"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
@@ -4100,10 +3722,10 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="4859129" y="4334564"/>
-            <a:ext cx="3740979" cy="3454333"/>
-            <a:chOff x="9442174" y="4583043"/>
-            <a:chExt cx="2671142" cy="2999441"/>
+            <a:off x="4847659" y="3844680"/>
+            <a:ext cx="3458537" cy="4142531"/>
+            <a:chOff x="9433983" y="4157672"/>
+            <a:chExt cx="2469472" cy="3597013"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
@@ -4119,8 +3741,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9442174" y="4746195"/>
-              <a:ext cx="2671142" cy="2836289"/>
+              <a:off x="9434474" y="4327967"/>
+              <a:ext cx="2468981" cy="3426718"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4166,7 +3788,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9442176" y="4583043"/>
+              <a:off x="9433983" y="4157672"/>
               <a:ext cx="1096168" cy="164543"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4211,10 +3833,10 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="5081933" y="4820448"/>
-            <a:ext cx="3324316" cy="2761497"/>
-            <a:chOff x="560044" y="1333501"/>
-            <a:chExt cx="2278406" cy="2699120"/>
+            <a:off x="5029199" y="4284351"/>
+            <a:ext cx="2984958" cy="3543305"/>
+            <a:chOff x="523901" y="809513"/>
+            <a:chExt cx="2045819" cy="3463267"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
@@ -4230,8 +3852,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="561975" y="1333501"/>
-              <a:ext cx="2266950" cy="2699120"/>
+              <a:off x="530909" y="809513"/>
+              <a:ext cx="2038811" cy="3463267"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4272,7 +3894,7 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                 </a:rPr>
-                <a:t>UserBean</a:t>
+                <a:t>TaskBean</a:t>
               </a:r>
             </a:p>
             <a:p>
@@ -4291,7 +3913,7 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                 </a:rPr>
-                <a:t> userId</a:t>
+                <a:t> taskName</a:t>
               </a:r>
               <a:r>
                 <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" u="none" baseline="0">
@@ -4318,7 +3940,7 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                 </a:rPr>
-                <a:t>- password</a:t>
+                <a:t>- categoryName</a:t>
               </a:r>
               <a:r>
                 <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" u="none" baseline="0">
@@ -4335,6 +3957,33 @@
                   </a:solidFill>
                 </a:rPr>
                 <a:t>String</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" u="none" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>- limitDate</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" u="none" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>：</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" u="none" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>Date</a:t>
               </a:r>
             </a:p>
             <a:p>
@@ -4367,47 +4016,12 @@
             <a:p>
               <a:pPr algn="l"/>
               <a:r>
-                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" u="none" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                </a:rPr>
-                <a:t>- updateDatetime</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" u="none" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                </a:rPr>
-                <a:t>：</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" u="none" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                </a:rPr>
-                <a:t>Timestamp</a:t>
-              </a:r>
-            </a:p>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-              </a:endParaRPr>
-            </a:p>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:r>
                 <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                 </a:rPr>
-                <a:t>+ getUserId()</a:t>
+                <a:t>- statusName </a:t>
               </a:r>
               <a:r>
                 <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
@@ -4434,7 +4048,69 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                 </a:rPr>
-                <a:t>+ setUserId(userId</a:t>
+                <a:t>- memo </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>：</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>String</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>+ getTaskName()</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>：</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>String</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>+ setTaskName(taskName</a:t>
               </a:r>
               <a:r>
                 <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
@@ -4477,7 +4153,7 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                 </a:rPr>
-                <a:t>+ getPassword()</a:t>
+                <a:t>+ getCategoryName()</a:t>
               </a:r>
               <a:r>
                 <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
@@ -4504,7 +4180,77 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                 </a:rPr>
-                <a:t>+ setPassword(password</a:t>
+                <a:t>+ setCategoryName(categoryName</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>：</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>String)</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>：</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>void</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>+ getLimitDate()</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>：</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>String</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>+ setLimitDate(limitDate</a:t>
               </a:r>
               <a:r>
                 <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
@@ -4617,7 +4363,7 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                 </a:rPr>
-                <a:t>+ getUpdateDatetime()</a:t>
+                <a:t>+ getStatusName()</a:t>
               </a:r>
               <a:r>
                 <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
@@ -4644,7 +4390,7 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                 </a:rPr>
-                <a:t>+ setUpdateDatetime(updateDatetime</a:t>
+                <a:t>+ setStatusName(statusName</a:t>
               </a:r>
               <a:r>
                 <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
@@ -4679,6 +4425,92 @@
                 <a:t>void</a:t>
               </a:r>
             </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>+ getMemo()</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>：</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>String</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>+ setMemo(memo</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>：</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>String)</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>：</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>void</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
           </xdr:txBody>
         </xdr:sp>
         <xdr:cxnSp macro="">
@@ -4694,8 +4526,8 @@
           </xdr:nvCxnSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="560044" y="1569773"/>
-              <a:ext cx="2269689" cy="0"/>
+              <a:off x="523901" y="1028977"/>
+              <a:ext cx="2034608" cy="7798"/>
             </a:xfrm>
             <a:prstGeom prst="line">
               <a:avLst/>
@@ -4734,8 +4566,8 @@
           </xdr:nvCxnSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="561392" y="2367104"/>
-              <a:ext cx="2277058" cy="0"/>
+              <a:off x="540716" y="2073856"/>
+              <a:ext cx="2029002" cy="7798"/>
             </a:xfrm>
             <a:prstGeom prst="line">
               <a:avLst/>
@@ -4768,15 +4600,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>991814</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>104289</xdr:rowOff>
+      <xdr:colOff>896229</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>30142</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>991854</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>65011</xdr:rowOff>
+      <xdr:colOff>903504</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>77082</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4794,8 +4626,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6456978" y="5413305"/>
-          <a:ext cx="40" cy="429165"/>
+          <a:off x="6369068" y="4970227"/>
+          <a:ext cx="7275" cy="531262"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4827,36 +4659,95 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>89723</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>145985</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>914587</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>53807</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>415639</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>51956</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>914587</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>82030</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="92" name="コネクタ: カギ線 91">
+        <xdr:cNvPr id="94" name="コネクタ: カギ線 93">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01F6634E-216B-3BEA-A9AD-0FB0202121AE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32CE27D6-67FF-B54B-5F2B-F24E05F35726}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="3060581" y="2578506"/>
+          <a:ext cx="2226325" cy="1474187"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 100000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:prstDash val="sysDash"/>
+          <a:tailEnd type="arrow" w="lg" len="lg"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>906854</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>39528</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>907282</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>138186</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="102" name="直線矢印コネクタ 101">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08CB6C26-659B-9219-F0D6-DBC52D1483E8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="24" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5591232" y="2543657"/>
-          <a:ext cx="1442640" cy="2369333"/>
+          <a:off x="6379693" y="2719443"/>
+          <a:ext cx="428" cy="1067302"/>
         </a:xfrm>
-        <a:prstGeom prst="bentConnector2">
+        <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
         <a:ln w="19050">
@@ -4886,112 +4777,190 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>590791</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>145985</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>51210</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>153630</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>138746</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>61057</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1095887</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>51210</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="94" name="コネクタ: カギ線 93">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="105" name="テキスト ボックス 104">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32CE27D6-67FF-B54B-5F2B-F24E05F35726}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09992EC9-D46F-7DB0-F74D-B06F66A4A846}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="2" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm rot="10800000" flipV="1">
-          <a:off x="2742127" y="2543657"/>
-          <a:ext cx="664679" cy="2378434"/>
+        <a:xfrm>
+          <a:off x="727178" y="1218791"/>
+          <a:ext cx="2499032" cy="1208548"/>
         </a:xfrm>
-        <a:prstGeom prst="bentConnector2">
+        <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="19050" cmpd="sng">
           <a:solidFill>
             <a:schemeClr val="tx1"/>
           </a:solidFill>
-          <a:prstDash val="sysDash"/>
-          <a:tailEnd type="arrow" w="lg" len="lg"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
+          <a:schemeClr val="dk1"/>
         </a:fontRef>
       </xdr:style>
-    </xdr:cxnSp>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>WebContent</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>266290</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>51210</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>788629</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>30726</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="106" name="フローチャート: 処理 105">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CF372D2-1490-14C3-2F9F-D2100DF07EB1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="942258" y="1607984"/>
+          <a:ext cx="1976694" cy="471129"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>&lt;&lt;JSP&gt;&gt;</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>view.jsp</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>430161</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>61451</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>436084</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>103283</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="102" name="直線矢印コネクタ 101">
+        <xdr:cNvPr id="115" name="直線矢印コネクタ 114">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08CB6C26-659B-9219-F0D6-DBC52D1483E8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29AA7BAB-599D-AA45-936B-E59E38E2CF86}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="3873500" y="5410200"/>
-          <a:ext cx="762000" cy="0"/>
+        <a:xfrm>
+          <a:off x="2576155" y="2425487"/>
+          <a:ext cx="5923" cy="1648459"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
         <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
           <a:prstDash val="sysDash"/>
+          <a:headEnd w="sm" len="sm"/>
           <a:tailEnd type="arrow" w="lg" len="lg"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="dk1"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="dk1"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="dk1"/>
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="tx1"/>
@@ -5463,28 +5432,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA498F99-F6C9-4CB9-9746-AAA03D333707}" name="テーブル1" displayName="テーブル1" ref="A1:F2" insertRow="1" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:F2" xr:uid="{AA498F99-F6C9-4CB9-9746-AAA03D333707}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{A751ED3E-8687-49E8-AF06-7093CF569AD7}" name="タスク" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{2057FEB7-6810-4FA2-B76B-657FE8BA58DD}" name="カテゴリ" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{1D2F16BC-B599-4D57-8038-6B8E28F40C1C}" name="期限" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{11146246-3441-451A-894B-243A5EC6B1FE}" name="担当者情報" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{9692A1AA-C1FA-481F-9AB3-486A8613D028}" name="ステータス" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{147F4C38-F038-4FEA-800F-DF90FA15194F}" name="メモ" dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -5692,21 +5639,21 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="103" t="s">
+      <c r="C2" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="104"/>
-      <c r="J2" s="104"/>
-      <c r="K2" s="104"/>
-      <c r="L2" s="104"/>
-      <c r="M2" s="104"/>
-      <c r="N2" s="104"/>
-      <c r="O2" s="104"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="94"/>
+      <c r="L2" s="94"/>
+      <c r="M2" s="94"/>
+      <c r="N2" s="94"/>
+      <c r="O2" s="94"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
@@ -5790,7 +5737,7 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="105" t="s">
+      <c r="E8" s="95" t="s">
         <v>65</v>
       </c>
       <c r="F8" s="90"/>
@@ -5807,29 +5754,29 @@
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="101" t="s">
+      <c r="G13" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="62"/>
-      <c r="I13" s="106">
+      <c r="H13" s="52"/>
+      <c r="I13" s="96">
         <v>46230</v>
       </c>
-      <c r="J13" s="61"/>
-      <c r="K13" s="62"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="52"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="101"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="101"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="62"/>
+      <c r="G14" s="91"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="52"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="101"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="101"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="62"/>
+      <c r="G15" s="91"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="52"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -5838,7 +5785,7 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="102" t="s">
+      <c r="G17" s="92" t="s">
         <v>64</v>
       </c>
       <c r="H17" s="90"/>
@@ -6858,19 +6805,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="102" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="87"/>
       <c r="C1" s="88"/>
-      <c r="D1" s="95" t="s">
+      <c r="D1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="95" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="83"/>
+      <c r="G1" s="55"/>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
@@ -6884,192 +6831,192 @@
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="89"/>
       <c r="B2" s="90"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="96" t="s">
+      <c r="C2" s="78"/>
+      <c r="D2" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="97"/>
-      <c r="F2" s="96" t="s">
+      <c r="E2" s="76"/>
+      <c r="F2" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="97"/>
-      <c r="H2" s="100">
+      <c r="G2" s="76"/>
+      <c r="H2" s="81">
         <v>46231</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="78"/>
+      <c r="J2" s="84"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="89"/>
       <c r="B3" s="90"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="79"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="85"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="92"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="80"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="98"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="84" t="s">
-        <v>81</v>
+      <c r="B5" s="54"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="100" t="s">
+        <v>75</v>
       </c>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="85"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="64"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="101" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="70" t="s">
+      <c r="B6" s="49"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="50"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="101" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="49"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="50"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="101" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="49"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="50"/>
+    </row>
+    <row r="9" spans="1:10" ht="87.75" customHeight="1">
+      <c r="A9" s="111" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="114" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="52"/>
+      <c r="D9" s="107" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="50"/>
+    </row>
+    <row r="10" spans="1:10" ht="100.5" customHeight="1">
+      <c r="A10" s="112"/>
+      <c r="B10" s="114" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="52"/>
+      <c r="D10" s="107" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="50"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="113"/>
+      <c r="B11" s="114" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="52"/>
+      <c r="D11" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="50"/>
+    </row>
+    <row r="12" spans="1:10" ht="34.5" customHeight="1">
+      <c r="A12" s="101" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="49"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="107" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="64"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="60" t="s">
-        <v>10</v>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="50"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A13" s="108" t="s">
+        <v>17</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="64"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="60" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="70" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="64"/>
-    </row>
-    <row r="9" spans="1:10" ht="87.75" customHeight="1">
-      <c r="A9" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="74" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="62"/>
-      <c r="D9" s="63" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="64"/>
-    </row>
-    <row r="10" spans="1:10" ht="100.5" customHeight="1">
-      <c r="A10" s="72"/>
-      <c r="B10" s="74" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="64"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="73"/>
-      <c r="B11" s="74" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="62"/>
-      <c r="D11" s="70" t="s">
+      <c r="B13" s="58"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="64"/>
-    </row>
-    <row r="12" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A12" s="60" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="61"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="63" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="64"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="68" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="139"/>
-      <c r="F13" s="139"/>
-      <c r="G13" s="139"/>
-      <c r="H13" s="139"/>
-      <c r="I13" s="139"/>
-      <c r="J13" s="140"/>
+      <c r="E13" s="109"/>
+      <c r="F13" s="109"/>
+      <c r="G13" s="109"/>
+      <c r="H13" s="109"/>
+      <c r="I13" s="109"/>
+      <c r="J13" s="110"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8060,18 +8007,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -8087,6 +8022,18 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -8105,19 +8052,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="86" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="87"/>
       <c r="C1" s="88"/>
-      <c r="D1" s="95" t="s">
+      <c r="D1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="95" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="83"/>
+      <c r="G1" s="55"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -8131,46 +8078,46 @@
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="89"/>
       <c r="B2" s="90"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="96" t="s">
+      <c r="C2" s="78"/>
+      <c r="D2" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="97"/>
-      <c r="F2" s="96" t="s">
+      <c r="E2" s="76"/>
+      <c r="F2" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="97"/>
-      <c r="H2" s="100">
+      <c r="G2" s="76"/>
+      <c r="H2" s="81">
         <v>46230</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="78"/>
+      <c r="J2" s="84"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="89"/>
       <c r="B3" s="90"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="79"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="85"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="92"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="80"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="98"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -9527,19 +9474,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="86" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="87"/>
       <c r="C1" s="88"/>
-      <c r="D1" s="95" t="s">
+      <c r="D1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="95" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="83"/>
+      <c r="G1" s="55"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -9553,46 +9500,46 @@
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="89"/>
       <c r="B2" s="90"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="96" t="s">
+      <c r="C2" s="78"/>
+      <c r="D2" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="97"/>
-      <c r="F2" s="96" t="s">
+      <c r="E2" s="76"/>
+      <c r="F2" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="97"/>
-      <c r="H2" s="100">
+      <c r="G2" s="76"/>
+      <c r="H2" s="81">
         <v>46231</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="78"/>
+      <c r="J2" s="84"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="89"/>
       <c r="B3" s="90"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="79"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="85"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A4" s="89"/>
-      <c r="B4" s="108"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="79"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="85"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="37"/>
@@ -10999,19 +10946,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="86" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="87"/>
       <c r="C1" s="88"/>
-      <c r="D1" s="95" t="s">
+      <c r="D1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="95" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="83"/>
+      <c r="G1" s="55"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -11025,188 +10972,188 @@
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="89"/>
       <c r="B2" s="90"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="96" t="s">
+      <c r="C2" s="78"/>
+      <c r="D2" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="97"/>
-      <c r="F2" s="96" t="s">
+      <c r="E2" s="76"/>
+      <c r="F2" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="97"/>
-      <c r="H2" s="100">
+      <c r="G2" s="76"/>
+      <c r="H2" s="81">
         <v>46231</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="78"/>
+      <c r="J2" s="84"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="89"/>
       <c r="B3" s="90"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="79"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="85"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
       <c r="A4" s="89"/>
       <c r="B4" s="90"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="79"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="85"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="109" t="s">
+      <c r="A5" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="115" t="s">
-        <v>87</v>
+      <c r="B5" s="54"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="63" t="s">
+        <v>81</v>
       </c>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="85"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="64"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="64"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="50"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="116"/>
-      <c r="B7" s="117"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="117"/>
-      <c r="H7" s="117"/>
-      <c r="I7" s="117"/>
-      <c r="J7" s="118"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="67"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="119"/>
-      <c r="B8" s="120"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="120"/>
-      <c r="I8" s="120"/>
-      <c r="J8" s="121"/>
+      <c r="A8" s="68"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="70"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="119"/>
-      <c r="B9" s="120"/>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="120"/>
-      <c r="H9" s="120"/>
-      <c r="I9" s="120"/>
-      <c r="J9" s="121"/>
+      <c r="A9" s="68"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="70"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="119"/>
-      <c r="B10" s="120"/>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120"/>
-      <c r="E10" s="120"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="120"/>
-      <c r="H10" s="120"/>
-      <c r="I10" s="120"/>
-      <c r="J10" s="121"/>
+      <c r="A10" s="68"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="70"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="119"/>
-      <c r="B11" s="120"/>
-      <c r="C11" s="120"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="120"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="120"/>
-      <c r="H11" s="120"/>
-      <c r="I11" s="120"/>
-      <c r="J11" s="121"/>
+      <c r="A11" s="68"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="70"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="119"/>
-      <c r="B12" s="120"/>
-      <c r="C12" s="120"/>
-      <c r="D12" s="120"/>
-      <c r="E12" s="120"/>
-      <c r="F12" s="120"/>
-      <c r="G12" s="120"/>
-      <c r="H12" s="120"/>
-      <c r="I12" s="120"/>
-      <c r="J12" s="121"/>
+      <c r="A12" s="68"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="70"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="122"/>
-      <c r="B13" s="123"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="123"/>
-      <c r="F13" s="123"/>
-      <c r="G13" s="123"/>
-      <c r="H13" s="123"/>
-      <c r="I13" s="123"/>
-      <c r="J13" s="124"/>
+      <c r="A13" s="71"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="73"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="111" t="s">
+      <c r="A14" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="64"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="50"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="111" t="s">
+      <c r="A15" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="70" t="s">
-        <v>86</v>
+      <c r="B15" s="49"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="48" t="s">
+        <v>80</v>
       </c>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="62"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="52"/>
       <c r="I15" s="14" t="s">
         <v>25</v>
       </c>
@@ -11215,11 +11162,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="111" t="s">
+      <c r="A16" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="62"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="52"/>
       <c r="D16" s="14" t="s">
         <v>27</v>
       </c>
@@ -11232,20 +11179,20 @@
       <c r="G16" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="125" t="s">
+      <c r="H16" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="61"/>
-      <c r="J16" s="64"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="50"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="112" t="s">
+      <c r="A17" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="113"/>
-      <c r="C17" s="114"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="62"/>
       <c r="D17" s="16" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>71</v>
@@ -11254,85 +11201,85 @@
         <v>67</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
-      <c r="H17" s="70" t="s">
-        <v>85</v>
+      <c r="H17" s="48" t="s">
+        <v>79</v>
       </c>
-      <c r="I17" s="61"/>
-      <c r="J17" s="64"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="50"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="112"/>
-      <c r="B18" s="61"/>
-      <c r="C18" s="62"/>
+      <c r="A18" s="51"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="52"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="64"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="50"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="112"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="62"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="52"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="64"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="50"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="112"/>
-      <c r="B20" s="61"/>
-      <c r="C20" s="62"/>
+      <c r="A20" s="51"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="52"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="64"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="50"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="112"/>
-      <c r="B21" s="61"/>
-      <c r="C21" s="62"/>
+      <c r="A21" s="51"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="52"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="64"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="50"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="112"/>
-      <c r="B22" s="61"/>
-      <c r="C22" s="62"/>
+      <c r="A22" s="51"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="52"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="61"/>
-      <c r="J22" s="64"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="50"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="110"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="67"/>
+      <c r="A23" s="57"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="59"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="66"/>
-      <c r="J23" s="69"/>
+      <c r="H23" s="79"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="80"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12313,16 +12260,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12339,11 +12281,16 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12353,64 +12300,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{300C5825-0E87-45EA-AE03-82526798BDE4}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="18.85546875" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:6" ht="18.75">
-      <c r="A1" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="D1" s="49" t="s">
-        <v>74</v>
-      </c>
-      <c r="E1" s="50" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="51" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="59"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="56"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="56"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="56"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="56"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="8"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
@@ -12421,7 +12310,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="102" t="s">
         <v>31</v>
       </c>
       <c r="B1" s="87"/>
@@ -12429,30 +12318,30 @@
       <c r="D1" s="87"/>
       <c r="E1" s="87"/>
       <c r="F1" s="88"/>
-      <c r="G1" s="95" t="s">
+      <c r="G1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="95" t="s">
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="95" t="s">
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="95" t="s">
+      <c r="P1" s="55"/>
+      <c r="Q1" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="83"/>
-      <c r="S1" s="95" t="s">
+      <c r="R1" s="55"/>
+      <c r="S1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="85"/>
+      <c r="T1" s="64"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="89"/>
@@ -12460,21 +12349,21 @@
       <c r="C2" s="90"/>
       <c r="D2" s="90"/>
       <c r="E2" s="90"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="130"/>
-      <c r="M2" s="130"/>
-      <c r="N2" s="97"/>
-      <c r="O2" s="96"/>
-      <c r="P2" s="97"/>
-      <c r="Q2" s="96"/>
-      <c r="R2" s="97"/>
-      <c r="S2" s="96"/>
-      <c r="T2" s="131"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="124"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="125"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="89"/>
@@ -12482,121 +12371,121 @@
       <c r="C3" s="90"/>
       <c r="D3" s="90"/>
       <c r="E3" s="90"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="98"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="77"/>
       <c r="H3" s="90"/>
       <c r="I3" s="90"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="98"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="77"/>
       <c r="L3" s="90"/>
       <c r="M3" s="90"/>
-      <c r="N3" s="91"/>
-      <c r="O3" s="98"/>
-      <c r="P3" s="91"/>
-      <c r="Q3" s="98"/>
-      <c r="R3" s="91"/>
-      <c r="S3" s="98"/>
-      <c r="T3" s="132"/>
+      <c r="N3" s="78"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="126"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="92"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="94"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="93"/>
-      <c r="M4" s="93"/>
-      <c r="N4" s="94"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="94"/>
-      <c r="Q4" s="99"/>
-      <c r="R4" s="94"/>
-      <c r="S4" s="99"/>
-      <c r="T4" s="133"/>
+      <c r="A4" s="103"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="106"/>
+      <c r="L4" s="104"/>
+      <c r="M4" s="104"/>
+      <c r="N4" s="105"/>
+      <c r="O4" s="106"/>
+      <c r="P4" s="105"/>
+      <c r="Q4" s="106"/>
+      <c r="R4" s="105"/>
+      <c r="S4" s="106"/>
+      <c r="T4" s="127"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="109" t="s">
+      <c r="A5" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="84" t="s">
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="100" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="82"/>
-      <c r="K5" s="82"/>
-      <c r="L5" s="82"/>
-      <c r="M5" s="82"/>
-      <c r="N5" s="82"/>
-      <c r="O5" s="82"/>
-      <c r="P5" s="82"/>
-      <c r="Q5" s="82"/>
-      <c r="R5" s="82"/>
-      <c r="S5" s="82"/>
-      <c r="T5" s="85"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="54"/>
+      <c r="Q5" s="54"/>
+      <c r="R5" s="54"/>
+      <c r="S5" s="54"/>
+      <c r="T5" s="64"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="70" t="s">
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="61"/>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="61"/>
-      <c r="S6" s="61"/>
-      <c r="T6" s="64"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+      <c r="R6" s="49"/>
+      <c r="S6" s="49"/>
+      <c r="T6" s="50"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="111" t="s">
+      <c r="A7" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="70" t="s">
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="61"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="61"/>
-      <c r="M7" s="61"/>
-      <c r="N7" s="61"/>
-      <c r="O7" s="61"/>
-      <c r="P7" s="61"/>
-      <c r="Q7" s="61"/>
-      <c r="R7" s="61"/>
-      <c r="S7" s="61"/>
-      <c r="T7" s="64"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="49"/>
+      <c r="R7" s="49"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="50"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -12795,37 +12684,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="111" t="s">
+      <c r="A15" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="136" t="s">
+      <c r="B15" s="52"/>
+      <c r="C15" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="62"/>
-      <c r="E15" s="125" t="s">
+      <c r="D15" s="52"/>
+      <c r="E15" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="62"/>
-      <c r="G15" s="125" t="s">
+      <c r="F15" s="52"/>
+      <c r="G15" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="61"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="125" t="s">
+      <c r="H15" s="49"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="62"/>
-      <c r="L15" s="125" t="s">
+      <c r="K15" s="52"/>
+      <c r="L15" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="61"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="125" t="s">
+      <c r="M15" s="49"/>
+      <c r="N15" s="52"/>
+      <c r="O15" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="61"/>
-      <c r="Q15" s="62"/>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="52"/>
       <c r="R15" s="14" t="s">
         <v>49</v>
       </c>
@@ -12837,37 +12726,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="134">
+      <c r="A16" s="116">
         <v>1</v>
       </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="135" t="s">
+      <c r="B16" s="52"/>
+      <c r="C16" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="62"/>
-      <c r="E16" s="135" t="s">
+      <c r="D16" s="52"/>
+      <c r="E16" s="117" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="62"/>
-      <c r="G16" s="126" t="s">
+      <c r="F16" s="52"/>
+      <c r="G16" s="122" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="61"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="126" t="s">
+      <c r="H16" s="49"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="122" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="62"/>
-      <c r="L16" s="128" t="s">
+      <c r="K16" s="52"/>
+      <c r="L16" s="120" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="61"/>
-      <c r="N16" s="62"/>
-      <c r="O16" s="128" t="s">
+      <c r="M16" s="49"/>
+      <c r="N16" s="52"/>
+      <c r="O16" s="120" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="61"/>
-      <c r="Q16" s="62"/>
+      <c r="P16" s="49"/>
+      <c r="Q16" s="52"/>
       <c r="R16" s="32"/>
       <c r="S16" s="32"/>
       <c r="T16" s="33"/>
@@ -12879,37 +12768,37 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="134">
+      <c r="A17" s="116">
         <v>2</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="135" t="s">
+      <c r="B17" s="52"/>
+      <c r="C17" s="117" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="62"/>
-      <c r="E17" s="135" t="s">
+      <c r="D17" s="52"/>
+      <c r="E17" s="117" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="62"/>
-      <c r="G17" s="126" t="s">
+      <c r="F17" s="52"/>
+      <c r="G17" s="122" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="61"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="126" t="s">
+      <c r="H17" s="49"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="122" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="62"/>
-      <c r="L17" s="128" t="s">
+      <c r="K17" s="52"/>
+      <c r="L17" s="120" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="61"/>
-      <c r="N17" s="62"/>
-      <c r="O17" s="128" t="s">
+      <c r="M17" s="49"/>
+      <c r="N17" s="52"/>
+      <c r="O17" s="120" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="61"/>
-      <c r="Q17" s="62"/>
+      <c r="P17" s="49"/>
+      <c r="Q17" s="52"/>
       <c r="R17" s="32"/>
       <c r="S17" s="32"/>
       <c r="T17" s="33"/>
@@ -12921,23 +12810,23 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="134"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="135"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="126"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="126"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="128"/>
-      <c r="M18" s="61"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="128"/>
-      <c r="P18" s="61"/>
-      <c r="Q18" s="62"/>
+      <c r="A18" s="116"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="122"/>
+      <c r="K18" s="52"/>
+      <c r="L18" s="120"/>
+      <c r="M18" s="49"/>
+      <c r="N18" s="52"/>
+      <c r="O18" s="120"/>
+      <c r="P18" s="49"/>
+      <c r="Q18" s="52"/>
       <c r="R18" s="32"/>
       <c r="S18" s="32"/>
       <c r="T18" s="33"/>
@@ -12949,23 +12838,23 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="134"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="135"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="135"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="126"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="126"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="128"/>
-      <c r="M19" s="61"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="128"/>
-      <c r="P19" s="61"/>
-      <c r="Q19" s="62"/>
+      <c r="A19" s="116"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="122"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="122"/>
+      <c r="K19" s="52"/>
+      <c r="L19" s="120"/>
+      <c r="M19" s="49"/>
+      <c r="N19" s="52"/>
+      <c r="O19" s="120"/>
+      <c r="P19" s="49"/>
+      <c r="Q19" s="52"/>
       <c r="R19" s="32"/>
       <c r="S19" s="32"/>
       <c r="T19" s="33"/>
@@ -12977,23 +12866,23 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="134"/>
-      <c r="B20" s="62"/>
-      <c r="C20" s="135"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="126"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="126"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="128"/>
-      <c r="M20" s="61"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="128"/>
-      <c r="P20" s="61"/>
-      <c r="Q20" s="62"/>
+      <c r="A20" s="116"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="122"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="122"/>
+      <c r="K20" s="52"/>
+      <c r="L20" s="120"/>
+      <c r="M20" s="49"/>
+      <c r="N20" s="52"/>
+      <c r="O20" s="120"/>
+      <c r="P20" s="49"/>
+      <c r="Q20" s="52"/>
       <c r="R20" s="32"/>
       <c r="S20" s="32"/>
       <c r="T20" s="33"/>
@@ -13005,23 +12894,23 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="134"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="135"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="135"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="126"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="126"/>
-      <c r="K21" s="62"/>
-      <c r="L21" s="128"/>
-      <c r="M21" s="61"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="128"/>
-      <c r="P21" s="61"/>
-      <c r="Q21" s="62"/>
+      <c r="A21" s="116"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="117"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="122"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="122"/>
+      <c r="K21" s="52"/>
+      <c r="L21" s="120"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="52"/>
+      <c r="O21" s="120"/>
+      <c r="P21" s="49"/>
+      <c r="Q21" s="52"/>
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="33"/>
@@ -13033,23 +12922,23 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="134"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="135"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="126"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="126"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="128"/>
-      <c r="M22" s="61"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="128"/>
-      <c r="P22" s="61"/>
-      <c r="Q22" s="62"/>
+      <c r="A22" s="116"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="122"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="122"/>
+      <c r="K22" s="52"/>
+      <c r="L22" s="120"/>
+      <c r="M22" s="49"/>
+      <c r="N22" s="52"/>
+      <c r="O22" s="120"/>
+      <c r="P22" s="49"/>
+      <c r="Q22" s="52"/>
       <c r="R22" s="32"/>
       <c r="S22" s="32"/>
       <c r="T22" s="33"/>
@@ -13061,23 +12950,23 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="134"/>
-      <c r="B23" s="62"/>
-      <c r="C23" s="135"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="135"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="126"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="126"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="128"/>
-      <c r="M23" s="61"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="128"/>
-      <c r="P23" s="61"/>
-      <c r="Q23" s="62"/>
+      <c r="A23" s="116"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="122"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="122"/>
+      <c r="K23" s="52"/>
+      <c r="L23" s="120"/>
+      <c r="M23" s="49"/>
+      <c r="N23" s="52"/>
+      <c r="O23" s="120"/>
+      <c r="P23" s="49"/>
+      <c r="Q23" s="52"/>
       <c r="R23" s="32"/>
       <c r="S23" s="32"/>
       <c r="T23" s="33"/>
@@ -13089,23 +12978,23 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="134"/>
-      <c r="B24" s="62"/>
-      <c r="C24" s="135"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="126"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="126"/>
-      <c r="K24" s="62"/>
-      <c r="L24" s="128"/>
-      <c r="M24" s="61"/>
-      <c r="N24" s="62"/>
-      <c r="O24" s="128"/>
-      <c r="P24" s="61"/>
-      <c r="Q24" s="62"/>
+      <c r="A24" s="116"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="122"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="122"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="120"/>
+      <c r="M24" s="49"/>
+      <c r="N24" s="52"/>
+      <c r="O24" s="120"/>
+      <c r="P24" s="49"/>
+      <c r="Q24" s="52"/>
       <c r="R24" s="32"/>
       <c r="S24" s="32"/>
       <c r="T24" s="33"/>
@@ -13117,23 +13006,23 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="134"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="135"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="135"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="126"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="126"/>
-      <c r="K25" s="62"/>
-      <c r="L25" s="128"/>
-      <c r="M25" s="61"/>
-      <c r="N25" s="62"/>
-      <c r="O25" s="128"/>
-      <c r="P25" s="61"/>
-      <c r="Q25" s="62"/>
+      <c r="A25" s="116"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="122"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="122"/>
+      <c r="K25" s="52"/>
+      <c r="L25" s="120"/>
+      <c r="M25" s="49"/>
+      <c r="N25" s="52"/>
+      <c r="O25" s="120"/>
+      <c r="P25" s="49"/>
+      <c r="Q25" s="52"/>
       <c r="R25" s="32"/>
       <c r="S25" s="32"/>
       <c r="T25" s="33"/>
@@ -13145,23 +13034,23 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="134"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="135"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="126"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="126"/>
-      <c r="K26" s="62"/>
-      <c r="L26" s="128"/>
-      <c r="M26" s="61"/>
-      <c r="N26" s="62"/>
-      <c r="O26" s="128"/>
-      <c r="P26" s="61"/>
-      <c r="Q26" s="62"/>
+      <c r="A26" s="116"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="122"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="122"/>
+      <c r="K26" s="52"/>
+      <c r="L26" s="120"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="52"/>
+      <c r="O26" s="120"/>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="52"/>
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
       <c r="T26" s="33"/>
@@ -13173,23 +13062,23 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="134"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="135"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="135"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="126"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="126"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="128"/>
-      <c r="M27" s="61"/>
-      <c r="N27" s="62"/>
-      <c r="O27" s="128"/>
-      <c r="P27" s="61"/>
-      <c r="Q27" s="62"/>
+      <c r="A27" s="116"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="117"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="122"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="122"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="120"/>
+      <c r="M27" s="49"/>
+      <c r="N27" s="52"/>
+      <c r="O27" s="120"/>
+      <c r="P27" s="49"/>
+      <c r="Q27" s="52"/>
       <c r="R27" s="32"/>
       <c r="S27" s="32"/>
       <c r="T27" s="33"/>
@@ -13201,23 +13090,23 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="134"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="135"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="135"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="126"/>
-      <c r="H28" s="61"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="126"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="128"/>
-      <c r="M28" s="61"/>
-      <c r="N28" s="62"/>
-      <c r="O28" s="128"/>
-      <c r="P28" s="61"/>
-      <c r="Q28" s="62"/>
+      <c r="A28" s="116"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="122"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="122"/>
+      <c r="K28" s="52"/>
+      <c r="L28" s="120"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="52"/>
+      <c r="O28" s="120"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="52"/>
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="33"/>
@@ -13229,23 +13118,23 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="134"/>
-      <c r="B29" s="62"/>
-      <c r="C29" s="135"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="135"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="126"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="126"/>
-      <c r="K29" s="62"/>
-      <c r="L29" s="128"/>
-      <c r="M29" s="61"/>
-      <c r="N29" s="62"/>
-      <c r="O29" s="128"/>
-      <c r="P29" s="61"/>
-      <c r="Q29" s="62"/>
+      <c r="A29" s="116"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="117"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="122"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="122"/>
+      <c r="K29" s="52"/>
+      <c r="L29" s="120"/>
+      <c r="M29" s="49"/>
+      <c r="N29" s="52"/>
+      <c r="O29" s="120"/>
+      <c r="P29" s="49"/>
+      <c r="Q29" s="52"/>
       <c r="R29" s="32"/>
       <c r="S29" s="32"/>
       <c r="T29" s="33"/>
@@ -13257,23 +13146,23 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="134"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="135"/>
-      <c r="D30" s="62"/>
-      <c r="E30" s="135"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="126"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="126"/>
-      <c r="K30" s="62"/>
-      <c r="L30" s="128"/>
-      <c r="M30" s="61"/>
-      <c r="N30" s="62"/>
-      <c r="O30" s="128"/>
-      <c r="P30" s="61"/>
-      <c r="Q30" s="62"/>
+      <c r="A30" s="116"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="122"/>
+      <c r="H30" s="49"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="122"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="120"/>
+      <c r="M30" s="49"/>
+      <c r="N30" s="52"/>
+      <c r="O30" s="120"/>
+      <c r="P30" s="49"/>
+      <c r="Q30" s="52"/>
       <c r="R30" s="32"/>
       <c r="S30" s="32"/>
       <c r="T30" s="33"/>
@@ -13285,23 +13174,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="137"/>
-      <c r="B31" s="67"/>
-      <c r="C31" s="138"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="138"/>
-      <c r="F31" s="67"/>
-      <c r="G31" s="127"/>
-      <c r="H31" s="66"/>
-      <c r="I31" s="67"/>
-      <c r="J31" s="127"/>
-      <c r="K31" s="67"/>
-      <c r="L31" s="129"/>
-      <c r="M31" s="66"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="129"/>
-      <c r="P31" s="66"/>
-      <c r="Q31" s="67"/>
+      <c r="A31" s="118"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="119"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="119"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="128"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="128"/>
+      <c r="K31" s="59"/>
+      <c r="L31" s="121"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="59"/>
+      <c r="O31" s="121"/>
+      <c r="P31" s="58"/>
+      <c r="Q31" s="59"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -14299,6 +14188,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -14323,118 +14324,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/プロジェクト型演習_成果ドキュメント_一覧表示.xlsx
+++ b/プロジェクト型演習_成果ドキュメント_一覧表示.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\project-based-learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B849FB-58A8-4959-9C70-D6D99C489BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CB2369-56B1-4923-A55F-55E3B9EDB14B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="85">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -382,10 +382,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>menu-servlet</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>タスク一覧表示画面</t>
     <rPh sb="3" eb="7">
       <t>イチランヒョウジ</t>
@@ -396,38 +392,17 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">基本フロー2：各項目内に該当するタスク情報が存在しなかった場合。
-1. 空欄で表示する。
-</t>
-    <rPh sb="0" eb="2">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="7" eb="11">
-      <t>カクコウモクナイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ガイトウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>クウラン</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ヒョウジ</t>
-    </rPh>
+    <t>menu.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>基本フロー1：未ログイン状態であった場合。
+1. 「ログイン画面」へ遷移する。</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>タスク情報が存在する場合：「タスク一覧表示画面」へ遷移し、タスク一覧を表形式で表示させる。
-タスク情報が存在しない場合：「タスク一覧表示画面」へ遷移し、情報が存在しない項目内容は空欄で表示される。</t>
+タスク情報が一つも存在しない場合：「タスク一覧表示画面」へ遷移し、表は出ず「情報が存在しません。」と文字表示させる。</t>
     <rPh sb="3" eb="5">
       <t>ジョウホウ</t>
     </rPh>
@@ -458,38 +433,74 @@
     <rPh sb="49" eb="51">
       <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="52" eb="54">
+    <rPh sb="52" eb="53">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="55" eb="57">
       <t>ソンザイ</t>
     </rPh>
-    <rPh sb="57" eb="59">
+    <rPh sb="60" eb="62">
       <t>バアイ</t>
     </rPh>
-    <rPh sb="64" eb="70">
+    <rPh sb="67" eb="73">
       <t>イチランヒョウジガメン</t>
     </rPh>
-    <rPh sb="72" eb="74">
+    <rPh sb="75" eb="77">
       <t>センイ</t>
     </rPh>
-    <rPh sb="76" eb="78">
+    <rPh sb="79" eb="80">
+      <t>オモテ</t>
+    </rPh>
+    <rPh sb="81" eb="82">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
       <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="79" eb="81">
+    <rPh sb="87" eb="89">
       <t>ソンザイ</t>
     </rPh>
-    <rPh sb="84" eb="86">
-      <t>コウモク</t>
+    <rPh sb="96" eb="98">
+      <t>モジ</t>
     </rPh>
-    <rPh sb="86" eb="88">
-      <t>ナイヨウ</t>
+    <rPh sb="98" eb="100">
+      <t>ヒョウジ</t>
     </rPh>
-    <rPh sb="87" eb="88">
-      <t>カタチ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">基本フロー2：タスク情報が一つも存在しない場合。
+1. 表は出ず「情報が存在しません。」と文字表示する。
+</t>
+    <rPh sb="0" eb="2">
+      <t>キホン</t>
     </rPh>
-    <rPh sb="89" eb="91">
-      <t>クウラン</t>
+    <rPh sb="10" eb="12">
+      <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="92" eb="94">
-      <t>ヒョウジ</t>
+    <rPh sb="13" eb="14">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="45" eb="49">
+      <t>モジヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1499,23 +1510,74 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1524,18 +1586,90 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1546,9 +1680,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1580,152 +1711,20 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1739,8 +1738,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2527,8 +2538,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="92872" y="2973187"/>
-          <a:ext cx="8610577" cy="5239562"/>
+          <a:off x="92872" y="3039640"/>
+          <a:ext cx="8647363" cy="5389676"/>
           <a:chOff x="9442174" y="4540527"/>
           <a:chExt cx="2671142" cy="4155109"/>
         </a:xfrm>
@@ -2653,8 +2664,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5027688" y="1080600"/>
-          <a:ext cx="2689358" cy="1951319"/>
+          <a:off x="5050828" y="1097016"/>
+          <a:ext cx="2703004" cy="2005905"/>
           <a:chOff x="1120775" y="3770428"/>
           <a:chExt cx="2701512" cy="1912822"/>
         </a:xfrm>
@@ -3064,8 +3075,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4274180" y="3607740"/>
-          <a:ext cx="4219953" cy="3569836"/>
+          <a:off x="4292772" y="3692389"/>
+          <a:ext cx="4238147" cy="3669912"/>
           <a:chOff x="320588" y="4493617"/>
           <a:chExt cx="4244135" cy="3112578"/>
         </a:xfrm>
@@ -3703,8 +3714,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="398020" y="3603708"/>
-          <a:ext cx="3596618" cy="4416002"/>
+          <a:off x="401184" y="3688357"/>
+          <a:ext cx="3612046" cy="4538823"/>
           <a:chOff x="4847659" y="3844680"/>
           <a:chExt cx="3458537" cy="4142531"/>
         </a:xfrm>
@@ -4239,7 +4250,7 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                 </a:rPr>
-                <a:t>String</a:t>
+                <a:t>Date</a:t>
               </a:r>
             </a:p>
             <a:p>
@@ -4266,7 +4277,7 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                 </a:rPr>
-                <a:t>String)</a:t>
+                <a:t>Date)</a:t>
               </a:r>
               <a:r>
                 <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="0" baseline="0">
@@ -4719,15 +4730,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>906854</xdr:colOff>
+      <xdr:colOff>901879</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>39528</xdr:rowOff>
+      <xdr:rowOff>157865</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>907282</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>138186</xdr:rowOff>
+      <xdr:rowOff>137719</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4739,13 +4750,14 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="2"/>
           <a:endCxn id="24" idx="0"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6379693" y="2719443"/>
-          <a:ext cx="428" cy="1067302"/>
+          <a:off x="6378754" y="2853780"/>
+          <a:ext cx="5403" cy="949363"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4917,15 +4929,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>430161</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>61451</xdr:rowOff>
+      <xdr:colOff>489692</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>52947</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>436084</xdr:colOff>
+      <xdr:colOff>501763</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>103283</xdr:rowOff>
+      <xdr:rowOff>102053</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4940,8 +4952,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2576155" y="2425487"/>
-          <a:ext cx="5923" cy="1648459"/>
+          <a:off x="2624313" y="2102523"/>
+          <a:ext cx="12071" cy="1988124"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4949,6 +4961,60 @@
         <a:ln w="19050">
           <a:prstDash val="sysDash"/>
           <a:headEnd w="sm" len="sm"/>
+          <a:tailEnd type="arrow" w="lg" len="lg"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>467746</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>85044</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>170090</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>85044</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="直線矢印コネクタ 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24BB7141-E042-959F-9C20-5CED7043C51A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3716451" y="4719977"/>
+          <a:ext cx="816429" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:prstDash val="sysDash"/>
           <a:tailEnd type="arrow" w="lg" len="lg"/>
         </a:ln>
       </xdr:spPr>
@@ -5639,85 +5705,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="93" t="s">
+      <c r="C2" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="94"/>
-      <c r="O2" s="94"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="93"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="93"/>
+      <c r="N2" s="93"/>
+      <c r="O2" s="93"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
-      <c r="O3" s="90"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="79"/>
+      <c r="O3" s="79"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="90"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="90"/>
-      <c r="M4" s="90"/>
-      <c r="N4" s="90"/>
-      <c r="O4" s="90"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="79"/>
+      <c r="N4" s="79"/>
+      <c r="O4" s="79"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
-      <c r="F5" s="90"/>
-      <c r="G5" s="90"/>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="90"/>
-      <c r="K5" s="90"/>
-      <c r="L5" s="90"/>
-      <c r="M5" s="90"/>
-      <c r="N5" s="90"/>
-      <c r="O5" s="90"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
+      <c r="K5" s="79"/>
+      <c r="L5" s="79"/>
+      <c r="M5" s="79"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
-      <c r="J6" s="90"/>
-      <c r="K6" s="90"/>
-      <c r="L6" s="90"/>
-      <c r="M6" s="90"/>
-      <c r="N6" s="90"/>
-      <c r="O6" s="90"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="79"/>
+      <c r="K6" s="79"/>
+      <c r="L6" s="79"/>
+      <c r="M6" s="79"/>
+      <c r="N6" s="79"/>
+      <c r="O6" s="79"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -5737,46 +5803,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="95" t="s">
+      <c r="E8" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="90"/>
-      <c r="G8" s="90"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="90"/>
-      <c r="J8" s="90"/>
-      <c r="K8" s="90"/>
-      <c r="L8" s="90"/>
-      <c r="M8" s="90"/>
+      <c r="F8" s="79"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="79"/>
+      <c r="J8" s="79"/>
+      <c r="K8" s="79"/>
+      <c r="L8" s="79"/>
+      <c r="M8" s="79"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="91" t="s">
+      <c r="G13" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="52"/>
-      <c r="I13" s="96">
+      <c r="H13" s="50"/>
+      <c r="I13" s="95">
         <v>46230</v>
       </c>
       <c r="J13" s="49"/>
-      <c r="K13" s="52"/>
+      <c r="K13" s="50"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="91"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="91"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="90"/>
       <c r="J14" s="49"/>
-      <c r="K14" s="52"/>
+      <c r="K14" s="50"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="91"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="91"/>
+      <c r="G15" s="90"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="90"/>
       <c r="J15" s="49"/>
-      <c r="K15" s="52"/>
+      <c r="K15" s="50"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -5785,13 +5851,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="92" t="s">
+      <c r="G17" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="90"/>
-      <c r="I17" s="90"/>
-      <c r="J17" s="90"/>
-      <c r="K17" s="90"/>
+      <c r="H17" s="79"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="79"/>
+      <c r="K17" s="79"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -6805,19 +6871,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="76"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
@@ -6829,72 +6895,72 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="89"/>
-      <c r="B2" s="90"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="75" t="s">
+      <c r="A2" s="78"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="76"/>
-      <c r="F2" s="75" t="s">
+      <c r="E2" s="86"/>
+      <c r="F2" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="76"/>
-      <c r="H2" s="81">
+      <c r="G2" s="86"/>
+      <c r="H2" s="89">
         <v>46231</v>
       </c>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="84"/>
+      <c r="J2" s="67"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="89"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="68"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="103"/>
-      <c r="B4" s="104"/>
-      <c r="C4" s="105"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="98"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="69"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="100" t="s">
+      <c r="B5" s="71"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="73" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="64"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="74"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="101" t="s">
+      <c r="A6" s="48" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="49"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="48" t="s">
+      <c r="C6" s="50"/>
+      <c r="D6" s="59" t="s">
         <v>77</v>
       </c>
       <c r="E6" s="49"/>
@@ -6902,15 +6968,15 @@
       <c r="G6" s="49"/>
       <c r="H6" s="49"/>
       <c r="I6" s="49"/>
-      <c r="J6" s="50"/>
+      <c r="J6" s="52"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="101" t="s">
+      <c r="A7" s="48" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="49"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="48" t="s">
+      <c r="C7" s="50"/>
+      <c r="D7" s="59" t="s">
         <v>66</v>
       </c>
       <c r="E7" s="49"/>
@@ -6918,15 +6984,15 @@
       <c r="G7" s="49"/>
       <c r="H7" s="49"/>
       <c r="I7" s="49"/>
-      <c r="J7" s="50"/>
+      <c r="J7" s="52"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="101" t="s">
+      <c r="A8" s="48" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="49"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="48" t="s">
+      <c r="C8" s="50"/>
+      <c r="D8" s="59" t="s">
         <v>76</v>
       </c>
       <c r="E8" s="49"/>
@@ -6934,17 +7000,17 @@
       <c r="G8" s="49"/>
       <c r="H8" s="49"/>
       <c r="I8" s="49"/>
-      <c r="J8" s="50"/>
+      <c r="J8" s="52"/>
     </row>
     <row r="9" spans="1:10" ht="87.75" customHeight="1">
-      <c r="A9" s="111" t="s">
+      <c r="A9" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="114" t="s">
+      <c r="B9" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="107" t="s">
+      <c r="C9" s="50"/>
+      <c r="D9" s="51" t="s">
         <v>78</v>
       </c>
       <c r="E9" s="49"/>
@@ -6952,47 +7018,47 @@
       <c r="G9" s="49"/>
       <c r="H9" s="49"/>
       <c r="I9" s="49"/>
-      <c r="J9" s="50"/>
+      <c r="J9" s="52"/>
     </row>
     <row r="10" spans="1:10" ht="100.5" customHeight="1">
-      <c r="A10" s="112"/>
-      <c r="B10" s="114" t="s">
+      <c r="A10" s="61"/>
+      <c r="B10" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="107" t="s">
-        <v>82</v>
+      <c r="C10" s="50"/>
+      <c r="D10" s="51" t="s">
+        <v>84</v>
       </c>
       <c r="E10" s="49"/>
       <c r="F10" s="49"/>
       <c r="G10" s="49"/>
       <c r="H10" s="49"/>
       <c r="I10" s="49"/>
-      <c r="J10" s="50"/>
+      <c r="J10" s="52"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="113"/>
-      <c r="B11" s="114" t="s">
+      <c r="A11" s="62"/>
+      <c r="B11" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="48" t="s">
-        <v>67</v>
+      <c r="C11" s="50"/>
+      <c r="D11" s="51" t="s">
+        <v>82</v>
       </c>
       <c r="E11" s="49"/>
       <c r="F11" s="49"/>
       <c r="G11" s="49"/>
       <c r="H11" s="49"/>
       <c r="I11" s="49"/>
-      <c r="J11" s="50"/>
+      <c r="J11" s="52"/>
     </row>
     <row r="12" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A12" s="101" t="s">
+      <c r="A12" s="48" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="49"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="107" t="s">
+      <c r="C12" s="50"/>
+      <c r="D12" s="51" t="s">
         <v>83</v>
       </c>
       <c r="E12" s="49"/>
@@ -7000,23 +7066,23 @@
       <c r="G12" s="49"/>
       <c r="H12" s="49"/>
       <c r="I12" s="49"/>
-      <c r="J12" s="50"/>
+      <c r="J12" s="52"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="108" t="s">
+      <c r="A13" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="79" t="s">
+      <c r="B13" s="54"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="109"/>
-      <c r="F13" s="109"/>
-      <c r="G13" s="109"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="109"/>
-      <c r="J13" s="110"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="58"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8007,6 +8073,18 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -8022,18 +8100,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -8052,19 +8118,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="96" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="76"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -8076,48 +8142,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="89"/>
-      <c r="B2" s="90"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="75" t="s">
+      <c r="A2" s="78"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="76"/>
-      <c r="F2" s="75" t="s">
+      <c r="E2" s="86"/>
+      <c r="F2" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="76"/>
-      <c r="H2" s="81">
+      <c r="G2" s="86"/>
+      <c r="H2" s="89">
         <v>46230</v>
       </c>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="84"/>
+      <c r="J2" s="67"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="89"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="68"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="103"/>
-      <c r="B4" s="104"/>
-      <c r="C4" s="105"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="98"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="69"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -9474,19 +9540,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="76"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -9498,48 +9564,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="89"/>
-      <c r="B2" s="90"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="75" t="s">
+      <c r="A2" s="78"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="76"/>
-      <c r="F2" s="75" t="s">
+      <c r="E2" s="86"/>
+      <c r="F2" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="76"/>
-      <c r="H2" s="81">
+      <c r="G2" s="86"/>
+      <c r="H2" s="89">
         <v>46231</v>
       </c>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="84"/>
+      <c r="J2" s="67"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="89"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="68"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="89"/>
-      <c r="B4" s="115"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="97"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="68"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="37"/>
@@ -10946,19 +11012,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="56" t="s">
+      <c r="B1" s="76"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -10970,67 +11036,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="89"/>
-      <c r="B2" s="90"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="75" t="s">
+      <c r="A2" s="78"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="76"/>
-      <c r="F2" s="75" t="s">
+      <c r="E2" s="86"/>
+      <c r="F2" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="76"/>
-      <c r="H2" s="81">
+      <c r="G2" s="86"/>
+      <c r="H2" s="89">
         <v>46231</v>
       </c>
-      <c r="I2" s="83" t="s">
+      <c r="I2" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="84"/>
+      <c r="J2" s="67"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="89"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="85"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="68"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="89"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="85"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="68"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="63" t="s">
-        <v>81</v>
+      <c r="B5" s="71"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="104" t="s">
+        <v>80</v>
       </c>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="64"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="74"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="100" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="49"/>
@@ -11041,94 +11107,94 @@
       <c r="G6" s="49"/>
       <c r="H6" s="49"/>
       <c r="I6" s="49"/>
-      <c r="J6" s="50"/>
+      <c r="J6" s="52"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="65"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="67"/>
+      <c r="A7" s="105"/>
+      <c r="B7" s="106"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="106"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="107"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="68"/>
-      <c r="B8" s="69"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="70"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="109"/>
+      <c r="C8" s="109"/>
+      <c r="D8" s="109"/>
+      <c r="E8" s="109"/>
+      <c r="F8" s="109"/>
+      <c r="G8" s="109"/>
+      <c r="H8" s="109"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="110"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="68"/>
-      <c r="B9" s="69"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69"/>
-      <c r="J9" s="70"/>
+      <c r="A9" s="108"/>
+      <c r="B9" s="109"/>
+      <c r="C9" s="109"/>
+      <c r="D9" s="109"/>
+      <c r="E9" s="109"/>
+      <c r="F9" s="109"/>
+      <c r="G9" s="109"/>
+      <c r="H9" s="109"/>
+      <c r="I9" s="109"/>
+      <c r="J9" s="110"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="68"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="69"/>
-      <c r="J10" s="70"/>
+      <c r="A10" s="108"/>
+      <c r="B10" s="109"/>
+      <c r="C10" s="109"/>
+      <c r="D10" s="109"/>
+      <c r="E10" s="109"/>
+      <c r="F10" s="109"/>
+      <c r="G10" s="109"/>
+      <c r="H10" s="109"/>
+      <c r="I10" s="109"/>
+      <c r="J10" s="110"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="68"/>
-      <c r="B11" s="69"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="69"/>
-      <c r="J11" s="70"/>
+      <c r="A11" s="108"/>
+      <c r="B11" s="109"/>
+      <c r="C11" s="109"/>
+      <c r="D11" s="109"/>
+      <c r="E11" s="109"/>
+      <c r="F11" s="109"/>
+      <c r="G11" s="109"/>
+      <c r="H11" s="109"/>
+      <c r="I11" s="109"/>
+      <c r="J11" s="110"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="68"/>
-      <c r="B12" s="69"/>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="69"/>
-      <c r="J12" s="70"/>
+      <c r="A12" s="108"/>
+      <c r="B12" s="109"/>
+      <c r="C12" s="109"/>
+      <c r="D12" s="109"/>
+      <c r="E12" s="109"/>
+      <c r="F12" s="109"/>
+      <c r="G12" s="109"/>
+      <c r="H12" s="109"/>
+      <c r="I12" s="109"/>
+      <c r="J12" s="110"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="71"/>
-      <c r="B13" s="72"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="73"/>
+      <c r="A13" s="111"/>
+      <c r="B13" s="112"/>
+      <c r="C13" s="112"/>
+      <c r="D13" s="112"/>
+      <c r="E13" s="112"/>
+      <c r="F13" s="112"/>
+      <c r="G13" s="112"/>
+      <c r="H13" s="112"/>
+      <c r="I13" s="112"/>
+      <c r="J13" s="113"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="60" t="s">
+      <c r="A14" s="100" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="49"/>
@@ -11139,21 +11205,21 @@
       <c r="G14" s="49"/>
       <c r="H14" s="49"/>
       <c r="I14" s="49"/>
-      <c r="J14" s="50"/>
+      <c r="J14" s="52"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="100" t="s">
         <v>24</v>
       </c>
       <c r="B15" s="49"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="48" t="s">
-        <v>80</v>
+      <c r="C15" s="50"/>
+      <c r="D15" s="59" t="s">
+        <v>81</v>
       </c>
       <c r="E15" s="49"/>
       <c r="F15" s="49"/>
       <c r="G15" s="49"/>
-      <c r="H15" s="52"/>
+      <c r="H15" s="50"/>
       <c r="I15" s="14" t="s">
         <v>25</v>
       </c>
@@ -11162,11 +11228,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="100" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="49"/>
-      <c r="C16" s="52"/>
+      <c r="C16" s="50"/>
       <c r="D16" s="14" t="s">
         <v>27</v>
       </c>
@@ -11179,18 +11245,18 @@
       <c r="G16" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="74" t="s">
+      <c r="H16" s="114" t="s">
         <v>17</v>
       </c>
       <c r="I16" s="49"/>
-      <c r="J16" s="50"/>
+      <c r="J16" s="52"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="62"/>
+      <c r="B17" s="102"/>
+      <c r="C17" s="103"/>
       <c r="D17" s="16" t="s">
         <v>73</v>
       </c>
@@ -11203,83 +11269,83 @@
       <c r="G17" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="48" t="s">
+      <c r="H17" s="59" t="s">
         <v>79</v>
       </c>
       <c r="I17" s="49"/>
-      <c r="J17" s="50"/>
+      <c r="J17" s="52"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="51"/>
+      <c r="A18" s="101"/>
       <c r="B18" s="49"/>
-      <c r="C18" s="52"/>
+      <c r="C18" s="50"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
       <c r="F18" s="17"/>
       <c r="G18" s="17"/>
-      <c r="H18" s="48"/>
+      <c r="H18" s="59"/>
       <c r="I18" s="49"/>
-      <c r="J18" s="50"/>
+      <c r="J18" s="52"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="51"/>
+      <c r="A19" s="101"/>
       <c r="B19" s="49"/>
-      <c r="C19" s="52"/>
+      <c r="C19" s="50"/>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
-      <c r="H19" s="48"/>
+      <c r="H19" s="59"/>
       <c r="I19" s="49"/>
-      <c r="J19" s="50"/>
+      <c r="J19" s="52"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="51"/>
+      <c r="A20" s="101"/>
       <c r="B20" s="49"/>
-      <c r="C20" s="52"/>
+      <c r="C20" s="50"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
-      <c r="H20" s="48"/>
+      <c r="H20" s="59"/>
       <c r="I20" s="49"/>
-      <c r="J20" s="50"/>
+      <c r="J20" s="52"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="51"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="49"/>
-      <c r="C21" s="52"/>
+      <c r="C21" s="50"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
-      <c r="H21" s="48"/>
+      <c r="H21" s="59"/>
       <c r="I21" s="49"/>
-      <c r="J21" s="50"/>
+      <c r="J21" s="52"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="51"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="49"/>
-      <c r="C22" s="52"/>
+      <c r="C22" s="50"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
       <c r="F22" s="17"/>
       <c r="G22" s="17"/>
-      <c r="H22" s="48"/>
+      <c r="H22" s="59"/>
       <c r="I22" s="49"/>
-      <c r="J22" s="50"/>
+      <c r="J22" s="52"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="57"/>
-      <c r="B23" s="58"/>
-      <c r="C23" s="59"/>
+      <c r="A23" s="99"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="55"/>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="80"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="115"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12260,11 +12326,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -12281,16 +12352,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12310,141 +12376,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="56" t="s">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="56" t="s">
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="56" t="s">
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="56" t="s">
+      <c r="P1" s="72"/>
+      <c r="Q1" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="55"/>
-      <c r="S1" s="56" t="s">
+      <c r="R1" s="72"/>
+      <c r="S1" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="64"/>
+      <c r="T1" s="74"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="89"/>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="75"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="75"/>
-      <c r="T2" s="125"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="85"/>
+      <c r="P2" s="86"/>
+      <c r="Q2" s="85"/>
+      <c r="R2" s="86"/>
+      <c r="S2" s="85"/>
+      <c r="T2" s="121"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="89"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="77"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="78"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="126"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="87"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="87"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="87"/>
+      <c r="T3" s="122"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="103"/>
-      <c r="B4" s="104"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="104"/>
-      <c r="J4" s="105"/>
-      <c r="K4" s="106"/>
-      <c r="L4" s="104"/>
-      <c r="M4" s="104"/>
-      <c r="N4" s="105"/>
-      <c r="O4" s="106"/>
-      <c r="P4" s="105"/>
-      <c r="Q4" s="106"/>
-      <c r="R4" s="105"/>
-      <c r="S4" s="106"/>
-      <c r="T4" s="127"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="82"/>
+      <c r="M4" s="82"/>
+      <c r="N4" s="83"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="83"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="83"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="123"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="100" t="s">
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
-      <c r="S5" s="54"/>
-      <c r="T5" s="64"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="71"/>
+      <c r="R5" s="71"/>
+      <c r="S5" s="71"/>
+      <c r="T5" s="74"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="100" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="49"/>
       <c r="C6" s="49"/>
       <c r="D6" s="49"/>
       <c r="E6" s="49"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="48" t="s">
+      <c r="F6" s="50"/>
+      <c r="G6" s="59" t="s">
         <v>18</v>
       </c>
       <c r="H6" s="49"/>
@@ -12459,18 +12525,18 @@
       <c r="Q6" s="49"/>
       <c r="R6" s="49"/>
       <c r="S6" s="49"/>
-      <c r="T6" s="50"/>
+      <c r="T6" s="52"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="60" t="s">
+      <c r="A7" s="100" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="49"/>
       <c r="C7" s="49"/>
       <c r="D7" s="49"/>
       <c r="E7" s="49"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="48" t="s">
+      <c r="F7" s="50"/>
+      <c r="G7" s="59" t="s">
         <v>36</v>
       </c>
       <c r="H7" s="49"/>
@@ -12485,7 +12551,7 @@
       <c r="Q7" s="49"/>
       <c r="R7" s="49"/>
       <c r="S7" s="49"/>
-      <c r="T7" s="50"/>
+      <c r="T7" s="52"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -12684,37 +12750,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="100" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="52"/>
-      <c r="C15" s="123" t="s">
+      <c r="B15" s="50"/>
+      <c r="C15" s="126" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="52"/>
-      <c r="E15" s="74" t="s">
+      <c r="D15" s="50"/>
+      <c r="E15" s="114" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="52"/>
-      <c r="G15" s="74" t="s">
+      <c r="F15" s="50"/>
+      <c r="G15" s="114" t="s">
         <v>45</v>
       </c>
       <c r="H15" s="49"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="74" t="s">
+      <c r="I15" s="50"/>
+      <c r="J15" s="114" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="52"/>
-      <c r="L15" s="74" t="s">
+      <c r="K15" s="50"/>
+      <c r="L15" s="114" t="s">
         <v>47</v>
       </c>
       <c r="M15" s="49"/>
-      <c r="N15" s="52"/>
-      <c r="O15" s="74" t="s">
+      <c r="N15" s="50"/>
+      <c r="O15" s="114" t="s">
         <v>48</v>
       </c>
       <c r="P15" s="49"/>
-      <c r="Q15" s="52"/>
+      <c r="Q15" s="50"/>
       <c r="R15" s="14" t="s">
         <v>49</v>
       </c>
@@ -12726,37 +12792,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="116">
+      <c r="A16" s="124">
         <v>1</v>
       </c>
-      <c r="B16" s="52"/>
-      <c r="C16" s="117" t="s">
+      <c r="B16" s="50"/>
+      <c r="C16" s="125" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="52"/>
-      <c r="E16" s="117" t="s">
+      <c r="D16" s="50"/>
+      <c r="E16" s="125" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="52"/>
-      <c r="G16" s="122" t="s">
+      <c r="F16" s="50"/>
+      <c r="G16" s="116" t="s">
         <v>54</v>
       </c>
       <c r="H16" s="49"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="122" t="s">
+      <c r="I16" s="50"/>
+      <c r="J16" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="52"/>
-      <c r="L16" s="120" t="s">
+      <c r="K16" s="50"/>
+      <c r="L16" s="118" t="s">
         <v>56</v>
       </c>
       <c r="M16" s="49"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="120" t="s">
+      <c r="N16" s="50"/>
+      <c r="O16" s="118" t="s">
         <v>57</v>
       </c>
       <c r="P16" s="49"/>
-      <c r="Q16" s="52"/>
+      <c r="Q16" s="50"/>
       <c r="R16" s="32"/>
       <c r="S16" s="32"/>
       <c r="T16" s="33"/>
@@ -12768,37 +12834,37 @@
       <c r="Z16" s="34"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="116">
+      <c r="A17" s="124">
         <v>2</v>
       </c>
-      <c r="B17" s="52"/>
-      <c r="C17" s="117" t="s">
+      <c r="B17" s="50"/>
+      <c r="C17" s="125" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="52"/>
-      <c r="E17" s="117" t="s">
+      <c r="D17" s="50"/>
+      <c r="E17" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="52"/>
-      <c r="G17" s="122" t="s">
+      <c r="F17" s="50"/>
+      <c r="G17" s="116" t="s">
         <v>60</v>
       </c>
       <c r="H17" s="49"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="122" t="s">
+      <c r="I17" s="50"/>
+      <c r="J17" s="116" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="52"/>
-      <c r="L17" s="120" t="s">
+      <c r="K17" s="50"/>
+      <c r="L17" s="118" t="s">
         <v>62</v>
       </c>
       <c r="M17" s="49"/>
-      <c r="N17" s="52"/>
-      <c r="O17" s="120" t="s">
+      <c r="N17" s="50"/>
+      <c r="O17" s="118" t="s">
         <v>63</v>
       </c>
       <c r="P17" s="49"/>
-      <c r="Q17" s="52"/>
+      <c r="Q17" s="50"/>
       <c r="R17" s="32"/>
       <c r="S17" s="32"/>
       <c r="T17" s="33"/>
@@ -12810,23 +12876,23 @@
       <c r="Z17" s="34"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="116"/>
-      <c r="B18" s="52"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="122"/>
+      <c r="A18" s="124"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="125"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="116"/>
       <c r="H18" s="49"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="122"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="120"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="116"/>
+      <c r="K18" s="50"/>
+      <c r="L18" s="118"/>
       <c r="M18" s="49"/>
-      <c r="N18" s="52"/>
-      <c r="O18" s="120"/>
+      <c r="N18" s="50"/>
+      <c r="O18" s="118"/>
       <c r="P18" s="49"/>
-      <c r="Q18" s="52"/>
+      <c r="Q18" s="50"/>
       <c r="R18" s="32"/>
       <c r="S18" s="32"/>
       <c r="T18" s="33"/>
@@ -12838,23 +12904,23 @@
       <c r="Z18" s="34"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="116"/>
-      <c r="B19" s="52"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="117"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="122"/>
+      <c r="A19" s="124"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="125"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="125"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="116"/>
       <c r="H19" s="49"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="122"/>
-      <c r="K19" s="52"/>
-      <c r="L19" s="120"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="116"/>
+      <c r="K19" s="50"/>
+      <c r="L19" s="118"/>
       <c r="M19" s="49"/>
-      <c r="N19" s="52"/>
-      <c r="O19" s="120"/>
+      <c r="N19" s="50"/>
+      <c r="O19" s="118"/>
       <c r="P19" s="49"/>
-      <c r="Q19" s="52"/>
+      <c r="Q19" s="50"/>
       <c r="R19" s="32"/>
       <c r="S19" s="32"/>
       <c r="T19" s="33"/>
@@ -12866,23 +12932,23 @@
       <c r="Z19" s="34"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="116"/>
-      <c r="B20" s="52"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="117"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="122"/>
+      <c r="A20" s="124"/>
+      <c r="B20" s="50"/>
+      <c r="C20" s="125"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="125"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="116"/>
       <c r="H20" s="49"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="122"/>
-      <c r="K20" s="52"/>
-      <c r="L20" s="120"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="116"/>
+      <c r="K20" s="50"/>
+      <c r="L20" s="118"/>
       <c r="M20" s="49"/>
-      <c r="N20" s="52"/>
-      <c r="O20" s="120"/>
+      <c r="N20" s="50"/>
+      <c r="O20" s="118"/>
       <c r="P20" s="49"/>
-      <c r="Q20" s="52"/>
+      <c r="Q20" s="50"/>
       <c r="R20" s="32"/>
       <c r="S20" s="32"/>
       <c r="T20" s="33"/>
@@ -12894,23 +12960,23 @@
       <c r="Z20" s="34"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="116"/>
-      <c r="B21" s="52"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="117"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="122"/>
+      <c r="A21" s="124"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="125"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="125"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="116"/>
       <c r="H21" s="49"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="122"/>
-      <c r="K21" s="52"/>
-      <c r="L21" s="120"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="116"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="118"/>
       <c r="M21" s="49"/>
-      <c r="N21" s="52"/>
-      <c r="O21" s="120"/>
+      <c r="N21" s="50"/>
+      <c r="O21" s="118"/>
       <c r="P21" s="49"/>
-      <c r="Q21" s="52"/>
+      <c r="Q21" s="50"/>
       <c r="R21" s="32"/>
       <c r="S21" s="32"/>
       <c r="T21" s="33"/>
@@ -12922,23 +12988,23 @@
       <c r="Z21" s="34"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="116"/>
-      <c r="B22" s="52"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="117"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="122"/>
+      <c r="A22" s="124"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="125"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="125"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="116"/>
       <c r="H22" s="49"/>
-      <c r="I22" s="52"/>
-      <c r="J22" s="122"/>
-      <c r="K22" s="52"/>
-      <c r="L22" s="120"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="116"/>
+      <c r="K22" s="50"/>
+      <c r="L22" s="118"/>
       <c r="M22" s="49"/>
-      <c r="N22" s="52"/>
-      <c r="O22" s="120"/>
+      <c r="N22" s="50"/>
+      <c r="O22" s="118"/>
       <c r="P22" s="49"/>
-      <c r="Q22" s="52"/>
+      <c r="Q22" s="50"/>
       <c r="R22" s="32"/>
       <c r="S22" s="32"/>
       <c r="T22" s="33"/>
@@ -12950,23 +13016,23 @@
       <c r="Z22" s="34"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="116"/>
-      <c r="B23" s="52"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="117"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="122"/>
+      <c r="A23" s="124"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="125"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="125"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="116"/>
       <c r="H23" s="49"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="122"/>
-      <c r="K23" s="52"/>
-      <c r="L23" s="120"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="116"/>
+      <c r="K23" s="50"/>
+      <c r="L23" s="118"/>
       <c r="M23" s="49"/>
-      <c r="N23" s="52"/>
-      <c r="O23" s="120"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="118"/>
       <c r="P23" s="49"/>
-      <c r="Q23" s="52"/>
+      <c r="Q23" s="50"/>
       <c r="R23" s="32"/>
       <c r="S23" s="32"/>
       <c r="T23" s="33"/>
@@ -12978,23 +13044,23 @@
       <c r="Z23" s="34"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="116"/>
-      <c r="B24" s="52"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="122"/>
+      <c r="A24" s="124"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="125"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="125"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="116"/>
       <c r="H24" s="49"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="122"/>
-      <c r="K24" s="52"/>
-      <c r="L24" s="120"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="116"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="118"/>
       <c r="M24" s="49"/>
-      <c r="N24" s="52"/>
-      <c r="O24" s="120"/>
+      <c r="N24" s="50"/>
+      <c r="O24" s="118"/>
       <c r="P24" s="49"/>
-      <c r="Q24" s="52"/>
+      <c r="Q24" s="50"/>
       <c r="R24" s="32"/>
       <c r="S24" s="32"/>
       <c r="T24" s="33"/>
@@ -13006,23 +13072,23 @@
       <c r="Z24" s="34"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="116"/>
-      <c r="B25" s="52"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="117"/>
-      <c r="F25" s="52"/>
-      <c r="G25" s="122"/>
+      <c r="A25" s="124"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="125"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="116"/>
       <c r="H25" s="49"/>
-      <c r="I25" s="52"/>
-      <c r="J25" s="122"/>
-      <c r="K25" s="52"/>
-      <c r="L25" s="120"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="116"/>
+      <c r="K25" s="50"/>
+      <c r="L25" s="118"/>
       <c r="M25" s="49"/>
-      <c r="N25" s="52"/>
-      <c r="O25" s="120"/>
+      <c r="N25" s="50"/>
+      <c r="O25" s="118"/>
       <c r="P25" s="49"/>
-      <c r="Q25" s="52"/>
+      <c r="Q25" s="50"/>
       <c r="R25" s="32"/>
       <c r="S25" s="32"/>
       <c r="T25" s="33"/>
@@ -13034,23 +13100,23 @@
       <c r="Z25" s="34"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="116"/>
-      <c r="B26" s="52"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="122"/>
+      <c r="A26" s="124"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="125"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="125"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="116"/>
       <c r="H26" s="49"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="122"/>
-      <c r="K26" s="52"/>
-      <c r="L26" s="120"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="116"/>
+      <c r="K26" s="50"/>
+      <c r="L26" s="118"/>
       <c r="M26" s="49"/>
-      <c r="N26" s="52"/>
-      <c r="O26" s="120"/>
+      <c r="N26" s="50"/>
+      <c r="O26" s="118"/>
       <c r="P26" s="49"/>
-      <c r="Q26" s="52"/>
+      <c r="Q26" s="50"/>
       <c r="R26" s="32"/>
       <c r="S26" s="32"/>
       <c r="T26" s="33"/>
@@ -13062,23 +13128,23 @@
       <c r="Z26" s="34"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="116"/>
-      <c r="B27" s="52"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="117"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="122"/>
+      <c r="A27" s="124"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="125"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="125"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="116"/>
       <c r="H27" s="49"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="122"/>
-      <c r="K27" s="52"/>
-      <c r="L27" s="120"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="116"/>
+      <c r="K27" s="50"/>
+      <c r="L27" s="118"/>
       <c r="M27" s="49"/>
-      <c r="N27" s="52"/>
-      <c r="O27" s="120"/>
+      <c r="N27" s="50"/>
+      <c r="O27" s="118"/>
       <c r="P27" s="49"/>
-      <c r="Q27" s="52"/>
+      <c r="Q27" s="50"/>
       <c r="R27" s="32"/>
       <c r="S27" s="32"/>
       <c r="T27" s="33"/>
@@ -13090,23 +13156,23 @@
       <c r="Z27" s="34"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="116"/>
-      <c r="B28" s="52"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="117"/>
-      <c r="F28" s="52"/>
-      <c r="G28" s="122"/>
+      <c r="A28" s="124"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="125"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="125"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="116"/>
       <c r="H28" s="49"/>
-      <c r="I28" s="52"/>
-      <c r="J28" s="122"/>
-      <c r="K28" s="52"/>
-      <c r="L28" s="120"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="116"/>
+      <c r="K28" s="50"/>
+      <c r="L28" s="118"/>
       <c r="M28" s="49"/>
-      <c r="N28" s="52"/>
-      <c r="O28" s="120"/>
+      <c r="N28" s="50"/>
+      <c r="O28" s="118"/>
       <c r="P28" s="49"/>
-      <c r="Q28" s="52"/>
+      <c r="Q28" s="50"/>
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="33"/>
@@ -13118,23 +13184,23 @@
       <c r="Z28" s="34"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="116"/>
-      <c r="B29" s="52"/>
-      <c r="C29" s="117"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="117"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="122"/>
+      <c r="A29" s="124"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="125"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="125"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="116"/>
       <c r="H29" s="49"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="122"/>
-      <c r="K29" s="52"/>
-      <c r="L29" s="120"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="116"/>
+      <c r="K29" s="50"/>
+      <c r="L29" s="118"/>
       <c r="M29" s="49"/>
-      <c r="N29" s="52"/>
-      <c r="O29" s="120"/>
+      <c r="N29" s="50"/>
+      <c r="O29" s="118"/>
       <c r="P29" s="49"/>
-      <c r="Q29" s="52"/>
+      <c r="Q29" s="50"/>
       <c r="R29" s="32"/>
       <c r="S29" s="32"/>
       <c r="T29" s="33"/>
@@ -13146,23 +13212,23 @@
       <c r="Z29" s="34"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="116"/>
-      <c r="B30" s="52"/>
-      <c r="C30" s="117"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="117"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="122"/>
+      <c r="A30" s="124"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="125"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="125"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="116"/>
       <c r="H30" s="49"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="122"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="120"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="116"/>
+      <c r="K30" s="50"/>
+      <c r="L30" s="118"/>
       <c r="M30" s="49"/>
-      <c r="N30" s="52"/>
-      <c r="O30" s="120"/>
+      <c r="N30" s="50"/>
+      <c r="O30" s="118"/>
       <c r="P30" s="49"/>
-      <c r="Q30" s="52"/>
+      <c r="Q30" s="50"/>
       <c r="R30" s="32"/>
       <c r="S30" s="32"/>
       <c r="T30" s="33"/>
@@ -13174,23 +13240,23 @@
       <c r="Z30" s="34"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="118"/>
-      <c r="B31" s="59"/>
-      <c r="C31" s="119"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="119"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="128"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="59"/>
-      <c r="J31" s="128"/>
-      <c r="K31" s="59"/>
-      <c r="L31" s="121"/>
-      <c r="M31" s="58"/>
-      <c r="N31" s="59"/>
-      <c r="O31" s="121"/>
-      <c r="P31" s="58"/>
-      <c r="Q31" s="59"/>
+      <c r="A31" s="127"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="128"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="128"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="117"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="55"/>
+      <c r="J31" s="117"/>
+      <c r="K31" s="55"/>
+      <c r="L31" s="119"/>
+      <c r="M31" s="54"/>
+      <c r="N31" s="55"/>
+      <c r="O31" s="119"/>
+      <c r="P31" s="54"/>
+      <c r="Q31" s="55"/>
       <c r="R31" s="35"/>
       <c r="S31" s="35"/>
       <c r="T31" s="36"/>
@@ -14188,62 +14254,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -14268,62 +14334,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/プロジェクト型演習_成果ドキュメント_一覧表示.xlsx
+++ b/プロジェクト型演習_成果ドキュメント_一覧表示.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\project-based-learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CB2369-56B1-4923-A55F-55E3B9EDB14B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{80F88FFC-3C71-4366-B539-F0167BA08B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -21,11 +21,12 @@
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="89">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -339,39 +340,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">1. ユーザが「メニュー画面」にて「タスク一覧表示」を押下する。
-2. システムがタスク一覧の各表示項目を表形式で表示する。
-</t>
-    <rPh sb="12" eb="14">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="47" eb="52">
-      <t>カクヒョウジコウモク</t>
-    </rPh>
-    <rPh sb="53" eb="54">
-      <t>ヒョウ</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>ケイシキ</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>メニュー画面へ遷移する。</t>
     <rPh sb="4" eb="6">
       <t>ガメン</t>
@@ -398,6 +366,83 @@
   <si>
     <t>基本フロー1：未ログイン状態であった場合。
 1. 「ログイン画面」へ遷移する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">基本フロー1：タスク情報が一つも存在しない場合。
+1. 表は出ず「情報が存在しません。」と文字表示する。
+</t>
+    <rPh sb="0" eb="2">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="45" eb="49">
+      <t>モジヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1. システムがタスク一覧の各表示項目「①タスク　②カテゴリ　③期限　④担当者　⑤ステータス　⑥メモ」を表形式で表示する。
+2.ユーザが編集ボタンを押下するとシステムが「編集画面」へ遷移する。</t>
+    <rPh sb="11" eb="13">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="14" eb="19">
+      <t>カクヒョウジコウモク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="36" eb="39">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="67" eb="72">
+      <t>タントウシャジョウホウ</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>ヘンシュウオウカヘンシュウガメンセンイ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -469,38 +514,30 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">基本フロー2：タスク情報が一つも存在しない場合。
-1. 表は出ず「情報が存在しません。」と文字表示する。
-</t>
+    <t>②</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集</t>
     <rPh sb="0" eb="2">
-      <t>キホン</t>
+      <t>ヘンシュウ</t>
     </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジョウホウ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>"編集"</t>
+    <rPh sb="1" eb="3">
+      <t>ヘンシュウ</t>
     </rPh>
-    <rPh sb="13" eb="14">
-      <t>ヒト</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>編集画面へ遷移する。</t>
+    <rPh sb="0" eb="4">
+      <t>ヘンシュウガメン</t>
     </rPh>
-    <rPh sb="16" eb="18">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>ヒョウ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>デ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="45" eb="49">
-      <t>モジヒョウジ</t>
+    <rPh sb="5" eb="7">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -5043,15 +5080,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>102212</xdr:colOff>
+      <xdr:colOff>159362</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>120159</xdr:rowOff>
+      <xdr:rowOff>63009</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>659424</xdr:colOff>
+      <xdr:colOff>716574</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>174015</xdr:rowOff>
+      <xdr:rowOff>116865</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5066,8 +5103,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="779952" y="1667972"/>
-          <a:ext cx="7600217" cy="1647461"/>
+          <a:off x="845162" y="1606059"/>
+          <a:ext cx="7586662" cy="1654056"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5186,16 +5223,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>611064</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>211014</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>198193</xdr:rowOff>
+      <xdr:rowOff>207718</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>706313</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>306263</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>207718</xdr:rowOff>
+      <xdr:rowOff>217243</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5210,8 +5247,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3862386" y="2808409"/>
-          <a:ext cx="1212605" cy="275126"/>
+          <a:off x="1239714" y="2817568"/>
+          <a:ext cx="1209674" cy="276225"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5318,16 +5355,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>274760</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>70155</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>84260</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>225670</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>611064</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>73270</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5338,14 +5375,12 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:endCxn id="5" idx="1"/>
-        </xdr:cNvCxnSpPr>
+        <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="3526082" y="2945972"/>
-          <a:ext cx="336304" cy="3115"/>
+        <a:xfrm>
+          <a:off x="427160" y="2835520"/>
+          <a:ext cx="820615" cy="117230"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -5371,16 +5406,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1078221</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>173346</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>202372</xdr:rowOff>
+      <xdr:rowOff>88072</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>244841</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>111491</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>197461</xdr:rowOff>
+      <xdr:rowOff>83161</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5395,8 +5430,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3212187" y="2812588"/>
-          <a:ext cx="283976" cy="260690"/>
+          <a:off x="173346" y="2697922"/>
+          <a:ext cx="281045" cy="261789"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5493,6 +5528,187 @@
         </a:extLst>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="フローチャート: 処理 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B3706CF-7154-93D5-91C4-FAD580E5BFA3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2543175" y="2819400"/>
+          <a:ext cx="1190625" cy="276225"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartProcess">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>編集</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="直線コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE1372B6-0A4C-2D46-630A-FDDBF2878769}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3733800" y="2962275"/>
+          <a:ext cx="838200" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="テキスト ボックス 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BC46468-E454-2152-56E2-AFB263E38C61}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4457700" y="2828925"/>
+          <a:ext cx="371475" cy="276225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>②</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -7011,7 +7227,7 @@
       </c>
       <c r="C9" s="50"/>
       <c r="D9" s="51" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E9" s="49"/>
       <c r="F9" s="49"/>
@@ -7027,7 +7243,7 @@
       </c>
       <c r="C10" s="50"/>
       <c r="D10" s="51" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E10" s="49"/>
       <c r="F10" s="49"/>
@@ -7043,7 +7259,7 @@
       </c>
       <c r="C11" s="50"/>
       <c r="D11" s="51" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E11" s="49"/>
       <c r="F11" s="49"/>
@@ -7052,14 +7268,14 @@
       <c r="I11" s="49"/>
       <c r="J11" s="52"/>
     </row>
-    <row r="12" spans="1:10" ht="34.5" customHeight="1">
+    <row r="12" spans="1:10" ht="36.950000000000003" customHeight="1">
       <c r="A12" s="48" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="49"/>
       <c r="C12" s="50"/>
       <c r="D12" s="51" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E12" s="49"/>
       <c r="F12" s="49"/>
@@ -11048,7 +11264,7 @@
       </c>
       <c r="G2" s="86"/>
       <c r="H2" s="89">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="I2" s="64" t="s">
         <v>72</v>
@@ -11086,7 +11302,7 @@
       <c r="B5" s="71"/>
       <c r="C5" s="72"/>
       <c r="D5" s="104" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E5" s="71"/>
       <c r="F5" s="71"/>
@@ -11214,7 +11430,7 @@
       <c r="B15" s="49"/>
       <c r="C15" s="50"/>
       <c r="D15" s="59" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E15" s="49"/>
       <c r="F15" s="49"/>
@@ -11270,20 +11486,32 @@
         <v>74</v>
       </c>
       <c r="H17" s="59" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I17" s="49"/>
       <c r="J17" s="52"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="101"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="59"/>
+      <c r="A18" s="101" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="102"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" s="59" t="s">
+        <v>88</v>
+      </c>
       <c r="I18" s="49"/>
       <c r="J18" s="52"/>
     </row>

--- a/プロジェクト型演習_成果ドキュメント_一覧表示.xlsx
+++ b/プロジェクト型演習_成果ドキュメント_一覧表示.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\project-based-learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80F88FFC-3C71-4366-B539-F0167BA08B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C4F06C-971B-4A71-9691-95BF18CCD783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -18,15 +18,15 @@
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
     <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
-    <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId6"/>
+    <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="101">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -364,156 +364,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>基本フロー1：未ログイン状態であった場合。
-1. 「ログイン画面」へ遷移する。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">基本フロー1：タスク情報が一つも存在しない場合。
-1. 表は出ず「情報が存在しません。」と文字表示する。
-</t>
-    <rPh sb="0" eb="2">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>ヒョウ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>デ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="45" eb="49">
-      <t>モジヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1. システムがタスク一覧の各表示項目「①タスク　②カテゴリ　③期限　④担当者　⑤ステータス　⑥メモ」を表形式で表示する。
-2.ユーザが編集ボタンを押下するとシステムが「編集画面」へ遷移する。</t>
-    <rPh sb="11" eb="13">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="14" eb="19">
-      <t>カクヒョウジコウモク</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="36" eb="39">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="67" eb="72">
-      <t>タントウシャジョウホウ</t>
-    </rPh>
-    <rPh sb="78" eb="79">
-      <t>ヒョウ</t>
-    </rPh>
-    <rPh sb="79" eb="81">
-      <t>ケイシキ</t>
-    </rPh>
-    <rPh sb="82" eb="84">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="94" eb="96">
-      <t>ヘンシュウオウカヘンシュウガメンセンイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスク情報が存在する場合：「タスク一覧表示画面」へ遷移し、タスク一覧を表形式で表示させる。
-タスク情報が一つも存在しない場合：「タスク一覧表示画面」へ遷移し、表は出ず「情報が存在しません。」と文字表示させる。</t>
-    <rPh sb="3" eb="5">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="19" eb="23">
-      <t>ヒョウジガメン</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>センイ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="35" eb="38">
-      <t>ヒョウケイシキ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="52" eb="53">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="67" eb="73">
-      <t>イチランヒョウジガメン</t>
-    </rPh>
-    <rPh sb="75" eb="77">
-      <t>センイ</t>
-    </rPh>
-    <rPh sb="79" eb="80">
-      <t>オモテ</t>
-    </rPh>
-    <rPh sb="81" eb="82">
-      <t>デ</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="87" eb="89">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="96" eb="98">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="98" eb="100">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>②</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -533,11 +383,333 @@
   </si>
   <si>
     <t>編集画面へ遷移する。</t>
-    <rPh sb="0" eb="4">
-      <t>ヘンシュウガメン</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガメン</t>
     </rPh>
     <rPh sb="5" eb="7">
       <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>③</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>削除</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>"削除"</t>
+    <rPh sb="1" eb="3">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>削除画面へ遷移する。</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>カテゴリ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>期限</t>
+    <rPh sb="0" eb="2">
+      <t>キゲン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ステータス</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>メモ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>担当者</t>
+    <rPh sb="0" eb="3">
+      <t>タントウシャ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>edit.jsp（機能は未実装）</t>
+    <rPh sb="9" eb="11">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ミジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>rest.jsp（機能は未実装）</t>
+    <rPh sb="9" eb="11">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ミジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク情報が存在する場合
+1-1.　システムがタスク一覧の各表示項目「①タスク　②カテゴリ　③期限　④担当者　⑤ステータス　⑥メモ」を表形式で表示する。
+タスク一覧を編集したい場合
+2-1.　ユーザが編集ボタンを押下する。
+2-2.　システムが「編集画面」へ遷移する。
+タスク一覧を削除したい場合
+3-1.　ユーザが削除ボタンを押下する。
+3-2.　システムが「削除画面」へ遷移する。
+メニュー画面へ戻りたい場合
+4-1.　ユーザがメニュー画面へボタンを押下する。
+4-2.　システムが「メニュー画面」へ遷移する。</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="27" eb="32">
+      <t>カクヒョウジコウモク</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="49" eb="52">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="89" eb="91">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="105" eb="107">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="124" eb="128">
+      <t>ヘンシュウガメン</t>
+    </rPh>
+    <rPh sb="130" eb="132">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="140" eb="142">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="143" eb="145">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="148" eb="150">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="157" eb="159">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="163" eb="165">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="200" eb="202">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="203" eb="204">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="207" eb="209">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">タスク情報が存在する場合：タスク一覧を表形式で表示させる。
+タスク情報が一つも存在しない場合：表は出ず「情報が存在しません。」と文字表示させる。
+タスク一覧を編集したい場合：「編集画面」へ遷移する。
+タスク一覧を削除したい場合：「削除画面」へ遷移する。
+メニュー画面へ戻りたい場合：「メニュー画面」へ遷移する。
+</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>ヒョウケイシキ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>オモテ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="88" eb="92">
+      <t>ヘンシュウガメン</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="115" eb="119">
+      <t>サクジョガメン</t>
+    </rPh>
+    <rPh sb="121" eb="123">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="131" eb="133">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="134" eb="135">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="138" eb="140">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="146" eb="148">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="150" eb="152">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">基本フロー1-1：タスク情報が一つも存在しない場合
+1. 表は出ず「情報が存在しません。」と文字表示する。
+</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="37" eb="41">
+      <t>モジヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>「タスク一覧表示画面」を読み込んだ時に未ログイン状態であった場合
+1. 「ログイン画面」へ遷移する。</t>
+    <rPh sb="4" eb="6">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ヒョウジガメン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>トキ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -549,7 +721,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -612,6 +784,53 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -627,7 +846,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="68">
+  <borders count="89">
     <border>
       <left/>
       <right/>
@@ -1114,17 +1333,6 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1368,13 +1576,304 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
       <right/>
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1382,19 +1881,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+      <bottom style="double">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1402,7 +1890,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1445,74 +1933,65 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1526,25 +2005,61 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="87" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1697,84 +2212,144 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1789,6 +2364,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5079,16 +5660,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>159362</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>161066</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>63009</xdr:rowOff>
+      <xdr:rowOff>173531</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>716574</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>116865</xdr:rowOff>
+      <xdr:colOff>754676</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>201409</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5103,8 +5684,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="845162" y="1606059"/>
-          <a:ext cx="7586662" cy="1654056"/>
+          <a:off x="161066" y="1730055"/>
+          <a:ext cx="8329769" cy="1898031"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5157,16 +5738,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>64110</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>91586</xdr:rowOff>
+      <xdr:rowOff>197420</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>348028</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>27475</xdr:rowOff>
+      <xdr:colOff>490681</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>115454</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5181,8 +5762,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1080721" y="2170600"/>
-          <a:ext cx="6988052" cy="998293"/>
+          <a:off x="346364" y="2294844"/>
+          <a:ext cx="7879772" cy="995610"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5223,93 +5804,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>211014</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>207718</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>306263</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>217243</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="正方形/長方形 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B077DD3-7E84-44AE-935A-5532D2D8EFAE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1239714" y="2817568"/>
-          <a:ext cx="1209674" cy="276225"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>メニュー画面へ</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>242521</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>201491</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>236682</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>81179</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>302236</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>209185</xdr:rowOff>
+      <xdr:colOff>702348</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>86394</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -5324,8 +5828,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="920261" y="2014904"/>
-          <a:ext cx="7102720" cy="7694"/>
+          <a:off x="236682" y="2154851"/>
+          <a:ext cx="8174963" cy="5215"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -5355,32 +5859,157 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>84260</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>225670</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>472698</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>225476</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>748921</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>220566</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="テキスト ボックス 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56B2BB04-10E3-4BE6-AA51-DDD30D91D6C5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2612883" y="1754180"/>
+          <a:ext cx="276223" cy="265553"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>145720</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>112556</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>346364</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>144318</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="テキスト ボックス 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BC46468-E454-2152-56E2-AFB263E38C61}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6765114" y="3287556"/>
+          <a:ext cx="1316705" cy="301156"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>②　　③</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>105834</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>119730</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>288636</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>182803</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="19" name="直線コネクタ 18">
+        <xdr:cNvPr id="9" name="直線コネクタ 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFF7955A-165A-4950-ACF6-0963DC70DFB4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE1372B6-0A4C-2D46-630A-FDDBF2878769}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="427160" y="2835520"/>
-          <a:ext cx="820615" cy="117230"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="6725228" y="3025336"/>
+          <a:ext cx="182802" cy="332467"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -5406,23 +6035,74 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>173346</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>88072</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>784664</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>101555</xdr:rowOff>
     </xdr:from>
     <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>788939</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>134697</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="51" name="直線コネクタ 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C7056A4-EF05-F79C-0354-A051F36A44FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7404058" y="3007161"/>
+          <a:ext cx="4275" cy="302536"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>111491</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>83161</xdr:rowOff>
+      <xdr:colOff>161124</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>46467</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>638827</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>46466</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="テキスト ボックス 32">
+        <xdr:cNvPr id="56" name="テキスト ボックス 55">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56B2BB04-10E3-4BE6-AA51-DDD30D91D6C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E7A60F6-2BBE-4410-1D56-3C6219ADA033}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5430,8 +6110,129 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="173346" y="2697922"/>
-          <a:ext cx="281045" cy="261789"/>
+          <a:off x="509600" y="3205979"/>
+          <a:ext cx="1174654" cy="267164"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>メニュー画面へ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>665535</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>182555</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>33194</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>187112</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="58" name="直線コネクタ 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AA548E1-D05C-5950-BC0E-720BAF71B7AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="1710962" y="3342067"/>
+          <a:ext cx="482781" cy="4557"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1057042</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>58082</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>277460</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>106789</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="60" name="テキスト ボックス 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01D5F8E3-87C5-C6F9-5914-CA7F5E5FCA8E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2102469" y="3217594"/>
+          <a:ext cx="335540" cy="315872"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5463,103 +6264,111 @@
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
             <a:t>①</a:t>
           </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>144318</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>12750</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>9</xdr:col>
+          <xdr:colOff>327151</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>202046</xdr:rowOff>
+        </xdr:to>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="5" name="図 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAB37930-FE80-8BE1-B9EB-E3F30885ADF0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+              <a:extLst>
+                <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
+                  <a14:cameraTool cellRange="Sheet1!$A$1:$G$2" spid="_x0000_s3092"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:srcRect/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="490682" y="2648962"/>
+              <a:ext cx="7571924" cy="458690"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>210649</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>18318</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>114957</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>65690</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>54952</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>131494</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1092091</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>270970</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="テキスト ボックス 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA2E6BCA-6079-BEC7-F42E-E26F52F0E072}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3F1B0BC-95F7-5900-56D0-459E23332DDC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1227260" y="2362933"/>
-          <a:ext cx="6548437" cy="378777"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="フローチャート: 処理 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B3706CF-7154-93D5-91C4-FAD580E5BFA3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
+        <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2543175" y="2819400"/>
-          <a:ext cx="1190625" cy="276225"/>
+          <a:off x="7209440" y="287393"/>
+          <a:ext cx="977134" cy="205280"/>
         </a:xfrm>
-        <a:prstGeom prst="flowChartProcess">
+        <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
@@ -5567,121 +6376,10 @@
             <a:lumMod val="75000"/>
           </a:schemeClr>
         </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>編集</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="直線コネクタ 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE1372B6-0A4C-2D46-630A-FDDBF2878769}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3733800" y="2962275"/>
-          <a:ext cx="838200" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050"/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="テキスト ボックス 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BC46468-E454-2152-56E2-AFB263E38C61}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4457700" y="2828925"/>
-          <a:ext cx="371475" cy="276225"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -5699,12 +6397,84 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
+          <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>②</a:t>
+            <a:t>編集</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1174204</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>65691</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2151336</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>262759</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="テキスト ボックス 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C93078B-B3EF-7636-E0AD-68C8520D015D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8268687" y="262760"/>
+          <a:ext cx="977132" cy="197068"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>削除</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -5921,85 +6691,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="92" t="s">
+      <c r="C2" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="93"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="102"/>
+      <c r="M2" s="102"/>
+      <c r="N2" s="102"/>
+      <c r="O2" s="102"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="79"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="79"/>
-      <c r="K4" s="79"/>
-      <c r="L4" s="79"/>
-      <c r="M4" s="79"/>
-      <c r="N4" s="79"/>
-      <c r="O4" s="79"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="79"/>
-      <c r="O5" s="79"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="88"/>
+      <c r="I5" s="88"/>
+      <c r="J5" s="88"/>
+      <c r="K5" s="88"/>
+      <c r="L5" s="88"/>
+      <c r="M5" s="88"/>
+      <c r="N5" s="88"/>
+      <c r="O5" s="88"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="79"/>
-      <c r="K6" s="79"/>
-      <c r="L6" s="79"/>
-      <c r="M6" s="79"/>
-      <c r="N6" s="79"/>
-      <c r="O6" s="79"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="88"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="88"/>
+      <c r="H6" s="88"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="88"/>
+      <c r="K6" s="88"/>
+      <c r="L6" s="88"/>
+      <c r="M6" s="88"/>
+      <c r="N6" s="88"/>
+      <c r="O6" s="88"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -6019,46 +6789,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="94" t="s">
+      <c r="E8" s="103" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="79"/>
-      <c r="G8" s="79"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="79"/>
-      <c r="J8" s="79"/>
-      <c r="K8" s="79"/>
-      <c r="L8" s="79"/>
-      <c r="M8" s="79"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="88"/>
+      <c r="I8" s="88"/>
+      <c r="J8" s="88"/>
+      <c r="K8" s="88"/>
+      <c r="L8" s="88"/>
+      <c r="M8" s="88"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="90" t="s">
+      <c r="G13" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="50"/>
-      <c r="I13" s="95">
+      <c r="H13" s="59"/>
+      <c r="I13" s="104">
         <v>46230</v>
       </c>
-      <c r="J13" s="49"/>
-      <c r="K13" s="50"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="59"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="90"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="90"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="50"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="99"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="59"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="90"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="90"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="50"/>
+      <c r="G15" s="99"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="59"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -6067,13 +6837,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="91" t="s">
+      <c r="G17" s="100" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="79"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="79"/>
-      <c r="K17" s="79"/>
+      <c r="H17" s="88"/>
+      <c r="I17" s="88"/>
+      <c r="J17" s="88"/>
+      <c r="K17" s="88"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -7087,19 +7857,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="84" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="84" t="s">
+      <c r="E1" s="81"/>
+      <c r="F1" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="72"/>
+      <c r="G1" s="81"/>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
@@ -7111,194 +7881,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="78"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="85" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="86"/>
-      <c r="F2" s="85" t="s">
+      <c r="E2" s="95"/>
+      <c r="F2" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="86"/>
-      <c r="H2" s="89">
+      <c r="G2" s="95"/>
+      <c r="H2" s="98">
         <v>46231</v>
       </c>
-      <c r="I2" s="64" t="s">
+      <c r="I2" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="67"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="78"/>
-      <c r="B3" s="79"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="68"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="69"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="73" t="s">
+      <c r="B5" s="80"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="74"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="83"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="59" t="s">
+      <c r="B6" s="58"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="52"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="61"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="59" t="s">
+      <c r="B7" s="58"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="52"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="61"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="59" t="s">
+      <c r="B8" s="58"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="52"/>
-    </row>
-    <row r="9" spans="1:10" ht="87.75" customHeight="1">
-      <c r="A9" s="60" t="s">
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="61"/>
+    </row>
+    <row r="9" spans="1:10" ht="200.1" customHeight="1">
+      <c r="A9" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="50"/>
-      <c r="D9" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="52"/>
-    </row>
-    <row r="10" spans="1:10" ht="100.5" customHeight="1">
-      <c r="A10" s="61"/>
-      <c r="B10" s="63" t="s">
+      <c r="C9" s="59"/>
+      <c r="D9" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="61"/>
+    </row>
+    <row r="10" spans="1:10" ht="45" customHeight="1">
+      <c r="A10" s="70"/>
+      <c r="B10" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="50"/>
-      <c r="D10" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="52"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="62"/>
-      <c r="B11" s="63" t="s">
+      <c r="C10" s="59"/>
+      <c r="D10" s="60" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" s="158"/>
+      <c r="F10" s="158"/>
+      <c r="G10" s="158"/>
+      <c r="H10" s="158"/>
+      <c r="I10" s="158"/>
+      <c r="J10" s="159"/>
+    </row>
+    <row r="11" spans="1:10" ht="45" customHeight="1">
+      <c r="A11" s="71"/>
+      <c r="B11" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="50"/>
-      <c r="D11" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="52"/>
-    </row>
-    <row r="12" spans="1:10" ht="36.950000000000003" customHeight="1">
-      <c r="A12" s="48" t="s">
+      <c r="C11" s="59"/>
+      <c r="D11" s="60" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="61"/>
+    </row>
+    <row r="12" spans="1:10" ht="80.099999999999994" customHeight="1">
+      <c r="A12" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="52"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="61"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="56" t="s">
+      <c r="B13" s="63"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="58"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="67"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8334,19 +9104,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="84" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="84" t="s">
+      <c r="E1" s="81"/>
+      <c r="F1" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="72"/>
+      <c r="G1" s="81"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -8358,48 +9128,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="78"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="85" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="86"/>
-      <c r="F2" s="85" t="s">
+      <c r="E2" s="95"/>
+      <c r="F2" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="86"/>
-      <c r="H2" s="89">
+      <c r="G2" s="95"/>
+      <c r="H2" s="98">
         <v>46230</v>
       </c>
-      <c r="I2" s="64" t="s">
+      <c r="I2" s="73" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="67"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="78"/>
-      <c r="B3" s="79"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="68"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="69"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -9756,19 +10526,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="84" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="84" t="s">
+      <c r="E1" s="81"/>
+      <c r="F1" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="72"/>
+      <c r="G1" s="81"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -9780,63 +10550,63 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="78"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="85" t="s">
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="86"/>
-      <c r="F2" s="85" t="s">
+      <c r="E2" s="95"/>
+      <c r="F2" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="86"/>
-      <c r="H2" s="89">
+      <c r="G2" s="95"/>
+      <c r="H2" s="98">
         <v>46231</v>
       </c>
-      <c r="I2" s="64" t="s">
+      <c r="I2" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="67"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="78"/>
-      <c r="B3" s="79"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="68"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="78"/>
-      <c r="B4" s="97"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="68"/>
+      <c r="A4" s="87"/>
+      <c r="B4" s="106"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A5" s="37"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="39"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="35"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A6" s="40"/>
+      <c r="A6" s="36"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -9845,10 +10615,10 @@
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
-      <c r="J6" s="41"/>
+      <c r="J6" s="37"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A7" s="40"/>
+      <c r="A7" s="36"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -9857,10 +10627,10 @@
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
-      <c r="J7" s="41"/>
+      <c r="J7" s="37"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A8" s="40"/>
+      <c r="A8" s="36"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -9869,10 +10639,10 @@
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
-      <c r="J8" s="41"/>
+      <c r="J8" s="37"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A9" s="40"/>
+      <c r="A9" s="36"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -9881,10 +10651,10 @@
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
-      <c r="J9" s="41"/>
+      <c r="J9" s="37"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A10" s="40"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -9893,10 +10663,10 @@
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
-      <c r="J10" s="41"/>
+      <c r="J10" s="37"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A11" s="40"/>
+      <c r="A11" s="36"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -9905,10 +10675,10 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
-      <c r="J11" s="41"/>
+      <c r="J11" s="37"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A12" s="40"/>
+      <c r="A12" s="36"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -9917,10 +10687,10 @@
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
-      <c r="J12" s="41"/>
+      <c r="J12" s="37"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A13" s="40"/>
+      <c r="A13" s="36"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
@@ -9929,10 +10699,10 @@
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
-      <c r="J13" s="41"/>
+      <c r="J13" s="37"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A14" s="40"/>
+      <c r="A14" s="36"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -9941,10 +10711,10 @@
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
-      <c r="J14" s="41"/>
+      <c r="J14" s="37"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A15" s="40"/>
+      <c r="A15" s="36"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -9953,10 +10723,10 @@
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
-      <c r="J15" s="41"/>
+      <c r="J15" s="37"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A16" s="40"/>
+      <c r="A16" s="36"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -9965,10 +10735,10 @@
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
-      <c r="J16" s="41"/>
+      <c r="J16" s="37"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A17" s="40"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -9977,10 +10747,10 @@
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
-      <c r="J17" s="41"/>
+      <c r="J17" s="37"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A18" s="40"/>
+      <c r="A18" s="36"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -9989,10 +10759,10 @@
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="41"/>
+      <c r="J18" s="37"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A19" s="40"/>
+      <c r="A19" s="36"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -10001,10 +10771,10 @@
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="41"/>
+      <c r="J19" s="37"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A20" s="40"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -10013,10 +10783,10 @@
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="41"/>
+      <c r="J20" s="37"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A21" s="40"/>
+      <c r="A21" s="36"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -10025,10 +10795,10 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
-      <c r="J21" s="41"/>
+      <c r="J21" s="37"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A22" s="40"/>
+      <c r="A22" s="36"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -10036,10 +10806,10 @@
       <c r="F22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
-      <c r="J22" s="41"/>
+      <c r="J22" s="37"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A23" s="40"/>
+      <c r="A23" s="36"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
@@ -10048,10 +10818,10 @@
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
-      <c r="J23" s="41"/>
+      <c r="J23" s="37"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A24" s="40"/>
+      <c r="A24" s="36"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
@@ -10060,10 +10830,10 @@
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
-      <c r="J24" s="41"/>
+      <c r="J24" s="37"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A25" s="40"/>
+      <c r="A25" s="36"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
@@ -10072,10 +10842,10 @@
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
-      <c r="J25" s="41"/>
+      <c r="J25" s="37"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A26" s="40"/>
+      <c r="A26" s="36"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -10084,10 +10854,10 @@
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
-      <c r="J26" s="41"/>
+      <c r="J26" s="37"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A27" s="40"/>
+      <c r="A27" s="36"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -10096,10 +10866,10 @@
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
-      <c r="J27" s="41"/>
+      <c r="J27" s="37"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A28" s="40"/>
+      <c r="A28" s="36"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -10108,10 +10878,10 @@
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
-      <c r="J28" s="41"/>
+      <c r="J28" s="37"/>
     </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A29" s="40"/>
+      <c r="A29" s="36"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -10120,10 +10890,10 @@
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
-      <c r="J29" s="41"/>
+      <c r="J29" s="37"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A30" s="40"/>
+      <c r="A30" s="36"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -10132,10 +10902,10 @@
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
-      <c r="J30" s="41"/>
+      <c r="J30" s="37"/>
     </row>
     <row r="31" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A31" s="40"/>
+      <c r="A31" s="36"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
@@ -10144,10 +10914,10 @@
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
-      <c r="J31" s="41"/>
+      <c r="J31" s="37"/>
     </row>
     <row r="32" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A32" s="40"/>
+      <c r="A32" s="36"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -10156,10 +10926,10 @@
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
-      <c r="J32" s="41"/>
+      <c r="J32" s="37"/>
     </row>
     <row r="33" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A33" s="40"/>
+      <c r="A33" s="36"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
@@ -10168,83 +10938,83 @@
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
-      <c r="J33" s="41"/>
+      <c r="J33" s="37"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A34" s="42"/>
-      <c r="J34" s="43"/>
+      <c r="A34" s="38"/>
+      <c r="J34" s="39"/>
     </row>
     <row r="35" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A35" s="42"/>
-      <c r="J35" s="43"/>
+      <c r="A35" s="38"/>
+      <c r="J35" s="39"/>
     </row>
     <row r="36" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A36" s="42"/>
-      <c r="J36" s="43"/>
+      <c r="A36" s="38"/>
+      <c r="J36" s="39"/>
     </row>
     <row r="37" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A37" s="42"/>
-      <c r="J37" s="43"/>
+      <c r="A37" s="38"/>
+      <c r="J37" s="39"/>
     </row>
     <row r="38" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A38" s="42"/>
-      <c r="J38" s="43"/>
+      <c r="A38" s="38"/>
+      <c r="J38" s="39"/>
     </row>
     <row r="39" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A39" s="42"/>
-      <c r="J39" s="43"/>
+      <c r="A39" s="38"/>
+      <c r="J39" s="39"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A40" s="42"/>
-      <c r="J40" s="43"/>
+      <c r="A40" s="38"/>
+      <c r="J40" s="39"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="42"/>
-      <c r="J41" s="43"/>
+      <c r="A41" s="38"/>
+      <c r="J41" s="39"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A42" s="42"/>
-      <c r="J42" s="43"/>
+      <c r="A42" s="38"/>
+      <c r="J42" s="39"/>
     </row>
     <row r="43" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A43" s="42"/>
-      <c r="J43" s="43"/>
+      <c r="A43" s="38"/>
+      <c r="J43" s="39"/>
     </row>
     <row r="44" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A44" s="42"/>
-      <c r="J44" s="44"/>
+      <c r="A44" s="38"/>
+      <c r="J44" s="40"/>
     </row>
     <row r="45" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A45" s="42"/>
-      <c r="J45" s="43"/>
+      <c r="A45" s="38"/>
+      <c r="J45" s="39"/>
     </row>
     <row r="46" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A46" s="42"/>
-      <c r="J46" s="43"/>
+      <c r="A46" s="38"/>
+      <c r="J46" s="39"/>
     </row>
     <row r="47" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A47" s="42"/>
-      <c r="J47" s="43"/>
+      <c r="A47" s="38"/>
+      <c r="J47" s="39"/>
     </row>
     <row r="48" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A48" s="42"/>
-      <c r="J48" s="43"/>
+      <c r="A48" s="38"/>
+      <c r="J48" s="39"/>
     </row>
     <row r="49" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A49" s="42"/>
-      <c r="J49" s="43"/>
+      <c r="A49" s="38"/>
+      <c r="J49" s="39"/>
     </row>
     <row r="50" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
-      <c r="A50" s="45"/>
-      <c r="B50" s="46"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="46"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="46"/>
-      <c r="H50" s="46"/>
-      <c r="I50" s="46"/>
-      <c r="J50" s="47"/>
+      <c r="A50" s="41"/>
+      <c r="B50" s="42"/>
+      <c r="C50" s="42"/>
+      <c r="D50" s="42"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="42"/>
+      <c r="I50" s="42"/>
+      <c r="J50" s="43"/>
     </row>
     <row r="51" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="52" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11215,372 +11985,494 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:J1005"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
     <col min="4" max="10" width="16.7109375" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" customWidth="1"/>
+    <col min="11" max="19" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="84" t="s">
+      <c r="B1" s="124"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="84" t="s">
+      <c r="E1" s="129"/>
+      <c r="F1" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="72"/>
-      <c r="H1" s="4" t="s">
+      <c r="G1" s="129"/>
+      <c r="H1" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="47" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="78"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="85" t="s">
+      <c r="A2" s="126"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="86"/>
-      <c r="F2" s="85" t="s">
+      <c r="E2" s="95"/>
+      <c r="F2" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="86"/>
-      <c r="H2" s="89">
+      <c r="G2" s="95"/>
+      <c r="H2" s="98">
         <v>46232</v>
       </c>
-      <c r="I2" s="64" t="s">
+      <c r="I2" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="67"/>
+      <c r="J2" s="121"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="78"/>
-      <c r="B3" s="79"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="68"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="78"/>
-      <c r="B4" s="79"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="68"/>
+      <c r="A3" s="126"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="122"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="126"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="122"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="98" t="s">
+      <c r="A5" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="104" t="s">
+      <c r="B5" s="80"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="131" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="74"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="132"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="100" t="s">
+      <c r="A6" s="130" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="52"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="105"/>
-      <c r="B7" s="106"/>
-      <c r="C7" s="106"/>
-      <c r="D7" s="106"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="107"/>
+      <c r="A7" s="133"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="134"/>
+      <c r="D7" s="134"/>
+      <c r="E7" s="134"/>
+      <c r="F7" s="134"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="134"/>
+      <c r="I7" s="134"/>
+      <c r="J7" s="135"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="108"/>
-      <c r="B8" s="109"/>
-      <c r="C8" s="109"/>
-      <c r="D8" s="109"/>
-      <c r="E8" s="109"/>
-      <c r="F8" s="109"/>
-      <c r="G8" s="109"/>
-      <c r="H8" s="109"/>
-      <c r="I8" s="109"/>
-      <c r="J8" s="110"/>
+      <c r="A8" s="136"/>
+      <c r="B8" s="137"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="137"/>
+      <c r="F8" s="137"/>
+      <c r="G8" s="137"/>
+      <c r="H8" s="137"/>
+      <c r="I8" s="137"/>
+      <c r="J8" s="138"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="108"/>
-      <c r="B9" s="109"/>
-      <c r="C9" s="109"/>
-      <c r="D9" s="109"/>
-      <c r="E9" s="109"/>
-      <c r="F9" s="109"/>
-      <c r="G9" s="109"/>
-      <c r="H9" s="109"/>
-      <c r="I9" s="109"/>
-      <c r="J9" s="110"/>
+      <c r="A9" s="136"/>
+      <c r="B9" s="137"/>
+      <c r="C9" s="137"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="137"/>
+      <c r="F9" s="137"/>
+      <c r="G9" s="137"/>
+      <c r="H9" s="137"/>
+      <c r="I9" s="137"/>
+      <c r="J9" s="138"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="108"/>
-      <c r="B10" s="109"/>
-      <c r="C10" s="109"/>
-      <c r="D10" s="109"/>
-      <c r="E10" s="109"/>
-      <c r="F10" s="109"/>
-      <c r="G10" s="109"/>
-      <c r="H10" s="109"/>
-      <c r="I10" s="109"/>
-      <c r="J10" s="110"/>
+      <c r="A10" s="136"/>
+      <c r="B10" s="137"/>
+      <c r="C10" s="137"/>
+      <c r="D10" s="137"/>
+      <c r="E10" s="137"/>
+      <c r="F10" s="137"/>
+      <c r="G10" s="137"/>
+      <c r="H10" s="137"/>
+      <c r="I10" s="137"/>
+      <c r="J10" s="138"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="108"/>
-      <c r="B11" s="109"/>
-      <c r="C11" s="109"/>
-      <c r="D11" s="109"/>
-      <c r="E11" s="109"/>
-      <c r="F11" s="109"/>
-      <c r="G11" s="109"/>
-      <c r="H11" s="109"/>
-      <c r="I11" s="109"/>
-      <c r="J11" s="110"/>
+      <c r="A11" s="136"/>
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="137"/>
+      <c r="G11" s="137"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="138"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="108"/>
-      <c r="B12" s="109"/>
-      <c r="C12" s="109"/>
-      <c r="D12" s="109"/>
-      <c r="E12" s="109"/>
-      <c r="F12" s="109"/>
-      <c r="G12" s="109"/>
-      <c r="H12" s="109"/>
-      <c r="I12" s="109"/>
-      <c r="J12" s="110"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="111"/>
-      <c r="B13" s="112"/>
-      <c r="C13" s="112"/>
-      <c r="D13" s="112"/>
-      <c r="E13" s="112"/>
-      <c r="F13" s="112"/>
-      <c r="G13" s="112"/>
-      <c r="H13" s="112"/>
-      <c r="I13" s="112"/>
-      <c r="J13" s="113"/>
+      <c r="A12" s="136"/>
+      <c r="B12" s="137"/>
+      <c r="C12" s="137"/>
+      <c r="D12" s="137"/>
+      <c r="E12" s="137"/>
+      <c r="F12" s="137"/>
+      <c r="G12" s="137"/>
+      <c r="H12" s="137"/>
+      <c r="I12" s="137"/>
+      <c r="J12" s="138"/>
+    </row>
+    <row r="13" spans="1:10" ht="21" customHeight="1">
+      <c r="A13" s="136"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="138"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="100" t="s">
+      <c r="A14" s="139"/>
+      <c r="B14" s="140"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="140"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="140"/>
+      <c r="I14" s="140"/>
+      <c r="J14" s="141"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="52"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="100" t="s">
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="114"/>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="49"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="59" t="s">
+      <c r="B16" s="58"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="14" t="s">
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J16" s="48" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="100" t="s">
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="130" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="49"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="14" t="s">
+      <c r="B17" s="58"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E17" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F17" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G17" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="114" t="s">
+      <c r="H17" s="142" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="49"/>
-      <c r="J16" s="52"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="101" t="s">
+      <c r="I17" s="58"/>
+      <c r="J17" s="114"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="107" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="102"/>
-      <c r="C17" s="103"/>
-      <c r="D17" s="16" t="s">
+      <c r="B18" s="112"/>
+      <c r="C18" s="113"/>
+      <c r="D18" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E18" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F18" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="G17" s="16" t="s">
+      <c r="G18" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="59" t="s">
+      <c r="H18" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="I17" s="49"/>
-      <c r="J17" s="52"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="101" t="s">
+      <c r="I18" s="58"/>
+      <c r="J18" s="114"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="107"/>
+      <c r="B19" s="112"/>
+      <c r="C19" s="113"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="114"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="130" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="114"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="130" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="58"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="68" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J21" s="48" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="130" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="58"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="142" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="58"/>
+      <c r="J22" s="114"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="107" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="108"/>
+      <c r="C23" s="109"/>
+      <c r="D23" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="I23" s="110"/>
+      <c r="J23" s="111"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="107"/>
+      <c r="B24" s="112"/>
+      <c r="C24" s="113"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="114"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="130" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="58"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="114"/>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A26" s="130" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="58"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" s="48" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A27" s="130" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="58"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="H27" s="142" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="58"/>
+      <c r="J27" s="114"/>
+    </row>
+    <row r="28" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A28" s="107" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="102"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="16" t="s">
+      <c r="B28" s="108"/>
+      <c r="C28" s="109"/>
+      <c r="D28" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E28" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F28" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G28" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="H18" s="59" t="s">
+      <c r="H28" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="I18" s="49"/>
-      <c r="J18" s="52"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="101"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="52"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="101"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="52"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="101"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="50"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="52"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="101"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="50"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="52"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="99"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="115"/>
-    </row>
-    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
+      <c r="I28" s="110"/>
+      <c r="J28" s="111"/>
+    </row>
+    <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A29" s="115"/>
+      <c r="B29" s="116"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="118"/>
+      <c r="I29" s="119"/>
+      <c r="J29" s="120"/>
+    </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12552,48 +13444,118 @@
     <row r="998" ht="12.75" customHeight="1"/>
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
+    <row r="1001" ht="12.75" customHeight="1"/>
+    <row r="1002" ht="12.75" customHeight="1"/>
+    <row r="1003" ht="12.75" customHeight="1"/>
+    <row r="1004" ht="12.75" customHeight="1"/>
+    <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
+  <mergeCells count="39">
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="D21:H21"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A7:J14"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D16:H16"/>
     <mergeCell ref="H17:J17"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="D2:E4"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H27:J27"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09D10575-ADAF-418F-8A46-2449D88F2A14}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="17.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col min="7" max="7" width="34.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.75">
+      <c r="A1" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" s="56"/>
+    </row>
+    <row r="2" spans="1:7" ht="27.75" customHeight="1">
+      <c r="A2" s="49"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="C4" s="52"/>
+      <c r="F4" s="51"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="F5" s="51"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" thickBot="1">
+      <c r="E10" s="50"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" thickTop="1"/>
+  </sheetData>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
@@ -12604,182 +13566,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="84" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="84" t="s">
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="84" t="s">
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="84" t="s">
+      <c r="P1" s="81"/>
+      <c r="Q1" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="72"/>
-      <c r="S1" s="84" t="s">
+      <c r="R1" s="81"/>
+      <c r="S1" s="93" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="74"/>
+      <c r="T1" s="83"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="78"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="86"/>
-      <c r="O2" s="85"/>
-      <c r="P2" s="86"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="86"/>
-      <c r="S2" s="85"/>
-      <c r="T2" s="121"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="94"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="94"/>
+      <c r="P2" s="95"/>
+      <c r="Q2" s="94"/>
+      <c r="R2" s="95"/>
+      <c r="S2" s="94"/>
+      <c r="T2" s="148"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="78"/>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="80"/>
-      <c r="O3" s="87"/>
-      <c r="P3" s="80"/>
-      <c r="Q3" s="87"/>
-      <c r="R3" s="80"/>
-      <c r="S3" s="87"/>
-      <c r="T3" s="122"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="96"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="96"/>
+      <c r="T3" s="149"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="123"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="91"/>
+      <c r="M4" s="91"/>
+      <c r="N4" s="92"/>
+      <c r="O4" s="97"/>
+      <c r="P4" s="92"/>
+      <c r="Q4" s="97"/>
+      <c r="R4" s="92"/>
+      <c r="S4" s="97"/>
+      <c r="T4" s="150"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="98" t="s">
+      <c r="A5" s="151" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="73" t="s">
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="71"/>
-      <c r="R5" s="71"/>
-      <c r="S5" s="71"/>
-      <c r="T5" s="74"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="80"/>
+      <c r="N5" s="80"/>
+      <c r="O5" s="80"/>
+      <c r="P5" s="80"/>
+      <c r="Q5" s="80"/>
+      <c r="R5" s="80"/>
+      <c r="S5" s="80"/>
+      <c r="T5" s="83"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="100" t="s">
+      <c r="A6" s="152" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="59" t="s">
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="49"/>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49"/>
-      <c r="T6" s="52"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="58"/>
+      <c r="P6" s="58"/>
+      <c r="Q6" s="58"/>
+      <c r="R6" s="58"/>
+      <c r="S6" s="58"/>
+      <c r="T6" s="61"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="100" t="s">
+      <c r="A7" s="152" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="59" t="s">
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="49"/>
-      <c r="R7" s="49"/>
-      <c r="S7" s="49"/>
-      <c r="T7" s="52"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="58"/>
+      <c r="L7" s="58"/>
+      <c r="M7" s="58"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="58"/>
+      <c r="P7" s="58"/>
+      <c r="Q7" s="58"/>
+      <c r="R7" s="58"/>
+      <c r="S7" s="58"/>
+      <c r="T7" s="61"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -12804,156 +13766,156 @@
       <c r="T8" s="10"/>
     </row>
     <row r="9" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A9" s="20"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="22" t="s">
+      <c r="A9" s="16"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23" t="s">
+      <c r="D9" s="19"/>
+      <c r="E9" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="23"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
-      <c r="N9" s="21"/>
-      <c r="O9" s="21"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="21"/>
-      <c r="R9" s="21"/>
-      <c r="S9" s="21"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="21"/>
-      <c r="V9" s="21"/>
-      <c r="W9" s="21"/>
-      <c r="X9" s="21"/>
-      <c r="Y9" s="21"/>
-      <c r="Z9" s="21"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="17"/>
     </row>
     <row r="10" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A10" s="20"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21" t="s">
+      <c r="A10" s="16"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
-      <c r="P10" s="21"/>
-      <c r="Q10" s="21"/>
-      <c r="R10" s="21"/>
-      <c r="S10" s="21"/>
-      <c r="T10" s="25"/>
-      <c r="U10" s="21"/>
-      <c r="V10" s="21"/>
-      <c r="W10" s="21"/>
-      <c r="X10" s="21"/>
-      <c r="Y10" s="21"/>
-      <c r="Z10" s="21"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="17"/>
+      <c r="V10" s="17"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="17"/>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="17"/>
     </row>
     <row r="11" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A11" s="20"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="21"/>
-      <c r="N11" s="21"/>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="25"/>
-      <c r="U11" s="21"/>
-      <c r="V11" s="21"/>
-      <c r="W11" s="21"/>
-      <c r="X11" s="21"/>
-      <c r="Y11" s="21"/>
-      <c r="Z11" s="21"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="17"/>
+      <c r="Y11" s="17"/>
+      <c r="Z11" s="17"/>
     </row>
     <row r="12" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A12" s="20"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21" t="s">
+      <c r="A12" s="16"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="27"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="21"/>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="21"/>
-      <c r="S12" s="21"/>
-      <c r="T12" s="25"/>
-      <c r="U12" s="21"/>
-      <c r="V12" s="21"/>
-      <c r="W12" s="21"/>
-      <c r="X12" s="21"/>
-      <c r="Y12" s="21"/>
-      <c r="Z12" s="21"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="17"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="17"/>
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="17"/>
     </row>
     <row r="13" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A13" s="20"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29" t="s">
+      <c r="A13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="29"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="25"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="17"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="17"/>
+      <c r="Y13" s="17"/>
+      <c r="Z13" s="17"/>
     </row>
     <row r="14" spans="1:26" ht="8.25" customHeight="1">
       <c r="A14" s="8"/>
@@ -12978,522 +13940,522 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="100" t="s">
+      <c r="A15" s="152" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="126" t="s">
+      <c r="B15" s="59"/>
+      <c r="C15" s="155" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="50"/>
-      <c r="E15" s="114" t="s">
+      <c r="D15" s="59"/>
+      <c r="E15" s="142" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="50"/>
-      <c r="G15" s="114" t="s">
+      <c r="F15" s="59"/>
+      <c r="G15" s="142" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="49"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="114" t="s">
+      <c r="H15" s="58"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="142" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="50"/>
-      <c r="L15" s="114" t="s">
+      <c r="K15" s="59"/>
+      <c r="L15" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="49"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="114" t="s">
+      <c r="M15" s="58"/>
+      <c r="N15" s="59"/>
+      <c r="O15" s="142" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="50"/>
+      <c r="P15" s="58"/>
+      <c r="Q15" s="59"/>
       <c r="R15" s="14" t="s">
         <v>49</v>
       </c>
       <c r="S15" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="T15" s="31" t="s">
+      <c r="T15" s="27" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="124">
+      <c r="A16" s="153">
         <v>1</v>
       </c>
-      <c r="B16" s="50"/>
-      <c r="C16" s="125" t="s">
+      <c r="B16" s="59"/>
+      <c r="C16" s="154" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="125" t="s">
+      <c r="D16" s="59"/>
+      <c r="E16" s="154" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="50"/>
-      <c r="G16" s="116" t="s">
+      <c r="F16" s="59"/>
+      <c r="G16" s="143" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="49"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="116" t="s">
+      <c r="H16" s="58"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="143" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="50"/>
-      <c r="L16" s="118" t="s">
+      <c r="K16" s="59"/>
+      <c r="L16" s="145" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="49"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="118" t="s">
+      <c r="M16" s="58"/>
+      <c r="N16" s="59"/>
+      <c r="O16" s="145" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="50"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="32"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="34"/>
-      <c r="V16" s="34"/>
-      <c r="W16" s="34"/>
-      <c r="X16" s="34"/>
-      <c r="Y16" s="34"/>
-      <c r="Z16" s="34"/>
+      <c r="P16" s="58"/>
+      <c r="Q16" s="59"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="30"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="30"/>
+      <c r="X16" s="30"/>
+      <c r="Y16" s="30"/>
+      <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="124">
+      <c r="A17" s="153">
         <v>2</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="125" t="s">
+      <c r="B17" s="59"/>
+      <c r="C17" s="154" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="50"/>
-      <c r="E17" s="125" t="s">
+      <c r="D17" s="59"/>
+      <c r="E17" s="154" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="50"/>
-      <c r="G17" s="116" t="s">
+      <c r="F17" s="59"/>
+      <c r="G17" s="143" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="49"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="116" t="s">
+      <c r="H17" s="58"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="143" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="50"/>
-      <c r="L17" s="118" t="s">
+      <c r="K17" s="59"/>
+      <c r="L17" s="145" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="49"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="118" t="s">
+      <c r="M17" s="58"/>
+      <c r="N17" s="59"/>
+      <c r="O17" s="145" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="49"/>
-      <c r="Q17" s="50"/>
-      <c r="R17" s="32"/>
-      <c r="S17" s="32"/>
-      <c r="T17" s="33"/>
-      <c r="U17" s="34"/>
-      <c r="V17" s="34"/>
-      <c r="W17" s="34"/>
-      <c r="X17" s="34"/>
-      <c r="Y17" s="34"/>
-      <c r="Z17" s="34"/>
+      <c r="P17" s="58"/>
+      <c r="Q17" s="59"/>
+      <c r="R17" s="28"/>
+      <c r="S17" s="28"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="30"/>
+      <c r="V17" s="30"/>
+      <c r="W17" s="30"/>
+      <c r="X17" s="30"/>
+      <c r="Y17" s="30"/>
+      <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="124"/>
-      <c r="B18" s="50"/>
-      <c r="C18" s="125"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="116"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="116"/>
-      <c r="K18" s="50"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="49"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="118"/>
-      <c r="P18" s="49"/>
-      <c r="Q18" s="50"/>
-      <c r="R18" s="32"/>
-      <c r="S18" s="32"/>
-      <c r="T18" s="33"/>
-      <c r="U18" s="34"/>
-      <c r="V18" s="34"/>
-      <c r="W18" s="34"/>
-      <c r="X18" s="34"/>
-      <c r="Y18" s="34"/>
-      <c r="Z18" s="34"/>
+      <c r="A18" s="153"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="154"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="154"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="143"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="59"/>
+      <c r="J18" s="143"/>
+      <c r="K18" s="59"/>
+      <c r="L18" s="145"/>
+      <c r="M18" s="58"/>
+      <c r="N18" s="59"/>
+      <c r="O18" s="145"/>
+      <c r="P18" s="58"/>
+      <c r="Q18" s="59"/>
+      <c r="R18" s="28"/>
+      <c r="S18" s="28"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="30"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="30"/>
+      <c r="X18" s="30"/>
+      <c r="Y18" s="30"/>
+      <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="124"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="125"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="118"/>
-      <c r="M19" s="49"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="118"/>
-      <c r="P19" s="49"/>
-      <c r="Q19" s="50"/>
-      <c r="R19" s="32"/>
-      <c r="S19" s="32"/>
-      <c r="T19" s="33"/>
-      <c r="U19" s="34"/>
-      <c r="V19" s="34"/>
-      <c r="W19" s="34"/>
-      <c r="X19" s="34"/>
-      <c r="Y19" s="34"/>
-      <c r="Z19" s="34"/>
+      <c r="A19" s="153"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="154"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="154"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="143"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="143"/>
+      <c r="K19" s="59"/>
+      <c r="L19" s="145"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="59"/>
+      <c r="O19" s="145"/>
+      <c r="P19" s="58"/>
+      <c r="Q19" s="59"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="29"/>
+      <c r="U19" s="30"/>
+      <c r="V19" s="30"/>
+      <c r="W19" s="30"/>
+      <c r="X19" s="30"/>
+      <c r="Y19" s="30"/>
+      <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="124"/>
-      <c r="B20" s="50"/>
-      <c r="C20" s="125"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="116"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="116"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="118"/>
-      <c r="M20" s="49"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="118"/>
-      <c r="P20" s="49"/>
-      <c r="Q20" s="50"/>
-      <c r="R20" s="32"/>
-      <c r="S20" s="32"/>
-      <c r="T20" s="33"/>
-      <c r="U20" s="34"/>
-      <c r="V20" s="34"/>
-      <c r="W20" s="34"/>
-      <c r="X20" s="34"/>
-      <c r="Y20" s="34"/>
-      <c r="Z20" s="34"/>
+      <c r="A20" s="153"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="154"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="154"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="143"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="59"/>
+      <c r="J20" s="143"/>
+      <c r="K20" s="59"/>
+      <c r="L20" s="145"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="59"/>
+      <c r="O20" s="145"/>
+      <c r="P20" s="58"/>
+      <c r="Q20" s="59"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="124"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="125"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="125"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="116"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="118"/>
-      <c r="M21" s="49"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="118"/>
-      <c r="P21" s="49"/>
-      <c r="Q21" s="50"/>
-      <c r="R21" s="32"/>
-      <c r="S21" s="32"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="34"/>
-      <c r="V21" s="34"/>
-      <c r="W21" s="34"/>
-      <c r="X21" s="34"/>
-      <c r="Y21" s="34"/>
-      <c r="Z21" s="34"/>
+      <c r="A21" s="153"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="154"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="154"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="143"/>
+      <c r="H21" s="58"/>
+      <c r="I21" s="59"/>
+      <c r="J21" s="143"/>
+      <c r="K21" s="59"/>
+      <c r="L21" s="145"/>
+      <c r="M21" s="58"/>
+      <c r="N21" s="59"/>
+      <c r="O21" s="145"/>
+      <c r="P21" s="58"/>
+      <c r="Q21" s="59"/>
+      <c r="R21" s="28"/>
+      <c r="S21" s="28"/>
+      <c r="T21" s="29"/>
+      <c r="U21" s="30"/>
+      <c r="V21" s="30"/>
+      <c r="W21" s="30"/>
+      <c r="X21" s="30"/>
+      <c r="Y21" s="30"/>
+      <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="124"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="125"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="116"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="116"/>
-      <c r="K22" s="50"/>
-      <c r="L22" s="118"/>
-      <c r="M22" s="49"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="118"/>
-      <c r="P22" s="49"/>
-      <c r="Q22" s="50"/>
-      <c r="R22" s="32"/>
-      <c r="S22" s="32"/>
-      <c r="T22" s="33"/>
-      <c r="U22" s="34"/>
-      <c r="V22" s="34"/>
-      <c r="W22" s="34"/>
-      <c r="X22" s="34"/>
-      <c r="Y22" s="34"/>
-      <c r="Z22" s="34"/>
+      <c r="A22" s="153"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="154"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="154"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="143"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="143"/>
+      <c r="K22" s="59"/>
+      <c r="L22" s="145"/>
+      <c r="M22" s="58"/>
+      <c r="N22" s="59"/>
+      <c r="O22" s="145"/>
+      <c r="P22" s="58"/>
+      <c r="Q22" s="59"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="30"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="30"/>
+      <c r="X22" s="30"/>
+      <c r="Y22" s="30"/>
+      <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="124"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="125"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="125"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="116"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="116"/>
-      <c r="K23" s="50"/>
-      <c r="L23" s="118"/>
-      <c r="M23" s="49"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="118"/>
-      <c r="P23" s="49"/>
-      <c r="Q23" s="50"/>
-      <c r="R23" s="32"/>
-      <c r="S23" s="32"/>
-      <c r="T23" s="33"/>
-      <c r="U23" s="34"/>
-      <c r="V23" s="34"/>
-      <c r="W23" s="34"/>
-      <c r="X23" s="34"/>
-      <c r="Y23" s="34"/>
-      <c r="Z23" s="34"/>
+      <c r="A23" s="153"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="154"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="154"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="143"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="143"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="145"/>
+      <c r="M23" s="58"/>
+      <c r="N23" s="59"/>
+      <c r="O23" s="145"/>
+      <c r="P23" s="58"/>
+      <c r="Q23" s="59"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="124"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="125"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="125"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="116"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="116"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="118"/>
-      <c r="M24" s="49"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="118"/>
-      <c r="P24" s="49"/>
-      <c r="Q24" s="50"/>
-      <c r="R24" s="32"/>
-      <c r="S24" s="32"/>
-      <c r="T24" s="33"/>
-      <c r="U24" s="34"/>
-      <c r="V24" s="34"/>
-      <c r="W24" s="34"/>
-      <c r="X24" s="34"/>
-      <c r="Y24" s="34"/>
-      <c r="Z24" s="34"/>
+      <c r="A24" s="153"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="154"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="154"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="143"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="143"/>
+      <c r="K24" s="59"/>
+      <c r="L24" s="145"/>
+      <c r="M24" s="58"/>
+      <c r="N24" s="59"/>
+      <c r="O24" s="145"/>
+      <c r="P24" s="58"/>
+      <c r="Q24" s="59"/>
+      <c r="R24" s="28"/>
+      <c r="S24" s="28"/>
+      <c r="T24" s="29"/>
+      <c r="U24" s="30"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="30"/>
+      <c r="X24" s="30"/>
+      <c r="Y24" s="30"/>
+      <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="124"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="125"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="125"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="116"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="116"/>
-      <c r="K25" s="50"/>
-      <c r="L25" s="118"/>
-      <c r="M25" s="49"/>
-      <c r="N25" s="50"/>
-      <c r="O25" s="118"/>
-      <c r="P25" s="49"/>
-      <c r="Q25" s="50"/>
-      <c r="R25" s="32"/>
-      <c r="S25" s="32"/>
-      <c r="T25" s="33"/>
-      <c r="U25" s="34"/>
-      <c r="V25" s="34"/>
-      <c r="W25" s="34"/>
-      <c r="X25" s="34"/>
-      <c r="Y25" s="34"/>
-      <c r="Z25" s="34"/>
+      <c r="A25" s="153"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="154"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="154"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="143"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="143"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="145"/>
+      <c r="M25" s="58"/>
+      <c r="N25" s="59"/>
+      <c r="O25" s="145"/>
+      <c r="P25" s="58"/>
+      <c r="Q25" s="59"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
+      <c r="T25" s="29"/>
+      <c r="U25" s="30"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="30"/>
+      <c r="X25" s="30"/>
+      <c r="Y25" s="30"/>
+      <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="124"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="125"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="125"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="116"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="116"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="118"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="118"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="32"/>
-      <c r="S26" s="32"/>
-      <c r="T26" s="33"/>
-      <c r="U26" s="34"/>
-      <c r="V26" s="34"/>
-      <c r="W26" s="34"/>
-      <c r="X26" s="34"/>
-      <c r="Y26" s="34"/>
-      <c r="Z26" s="34"/>
+      <c r="A26" s="153"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="154"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="154"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="143"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="143"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="145"/>
+      <c r="M26" s="58"/>
+      <c r="N26" s="59"/>
+      <c r="O26" s="145"/>
+      <c r="P26" s="58"/>
+      <c r="Q26" s="59"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="124"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="125"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="125"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="116"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="118"/>
-      <c r="M27" s="49"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="118"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="50"/>
-      <c r="R27" s="32"/>
-      <c r="S27" s="32"/>
-      <c r="T27" s="33"/>
-      <c r="U27" s="34"/>
-      <c r="V27" s="34"/>
-      <c r="W27" s="34"/>
-      <c r="X27" s="34"/>
-      <c r="Y27" s="34"/>
-      <c r="Z27" s="34"/>
+      <c r="A27" s="153"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="154"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="154"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="143"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="143"/>
+      <c r="K27" s="59"/>
+      <c r="L27" s="145"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="59"/>
+      <c r="O27" s="145"/>
+      <c r="P27" s="58"/>
+      <c r="Q27" s="59"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="29"/>
+      <c r="U27" s="30"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="30"/>
+      <c r="X27" s="30"/>
+      <c r="Y27" s="30"/>
+      <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="124"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="125"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="125"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="116"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="116"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="118"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="118"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="50"/>
-      <c r="R28" s="32"/>
-      <c r="S28" s="32"/>
-      <c r="T28" s="33"/>
-      <c r="U28" s="34"/>
-      <c r="V28" s="34"/>
-      <c r="W28" s="34"/>
-      <c r="X28" s="34"/>
-      <c r="Y28" s="34"/>
-      <c r="Z28" s="34"/>
+      <c r="A28" s="153"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="154"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="154"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="143"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="143"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="145"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="59"/>
+      <c r="O28" s="145"/>
+      <c r="P28" s="58"/>
+      <c r="Q28" s="59"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="30"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="30"/>
+      <c r="X28" s="30"/>
+      <c r="Y28" s="30"/>
+      <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="124"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="125"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="125"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="116"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="116"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="118"/>
-      <c r="M29" s="49"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="118"/>
-      <c r="P29" s="49"/>
-      <c r="Q29" s="50"/>
-      <c r="R29" s="32"/>
-      <c r="S29" s="32"/>
-      <c r="T29" s="33"/>
-      <c r="U29" s="34"/>
-      <c r="V29" s="34"/>
-      <c r="W29" s="34"/>
-      <c r="X29" s="34"/>
-      <c r="Y29" s="34"/>
-      <c r="Z29" s="34"/>
+      <c r="A29" s="153"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="154"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="154"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="143"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="143"/>
+      <c r="K29" s="59"/>
+      <c r="L29" s="145"/>
+      <c r="M29" s="58"/>
+      <c r="N29" s="59"/>
+      <c r="O29" s="145"/>
+      <c r="P29" s="58"/>
+      <c r="Q29" s="59"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="124"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="125"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="125"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="116"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="116"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="118"/>
-      <c r="M30" s="49"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="118"/>
-      <c r="P30" s="49"/>
-      <c r="Q30" s="50"/>
-      <c r="R30" s="32"/>
-      <c r="S30" s="32"/>
-      <c r="T30" s="33"/>
-      <c r="U30" s="34"/>
-      <c r="V30" s="34"/>
-      <c r="W30" s="34"/>
-      <c r="X30" s="34"/>
-      <c r="Y30" s="34"/>
-      <c r="Z30" s="34"/>
+      <c r="A30" s="153"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="154"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="154"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="143"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="59"/>
+      <c r="J30" s="143"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="145"/>
+      <c r="M30" s="58"/>
+      <c r="N30" s="59"/>
+      <c r="O30" s="145"/>
+      <c r="P30" s="58"/>
+      <c r="Q30" s="59"/>
+      <c r="R30" s="28"/>
+      <c r="S30" s="28"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="30"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="30"/>
+      <c r="X30" s="30"/>
+      <c r="Y30" s="30"/>
+      <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="127"/>
-      <c r="B31" s="55"/>
-      <c r="C31" s="128"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="128"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="117"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="117"/>
-      <c r="K31" s="55"/>
-      <c r="L31" s="119"/>
-      <c r="M31" s="54"/>
-      <c r="N31" s="55"/>
-      <c r="O31" s="119"/>
-      <c r="P31" s="54"/>
-      <c r="Q31" s="55"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="36"/>
-      <c r="U31" s="34"/>
-      <c r="V31" s="34"/>
-      <c r="W31" s="34"/>
-      <c r="X31" s="34"/>
-      <c r="Y31" s="34"/>
-      <c r="Z31" s="34"/>
+      <c r="A31" s="156"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="157"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="157"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="144"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="64"/>
+      <c r="J31" s="144"/>
+      <c r="K31" s="64"/>
+      <c r="L31" s="146"/>
+      <c r="M31" s="63"/>
+      <c r="N31" s="64"/>
+      <c r="O31" s="146"/>
+      <c r="P31" s="63"/>
+      <c r="Q31" s="64"/>
+      <c r="R31" s="31"/>
+      <c r="S31" s="31"/>
+      <c r="T31" s="32"/>
+      <c r="U31" s="30"/>
+      <c r="V31" s="30"/>
+      <c r="W31" s="30"/>
+      <c r="X31" s="30"/>
+      <c r="Y31" s="30"/>
+      <c r="Z31" s="30"/>
     </row>
     <row r="32" spans="1:26" ht="12.75" customHeight="1">
       <c r="D32" s="3"/>

--- a/プロジェクト型演習_成果ドキュメント_一覧表示.xlsx
+++ b/プロジェクト型演習_成果ドキュメント_一覧表示.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\project-based-learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C4F06C-971B-4A71-9691-95BF18CCD783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413CFA3E-2C12-49AE-BCB7-30C786CB5A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="180" windowWidth="18420" windowHeight="10515" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -2062,21 +2062,228 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2095,9 +2302,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -2110,101 +2314,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2212,164 +2326,50 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4217,7 +4217,7 @@
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
                 </a:rPr>
-                <a:t>TaskBean</a:t>
+                <a:t>List&lt;TaskBean&gt;</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -6297,7 +6297,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Sheet1!$A$1:$G$2" spid="_x0000_s3092"/>
+                  <a14:cameraTool cellRange="Sheet1!$A$1:$G$2" spid="_x0000_s3093"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -6691,85 +6691,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="101" t="s">
+      <c r="C2" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="102"/>
-      <c r="O2" s="102"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109"/>
+      <c r="K2" s="109"/>
+      <c r="L2" s="109"/>
+      <c r="M2" s="109"/>
+      <c r="N2" s="109"/>
+      <c r="O2" s="109"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="88"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="99"/>
+      <c r="O3" s="99"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88"/>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="99"/>
+      <c r="M4" s="99"/>
+      <c r="N4" s="99"/>
+      <c r="O4" s="99"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="88"/>
-      <c r="D5" s="88"/>
-      <c r="E5" s="88"/>
-      <c r="F5" s="88"/>
-      <c r="G5" s="88"/>
-      <c r="H5" s="88"/>
-      <c r="I5" s="88"/>
-      <c r="J5" s="88"/>
-      <c r="K5" s="88"/>
-      <c r="L5" s="88"/>
-      <c r="M5" s="88"/>
-      <c r="N5" s="88"/>
-      <c r="O5" s="88"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="99"/>
+      <c r="M5" s="99"/>
+      <c r="N5" s="99"/>
+      <c r="O5" s="99"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="88"/>
-      <c r="O6" s="88"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99"/>
+      <c r="L6" s="99"/>
+      <c r="M6" s="99"/>
+      <c r="N6" s="99"/>
+      <c r="O6" s="99"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -6789,46 +6789,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="103" t="s">
+      <c r="E8" s="110" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="88"/>
-      <c r="I8" s="88"/>
-      <c r="J8" s="88"/>
-      <c r="K8" s="88"/>
-      <c r="L8" s="88"/>
-      <c r="M8" s="88"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="99"/>
+      <c r="K8" s="99"/>
+      <c r="L8" s="99"/>
+      <c r="M8" s="99"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="99" t="s">
+      <c r="G13" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="59"/>
-      <c r="I13" s="104">
+      <c r="H13" s="62"/>
+      <c r="I13" s="111">
         <v>46230</v>
       </c>
-      <c r="J13" s="58"/>
-      <c r="K13" s="59"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="62"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="99"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="99"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="59"/>
+      <c r="G14" s="106"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="106"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="62"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="99"/>
-      <c r="H15" s="59"/>
-      <c r="I15" s="99"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="59"/>
+      <c r="G15" s="106"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="106"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="62"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -6837,13 +6837,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="100" t="s">
+      <c r="G17" s="107" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="88"/>
-      <c r="I17" s="88"/>
-      <c r="J17" s="88"/>
-      <c r="K17" s="88"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="99"/>
+      <c r="J17" s="99"/>
+      <c r="K17" s="99"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -7857,19 +7857,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="93" t="s">
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="93" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="81"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
@@ -7881,194 +7881,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
+      <c r="A2" s="124"/>
+      <c r="B2" s="99"/>
       <c r="C2" s="89"/>
-      <c r="D2" s="94" t="s">
+      <c r="D2" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="95"/>
-      <c r="F2" s="94" t="s">
+      <c r="E2" s="87"/>
+      <c r="F2" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="95"/>
-      <c r="H2" s="98">
+      <c r="G2" s="87"/>
+      <c r="H2" s="90">
         <v>46231</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="92" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="113"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
-      <c r="B3" s="88"/>
+      <c r="A3" s="124"/>
+      <c r="B3" s="99"/>
       <c r="C3" s="89"/>
-      <c r="D3" s="96"/>
+      <c r="D3" s="88"/>
       <c r="E3" s="89"/>
-      <c r="F3" s="96"/>
+      <c r="F3" s="88"/>
       <c r="G3" s="89"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="114"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="92"/>
-      <c r="D4" s="97"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="78"/>
+      <c r="A4" s="125"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="115"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="79" t="s">
+      <c r="A5" s="116" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="82" t="s">
+      <c r="B5" s="71"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="117" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="83"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="118"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="119" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="68" t="s">
+      <c r="B6" s="61"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="66" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="120"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="119" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="68" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="120"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="68" t="s">
+      <c r="B8" s="61"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="66" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="120"/>
     </row>
     <row r="9" spans="1:10" ht="200.1" customHeight="1">
-      <c r="A9" s="69" t="s">
+      <c r="A9" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="140" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="59"/>
-      <c r="D9" s="60" t="s">
+      <c r="C9" s="62"/>
+      <c r="D9" s="130" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="120"/>
     </row>
     <row r="10" spans="1:10" ht="45" customHeight="1">
-      <c r="A10" s="70"/>
-      <c r="B10" s="72" t="s">
+      <c r="A10" s="138"/>
+      <c r="B10" s="140" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="59"/>
-      <c r="D10" s="60" t="s">
+      <c r="C10" s="62"/>
+      <c r="D10" s="130" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="158"/>
-      <c r="F10" s="158"/>
-      <c r="G10" s="158"/>
-      <c r="H10" s="158"/>
-      <c r="I10" s="158"/>
-      <c r="J10" s="159"/>
+      <c r="E10" s="141"/>
+      <c r="F10" s="141"/>
+      <c r="G10" s="141"/>
+      <c r="H10" s="141"/>
+      <c r="I10" s="141"/>
+      <c r="J10" s="142"/>
     </row>
     <row r="11" spans="1:10" ht="45" customHeight="1">
-      <c r="A11" s="71"/>
-      <c r="B11" s="72" t="s">
+      <c r="A11" s="139"/>
+      <c r="B11" s="140" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="59"/>
-      <c r="D11" s="60" t="s">
+      <c r="C11" s="62"/>
+      <c r="D11" s="130" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="120"/>
     </row>
     <row r="12" spans="1:10" ht="80.099999999999994" customHeight="1">
-      <c r="A12" s="57" t="s">
+      <c r="A12" s="119" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="58"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="60" t="s">
+      <c r="B12" s="61"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="130" t="s">
         <v>98</v>
       </c>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="120"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="131" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="63"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="65" t="s">
+      <c r="B13" s="132"/>
+      <c r="C13" s="133"/>
+      <c r="D13" s="134" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="66"/>
-      <c r="J13" s="67"/>
+      <c r="E13" s="135"/>
+      <c r="F13" s="135"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="135"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="136"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9059,18 +9059,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -9086,6 +9074,18 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -9104,19 +9104,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="143" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="93" t="s">
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="93" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="81"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -9128,48 +9128,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
+      <c r="A2" s="124"/>
+      <c r="B2" s="99"/>
       <c r="C2" s="89"/>
-      <c r="D2" s="94" t="s">
+      <c r="D2" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="95"/>
-      <c r="F2" s="94" t="s">
+      <c r="E2" s="87"/>
+      <c r="F2" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="95"/>
-      <c r="H2" s="98">
+      <c r="G2" s="87"/>
+      <c r="H2" s="90">
         <v>46230</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="92" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="113"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
-      <c r="B3" s="88"/>
+      <c r="A3" s="124"/>
+      <c r="B3" s="99"/>
       <c r="C3" s="89"/>
-      <c r="D3" s="96"/>
+      <c r="D3" s="88"/>
       <c r="E3" s="89"/>
-      <c r="F3" s="96"/>
+      <c r="F3" s="88"/>
       <c r="G3" s="89"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="114"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="92"/>
-      <c r="D4" s="97"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="78"/>
+      <c r="A4" s="125"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="115"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -10526,19 +10526,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="93" t="s">
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="93" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="81"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -10550,48 +10550,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
+      <c r="A2" s="124"/>
+      <c r="B2" s="99"/>
       <c r="C2" s="89"/>
-      <c r="D2" s="94" t="s">
+      <c r="D2" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="95"/>
-      <c r="F2" s="94" t="s">
+      <c r="E2" s="87"/>
+      <c r="F2" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="95"/>
-      <c r="H2" s="98">
+      <c r="G2" s="87"/>
+      <c r="H2" s="90">
         <v>46231</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="92" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="113"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
-      <c r="B3" s="88"/>
+      <c r="A3" s="124"/>
+      <c r="B3" s="99"/>
       <c r="C3" s="89"/>
-      <c r="D3" s="96"/>
+      <c r="D3" s="88"/>
       <c r="E3" s="89"/>
-      <c r="F3" s="96"/>
+      <c r="F3" s="88"/>
       <c r="G3" s="89"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="114"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="87"/>
-      <c r="B4" s="106"/>
+      <c r="A4" s="124"/>
+      <c r="B4" s="144"/>
       <c r="C4" s="89"/>
-      <c r="D4" s="96"/>
+      <c r="D4" s="88"/>
       <c r="E4" s="89"/>
-      <c r="F4" s="96"/>
+      <c r="F4" s="88"/>
       <c r="G4" s="89"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="114"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="33"/>
@@ -11998,19 +11998,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="128" t="s">
+      <c r="B1" s="96"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="129"/>
-      <c r="F1" s="128" t="s">
+      <c r="E1" s="74"/>
+      <c r="F1" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="129"/>
+      <c r="G1" s="74"/>
       <c r="H1" s="45" t="s">
         <v>5</v>
       </c>
@@ -12022,202 +12022,202 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="126"/>
-      <c r="B2" s="88"/>
+      <c r="A2" s="98"/>
+      <c r="B2" s="99"/>
       <c r="C2" s="89"/>
-      <c r="D2" s="94" t="s">
+      <c r="D2" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="95"/>
-      <c r="F2" s="94" t="s">
+      <c r="E2" s="87"/>
+      <c r="F2" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="95"/>
-      <c r="H2" s="98">
+      <c r="G2" s="87"/>
+      <c r="H2" s="90">
         <v>46232</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="92" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="121"/>
+      <c r="J2" s="93"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="126"/>
-      <c r="B3" s="88"/>
+      <c r="A3" s="98"/>
+      <c r="B3" s="99"/>
       <c r="C3" s="89"/>
-      <c r="D3" s="96"/>
+      <c r="D3" s="88"/>
       <c r="E3" s="89"/>
-      <c r="F3" s="96"/>
+      <c r="F3" s="88"/>
       <c r="G3" s="89"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="122"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="94"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="126"/>
-      <c r="B4" s="88"/>
+      <c r="A4" s="98"/>
+      <c r="B4" s="99"/>
       <c r="C4" s="89"/>
-      <c r="D4" s="96"/>
+      <c r="D4" s="88"/>
       <c r="E4" s="89"/>
-      <c r="F4" s="96"/>
+      <c r="F4" s="88"/>
       <c r="G4" s="89"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="122"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="94"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="131" t="s">
+      <c r="B5" s="71"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="75" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="132"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="76"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="130" t="s">
+      <c r="A6" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="114"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="65"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="133"/>
-      <c r="B7" s="134"/>
-      <c r="C7" s="134"/>
-      <c r="D7" s="134"/>
-      <c r="E7" s="134"/>
-      <c r="F7" s="134"/>
-      <c r="G7" s="134"/>
-      <c r="H7" s="134"/>
-      <c r="I7" s="134"/>
-      <c r="J7" s="135"/>
+      <c r="A7" s="77"/>
+      <c r="B7" s="78"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="78"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="78"/>
+      <c r="I7" s="78"/>
+      <c r="J7" s="79"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="136"/>
-      <c r="B8" s="137"/>
-      <c r="C8" s="137"/>
-      <c r="D8" s="137"/>
-      <c r="E8" s="137"/>
-      <c r="F8" s="137"/>
-      <c r="G8" s="137"/>
-      <c r="H8" s="137"/>
-      <c r="I8" s="137"/>
-      <c r="J8" s="138"/>
+      <c r="A8" s="80"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="82"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="136"/>
-      <c r="B9" s="137"/>
-      <c r="C9" s="137"/>
-      <c r="D9" s="137"/>
-      <c r="E9" s="137"/>
-      <c r="F9" s="137"/>
-      <c r="G9" s="137"/>
-      <c r="H9" s="137"/>
-      <c r="I9" s="137"/>
-      <c r="J9" s="138"/>
+      <c r="A9" s="80"/>
+      <c r="B9" s="81"/>
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="82"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="136"/>
-      <c r="B10" s="137"/>
-      <c r="C10" s="137"/>
-      <c r="D10" s="137"/>
-      <c r="E10" s="137"/>
-      <c r="F10" s="137"/>
-      <c r="G10" s="137"/>
-      <c r="H10" s="137"/>
-      <c r="I10" s="137"/>
-      <c r="J10" s="138"/>
+      <c r="A10" s="80"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="82"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="136"/>
-      <c r="B11" s="137"/>
-      <c r="C11" s="137"/>
-      <c r="D11" s="137"/>
-      <c r="E11" s="137"/>
-      <c r="F11" s="137"/>
-      <c r="G11" s="137"/>
-      <c r="H11" s="137"/>
-      <c r="I11" s="137"/>
-      <c r="J11" s="138"/>
+      <c r="A11" s="80"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="82"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="136"/>
-      <c r="B12" s="137"/>
-      <c r="C12" s="137"/>
-      <c r="D12" s="137"/>
-      <c r="E12" s="137"/>
-      <c r="F12" s="137"/>
-      <c r="G12" s="137"/>
-      <c r="H12" s="137"/>
-      <c r="I12" s="137"/>
-      <c r="J12" s="138"/>
+      <c r="A12" s="80"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="82"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="136"/>
-      <c r="B13" s="137"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="138"/>
+      <c r="A13" s="80"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="82"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="139"/>
-      <c r="B14" s="140"/>
-      <c r="C14" s="140"/>
-      <c r="D14" s="140"/>
-      <c r="E14" s="140"/>
-      <c r="F14" s="140"/>
-      <c r="G14" s="140"/>
-      <c r="H14" s="140"/>
-      <c r="I14" s="140"/>
-      <c r="J14" s="141"/>
+      <c r="A14" s="83"/>
+      <c r="B14" s="84"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="84"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="84"/>
+      <c r="J14" s="85"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="130" t="s">
+      <c r="A15" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="58"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="114"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="65"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="130" t="s">
+      <c r="A16" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="58"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="68" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="59"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="62"/>
       <c r="I16" s="14" t="s">
         <v>25</v>
       </c>
@@ -12226,11 +12226,11 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="130" t="s">
+      <c r="A17" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="59"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="62"/>
       <c r="D17" s="14" t="s">
         <v>27</v>
       </c>
@@ -12243,18 +12243,18 @@
       <c r="G17" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="142" t="s">
+      <c r="H17" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="I17" s="58"/>
-      <c r="J17" s="114"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="65"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="107" t="s">
+      <c r="A18" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="112"/>
-      <c r="C18" s="113"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="59"/>
       <c r="D18" s="15" t="s">
         <v>73</v>
       </c>
@@ -12267,51 +12267,51 @@
       <c r="G18" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="H18" s="68" t="s">
+      <c r="H18" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="I18" s="58"/>
-      <c r="J18" s="114"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="65"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="107"/>
-      <c r="B19" s="112"/>
-      <c r="C19" s="113"/>
+      <c r="A19" s="57"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="59"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="15"/>
       <c r="G19" s="15"/>
-      <c r="H19" s="68"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="114"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="65"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="130" t="s">
+      <c r="A20" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="114"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="65"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="130" t="s">
+      <c r="A21" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="58"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="68" t="s">
+      <c r="B21" s="61"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="59"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="62"/>
       <c r="I21" s="14" t="s">
         <v>25</v>
       </c>
@@ -12320,11 +12320,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="130" t="s">
+      <c r="A22" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="58"/>
-      <c r="C22" s="59"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="62"/>
       <c r="D22" s="14" t="s">
         <v>27</v>
       </c>
@@ -12337,18 +12337,18 @@
       <c r="G22" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H22" s="142" t="s">
+      <c r="H22" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="I22" s="58"/>
-      <c r="J22" s="114"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="65"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="107" t="s">
+      <c r="A23" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="108"/>
-      <c r="C23" s="109"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="64"/>
       <c r="D23" s="15" t="s">
         <v>82</v>
       </c>
@@ -12361,51 +12361,51 @@
       <c r="G23" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="H23" s="68" t="s">
+      <c r="H23" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="I23" s="110"/>
-      <c r="J23" s="111"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="69"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="107"/>
-      <c r="B24" s="112"/>
-      <c r="C24" s="113"/>
+      <c r="A24" s="57"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="59"/>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
-      <c r="H24" s="68"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="114"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="65"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="130" t="s">
+      <c r="A25" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="114"/>
+      <c r="B25" s="61"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="61"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="65"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="130" t="s">
+      <c r="A26" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="58"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="68" t="s">
+      <c r="B26" s="61"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="59"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="62"/>
       <c r="I26" s="14" t="s">
         <v>25</v>
       </c>
@@ -12414,11 +12414,11 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="130" t="s">
+      <c r="A27" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="58"/>
-      <c r="C27" s="59"/>
+      <c r="B27" s="61"/>
+      <c r="C27" s="62"/>
       <c r="D27" s="14" t="s">
         <v>27</v>
       </c>
@@ -12431,18 +12431,18 @@
       <c r="G27" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H27" s="142" t="s">
+      <c r="H27" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="I27" s="58"/>
-      <c r="J27" s="114"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="65"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="107" t="s">
+      <c r="A28" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="B28" s="108"/>
-      <c r="C28" s="109"/>
+      <c r="B28" s="63"/>
+      <c r="C28" s="64"/>
       <c r="D28" s="15" t="s">
         <v>86</v>
       </c>
@@ -12455,23 +12455,23 @@
       <c r="G28" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="H28" s="68" t="s">
+      <c r="H28" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="I28" s="110"/>
-      <c r="J28" s="111"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="69"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="115"/>
-      <c r="B29" s="116"/>
-      <c r="C29" s="117"/>
+      <c r="A29" s="100"/>
+      <c r="B29" s="101"/>
+      <c r="C29" s="102"/>
       <c r="D29" s="44"/>
       <c r="E29" s="44"/>
       <c r="F29" s="44"/>
       <c r="G29" s="44"/>
-      <c r="H29" s="118"/>
-      <c r="I29" s="119"/>
-      <c r="J29" s="120"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="104"/>
+      <c r="J29" s="105"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13451,18 +13451,17 @@
     <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -13479,17 +13478,18 @@
     <mergeCell ref="H18:J18"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H27:J27"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="D21:H21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13566,182 +13566,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="121" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="93" t="s">
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="93" t="s">
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="93" t="s">
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="93" t="s">
+      <c r="P1" s="72"/>
+      <c r="Q1" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="81"/>
-      <c r="S1" s="93" t="s">
+      <c r="R1" s="72"/>
+      <c r="S1" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="83"/>
+      <c r="T1" s="118"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
+      <c r="A2" s="124"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
       <c r="F2" s="89"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="94"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="94"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="94"/>
-      <c r="T2" s="148"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="155"/>
+      <c r="M2" s="155"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="86"/>
+      <c r="P2" s="87"/>
+      <c r="Q2" s="86"/>
+      <c r="R2" s="87"/>
+      <c r="S2" s="86"/>
+      <c r="T2" s="156"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
+      <c r="A3" s="124"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
       <c r="F3" s="89"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
       <c r="J3" s="89"/>
-      <c r="K3" s="96"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
       <c r="N3" s="89"/>
-      <c r="O3" s="96"/>
+      <c r="O3" s="88"/>
       <c r="P3" s="89"/>
-      <c r="Q3" s="96"/>
+      <c r="Q3" s="88"/>
       <c r="R3" s="89"/>
-      <c r="S3" s="96"/>
-      <c r="T3" s="149"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="157"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="92"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="92"/>
-      <c r="K4" s="97"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="91"/>
-      <c r="N4" s="92"/>
-      <c r="O4" s="97"/>
-      <c r="P4" s="92"/>
-      <c r="Q4" s="97"/>
-      <c r="R4" s="92"/>
-      <c r="S4" s="97"/>
-      <c r="T4" s="150"/>
+      <c r="A4" s="125"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="126"/>
+      <c r="J4" s="127"/>
+      <c r="K4" s="129"/>
+      <c r="L4" s="126"/>
+      <c r="M4" s="126"/>
+      <c r="N4" s="127"/>
+      <c r="O4" s="129"/>
+      <c r="P4" s="127"/>
+      <c r="Q4" s="129"/>
+      <c r="R4" s="127"/>
+      <c r="S4" s="129"/>
+      <c r="T4" s="158"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
       <c r="A5" s="151" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="82" t="s">
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="80"/>
-      <c r="O5" s="80"/>
-      <c r="P5" s="80"/>
-      <c r="Q5" s="80"/>
-      <c r="R5" s="80"/>
-      <c r="S5" s="80"/>
-      <c r="T5" s="83"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="71"/>
+      <c r="R5" s="71"/>
+      <c r="S5" s="71"/>
+      <c r="T5" s="118"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="152" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="68" t="s">
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
-      <c r="M6" s="58"/>
-      <c r="N6" s="58"/>
-      <c r="O6" s="58"/>
-      <c r="P6" s="58"/>
-      <c r="Q6" s="58"/>
-      <c r="R6" s="58"/>
-      <c r="S6" s="58"/>
-      <c r="T6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="120"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="152" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="68" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="58"/>
-      <c r="P7" s="58"/>
-      <c r="Q7" s="58"/>
-      <c r="R7" s="58"/>
-      <c r="S7" s="58"/>
-      <c r="T7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="61"/>
+      <c r="N7" s="61"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="61"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="61"/>
+      <c r="S7" s="61"/>
+      <c r="T7" s="120"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -13943,34 +13943,34 @@
       <c r="A15" s="152" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="155" t="s">
+      <c r="B15" s="62"/>
+      <c r="C15" s="154" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="59"/>
-      <c r="E15" s="142" t="s">
+      <c r="D15" s="62"/>
+      <c r="E15" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="59"/>
-      <c r="G15" s="142" t="s">
+      <c r="F15" s="62"/>
+      <c r="G15" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="58"/>
-      <c r="I15" s="59"/>
-      <c r="J15" s="142" t="s">
+      <c r="H15" s="61"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="59"/>
-      <c r="L15" s="142" t="s">
+      <c r="K15" s="62"/>
+      <c r="L15" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="58"/>
-      <c r="N15" s="59"/>
-      <c r="O15" s="142" t="s">
+      <c r="M15" s="61"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="58"/>
-      <c r="Q15" s="59"/>
+      <c r="P15" s="61"/>
+      <c r="Q15" s="62"/>
       <c r="R15" s="14" t="s">
         <v>49</v>
       </c>
@@ -13982,37 +13982,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="153">
+      <c r="A16" s="145">
         <v>1</v>
       </c>
-      <c r="B16" s="59"/>
-      <c r="C16" s="154" t="s">
+      <c r="B16" s="62"/>
+      <c r="C16" s="146" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="59"/>
-      <c r="E16" s="154" t="s">
+      <c r="D16" s="62"/>
+      <c r="E16" s="146" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="59"/>
-      <c r="G16" s="143" t="s">
+      <c r="F16" s="62"/>
+      <c r="G16" s="153" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="58"/>
-      <c r="I16" s="59"/>
-      <c r="J16" s="143" t="s">
+      <c r="H16" s="61"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="153" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="59"/>
-      <c r="L16" s="145" t="s">
+      <c r="K16" s="62"/>
+      <c r="L16" s="149" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="58"/>
-      <c r="N16" s="59"/>
-      <c r="O16" s="145" t="s">
+      <c r="M16" s="61"/>
+      <c r="N16" s="62"/>
+      <c r="O16" s="149" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="58"/>
-      <c r="Q16" s="59"/>
+      <c r="P16" s="61"/>
+      <c r="Q16" s="62"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
@@ -14024,37 +14024,37 @@
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="153">
+      <c r="A17" s="145">
         <v>2</v>
       </c>
-      <c r="B17" s="59"/>
-      <c r="C17" s="154" t="s">
+      <c r="B17" s="62"/>
+      <c r="C17" s="146" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="59"/>
-      <c r="E17" s="154" t="s">
+      <c r="D17" s="62"/>
+      <c r="E17" s="146" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="59"/>
-      <c r="G17" s="143" t="s">
+      <c r="F17" s="62"/>
+      <c r="G17" s="153" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="58"/>
-      <c r="I17" s="59"/>
-      <c r="J17" s="143" t="s">
+      <c r="H17" s="61"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="153" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="59"/>
-      <c r="L17" s="145" t="s">
+      <c r="K17" s="62"/>
+      <c r="L17" s="149" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="58"/>
-      <c r="N17" s="59"/>
-      <c r="O17" s="145" t="s">
+      <c r="M17" s="61"/>
+      <c r="N17" s="62"/>
+      <c r="O17" s="149" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="58"/>
-      <c r="Q17" s="59"/>
+      <c r="P17" s="61"/>
+      <c r="Q17" s="62"/>
       <c r="R17" s="28"/>
       <c r="S17" s="28"/>
       <c r="T17" s="29"/>
@@ -14066,23 +14066,23 @@
       <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="153"/>
-      <c r="B18" s="59"/>
-      <c r="C18" s="154"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="154"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="143"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="59"/>
-      <c r="J18" s="143"/>
-      <c r="K18" s="59"/>
-      <c r="L18" s="145"/>
-      <c r="M18" s="58"/>
-      <c r="N18" s="59"/>
-      <c r="O18" s="145"/>
-      <c r="P18" s="58"/>
-      <c r="Q18" s="59"/>
+      <c r="A18" s="145"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="146"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="146"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="153"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="153"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="149"/>
+      <c r="M18" s="61"/>
+      <c r="N18" s="62"/>
+      <c r="O18" s="149"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="62"/>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
       <c r="T18" s="29"/>
@@ -14094,23 +14094,23 @@
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="153"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="154"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="154"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="143"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="59"/>
-      <c r="J19" s="143"/>
-      <c r="K19" s="59"/>
-      <c r="L19" s="145"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="59"/>
-      <c r="O19" s="145"/>
-      <c r="P19" s="58"/>
-      <c r="Q19" s="59"/>
+      <c r="A19" s="145"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="146"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="146"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="153"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="153"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="149"/>
+      <c r="M19" s="61"/>
+      <c r="N19" s="62"/>
+      <c r="O19" s="149"/>
+      <c r="P19" s="61"/>
+      <c r="Q19" s="62"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
       <c r="T19" s="29"/>
@@ -14122,23 +14122,23 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="153"/>
-      <c r="B20" s="59"/>
-      <c r="C20" s="154"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="154"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="143"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="59"/>
-      <c r="J20" s="143"/>
-      <c r="K20" s="59"/>
-      <c r="L20" s="145"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="59"/>
-      <c r="O20" s="145"/>
-      <c r="P20" s="58"/>
-      <c r="Q20" s="59"/>
+      <c r="A20" s="145"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="146"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="146"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="153"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="153"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="149"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="149"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="62"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
       <c r="T20" s="29"/>
@@ -14150,23 +14150,23 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="153"/>
-      <c r="B21" s="59"/>
-      <c r="C21" s="154"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="154"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="59"/>
-      <c r="J21" s="143"/>
-      <c r="K21" s="59"/>
-      <c r="L21" s="145"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="59"/>
-      <c r="O21" s="145"/>
-      <c r="P21" s="58"/>
-      <c r="Q21" s="59"/>
+      <c r="A21" s="145"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="146"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="146"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="153"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="153"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="149"/>
+      <c r="M21" s="61"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="149"/>
+      <c r="P21" s="61"/>
+      <c r="Q21" s="62"/>
       <c r="R21" s="28"/>
       <c r="S21" s="28"/>
       <c r="T21" s="29"/>
@@ -14178,23 +14178,23 @@
       <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="153"/>
-      <c r="B22" s="59"/>
-      <c r="C22" s="154"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="154"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="143"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="143"/>
-      <c r="K22" s="59"/>
-      <c r="L22" s="145"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="59"/>
-      <c r="O22" s="145"/>
-      <c r="P22" s="58"/>
-      <c r="Q22" s="59"/>
+      <c r="A22" s="145"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="146"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="146"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="153"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="153"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="149"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="149"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="62"/>
       <c r="R22" s="28"/>
       <c r="S22" s="28"/>
       <c r="T22" s="29"/>
@@ -14206,23 +14206,23 @@
       <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="153"/>
-      <c r="B23" s="59"/>
-      <c r="C23" s="154"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="154"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="143"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="143"/>
-      <c r="K23" s="59"/>
-      <c r="L23" s="145"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="59"/>
-      <c r="O23" s="145"/>
-      <c r="P23" s="58"/>
-      <c r="Q23" s="59"/>
+      <c r="A23" s="145"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="146"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="146"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="153"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="153"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="149"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="62"/>
+      <c r="O23" s="149"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="62"/>
       <c r="R23" s="28"/>
       <c r="S23" s="28"/>
       <c r="T23" s="29"/>
@@ -14234,23 +14234,23 @@
       <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="153"/>
-      <c r="B24" s="59"/>
-      <c r="C24" s="154"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="154"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="143"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="59"/>
-      <c r="J24" s="143"/>
-      <c r="K24" s="59"/>
-      <c r="L24" s="145"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="59"/>
-      <c r="O24" s="145"/>
-      <c r="P24" s="58"/>
-      <c r="Q24" s="59"/>
+      <c r="A24" s="145"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="146"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="146"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="153"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="153"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="149"/>
+      <c r="M24" s="61"/>
+      <c r="N24" s="62"/>
+      <c r="O24" s="149"/>
+      <c r="P24" s="61"/>
+      <c r="Q24" s="62"/>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
       <c r="T24" s="29"/>
@@ -14262,23 +14262,23 @@
       <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="153"/>
-      <c r="B25" s="59"/>
-      <c r="C25" s="154"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="154"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="143"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="143"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="145"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="59"/>
-      <c r="O25" s="145"/>
-      <c r="P25" s="58"/>
-      <c r="Q25" s="59"/>
+      <c r="A25" s="145"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="146"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="146"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="153"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="153"/>
+      <c r="K25" s="62"/>
+      <c r="L25" s="149"/>
+      <c r="M25" s="61"/>
+      <c r="N25" s="62"/>
+      <c r="O25" s="149"/>
+      <c r="P25" s="61"/>
+      <c r="Q25" s="62"/>
       <c r="R25" s="28"/>
       <c r="S25" s="28"/>
       <c r="T25" s="29"/>
@@ -14290,23 +14290,23 @@
       <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="153"/>
-      <c r="B26" s="59"/>
-      <c r="C26" s="154"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="154"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="143"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="143"/>
-      <c r="K26" s="59"/>
-      <c r="L26" s="145"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="59"/>
-      <c r="O26" s="145"/>
-      <c r="P26" s="58"/>
-      <c r="Q26" s="59"/>
+      <c r="A26" s="145"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="146"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="146"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="153"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="153"/>
+      <c r="K26" s="62"/>
+      <c r="L26" s="149"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="62"/>
+      <c r="O26" s="149"/>
+      <c r="P26" s="61"/>
+      <c r="Q26" s="62"/>
       <c r="R26" s="28"/>
       <c r="S26" s="28"/>
       <c r="T26" s="29"/>
@@ -14318,23 +14318,23 @@
       <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="153"/>
-      <c r="B27" s="59"/>
-      <c r="C27" s="154"/>
-      <c r="D27" s="59"/>
-      <c r="E27" s="154"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="143"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="59"/>
-      <c r="J27" s="143"/>
-      <c r="K27" s="59"/>
-      <c r="L27" s="145"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="59"/>
-      <c r="O27" s="145"/>
-      <c r="P27" s="58"/>
-      <c r="Q27" s="59"/>
+      <c r="A27" s="145"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="146"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="146"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="153"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="153"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="149"/>
+      <c r="M27" s="61"/>
+      <c r="N27" s="62"/>
+      <c r="O27" s="149"/>
+      <c r="P27" s="61"/>
+      <c r="Q27" s="62"/>
       <c r="R27" s="28"/>
       <c r="S27" s="28"/>
       <c r="T27" s="29"/>
@@ -14346,23 +14346,23 @@
       <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="153"/>
-      <c r="B28" s="59"/>
-      <c r="C28" s="154"/>
-      <c r="D28" s="59"/>
-      <c r="E28" s="154"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="143"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="59"/>
-      <c r="J28" s="143"/>
-      <c r="K28" s="59"/>
-      <c r="L28" s="145"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="59"/>
-      <c r="O28" s="145"/>
-      <c r="P28" s="58"/>
-      <c r="Q28" s="59"/>
+      <c r="A28" s="145"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="146"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="146"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="153"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="153"/>
+      <c r="K28" s="62"/>
+      <c r="L28" s="149"/>
+      <c r="M28" s="61"/>
+      <c r="N28" s="62"/>
+      <c r="O28" s="149"/>
+      <c r="P28" s="61"/>
+      <c r="Q28" s="62"/>
       <c r="R28" s="28"/>
       <c r="S28" s="28"/>
       <c r="T28" s="29"/>
@@ -14374,23 +14374,23 @@
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="153"/>
-      <c r="B29" s="59"/>
-      <c r="C29" s="154"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="154"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="143"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="59"/>
-      <c r="J29" s="143"/>
-      <c r="K29" s="59"/>
-      <c r="L29" s="145"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="59"/>
-      <c r="O29" s="145"/>
-      <c r="P29" s="58"/>
-      <c r="Q29" s="59"/>
+      <c r="A29" s="145"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="146"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="146"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="153"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="153"/>
+      <c r="K29" s="62"/>
+      <c r="L29" s="149"/>
+      <c r="M29" s="61"/>
+      <c r="N29" s="62"/>
+      <c r="O29" s="149"/>
+      <c r="P29" s="61"/>
+      <c r="Q29" s="62"/>
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
       <c r="T29" s="29"/>
@@ -14402,23 +14402,23 @@
       <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="153"/>
-      <c r="B30" s="59"/>
-      <c r="C30" s="154"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="154"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="143"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="59"/>
-      <c r="J30" s="143"/>
-      <c r="K30" s="59"/>
-      <c r="L30" s="145"/>
-      <c r="M30" s="58"/>
-      <c r="N30" s="59"/>
-      <c r="O30" s="145"/>
-      <c r="P30" s="58"/>
-      <c r="Q30" s="59"/>
+      <c r="A30" s="145"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="146"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="146"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="153"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="153"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="149"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="149"/>
+      <c r="P30" s="61"/>
+      <c r="Q30" s="62"/>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
       <c r="T30" s="29"/>
@@ -14430,23 +14430,23 @@
       <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="156"/>
-      <c r="B31" s="64"/>
-      <c r="C31" s="157"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="157"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="144"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="64"/>
-      <c r="J31" s="144"/>
-      <c r="K31" s="64"/>
-      <c r="L31" s="146"/>
-      <c r="M31" s="63"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="146"/>
-      <c r="P31" s="63"/>
-      <c r="Q31" s="64"/>
+      <c r="A31" s="147"/>
+      <c r="B31" s="133"/>
+      <c r="C31" s="148"/>
+      <c r="D31" s="133"/>
+      <c r="E31" s="148"/>
+      <c r="F31" s="133"/>
+      <c r="G31" s="159"/>
+      <c r="H31" s="132"/>
+      <c r="I31" s="133"/>
+      <c r="J31" s="159"/>
+      <c r="K31" s="133"/>
+      <c r="L31" s="150"/>
+      <c r="M31" s="132"/>
+      <c r="N31" s="133"/>
+      <c r="O31" s="150"/>
+      <c r="P31" s="132"/>
+      <c r="Q31" s="133"/>
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
       <c r="T31" s="32"/>
@@ -15444,6 +15444,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -15468,118 +15580,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/プロジェクト型演習_成果ドキュメント_一覧表示.xlsx
+++ b/プロジェクト型演習_成果ドキュメント_一覧表示.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\project-based-learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413CFA3E-2C12-49AE-BCB7-30C786CB5A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEC6874-F03B-411F-8E20-40496DE81294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="180" windowWidth="18420" windowHeight="10515" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="180" windowWidth="18420" windowHeight="10515" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -2062,269 +2062,299 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2332,44 +2362,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5661,15 +5661,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>161066</xdr:colOff>
+      <xdr:colOff>142875</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>173531</xdr:rowOff>
+      <xdr:rowOff>125906</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>754676</xdr:colOff>
+      <xdr:colOff>736485</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>201409</xdr:rowOff>
+      <xdr:rowOff>153784</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5684,8 +5684,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="161066" y="1730055"/>
-          <a:ext cx="8329769" cy="1898031"/>
+          <a:off x="142875" y="1649906"/>
+          <a:ext cx="8344579" cy="1861441"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5731,72 +5731,6 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>197420</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>490681</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>115454</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="正方形/長方形 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60822DD2-196A-2994-25B2-035F7F2DFB0D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="346364" y="2294844"/>
-          <a:ext cx="7879772" cy="995610"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -6297,7 +6231,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="Sheet1!$A$1:$G$2" spid="_x0000_s3093"/>
+                  <a14:cameraTool cellRange="Sheet1!$A$1:$G$2" spid="_x0000_s3094"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -6691,85 +6625,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="108" t="s">
+      <c r="C2" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="109"/>
-      <c r="K2" s="109"/>
-      <c r="L2" s="109"/>
-      <c r="M2" s="109"/>
-      <c r="N2" s="109"/>
-      <c r="O2" s="109"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="79"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="99"/>
-      <c r="M3" s="99"/>
-      <c r="N3" s="99"/>
-      <c r="O3" s="99"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="99"/>
-      <c r="O4" s="99"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="99"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="99"/>
-      <c r="I5" s="99"/>
-      <c r="J5" s="99"/>
-      <c r="K5" s="99"/>
-      <c r="L5" s="99"/>
-      <c r="M5" s="99"/>
-      <c r="N5" s="99"/>
-      <c r="O5" s="99"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="66"/>
+      <c r="O5" s="66"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="99"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="99"/>
-      <c r="H6" s="99"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="99"/>
-      <c r="K6" s="99"/>
-      <c r="L6" s="99"/>
-      <c r="M6" s="99"/>
-      <c r="N6" s="99"/>
-      <c r="O6" s="99"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="66"/>
+      <c r="O6" s="66"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -6789,46 +6723,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="110" t="s">
+      <c r="E8" s="80" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="99"/>
-      <c r="G8" s="99"/>
-      <c r="H8" s="99"/>
-      <c r="I8" s="99"/>
-      <c r="J8" s="99"/>
-      <c r="K8" s="99"/>
-      <c r="L8" s="99"/>
-      <c r="M8" s="99"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="66"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="106" t="s">
+      <c r="G13" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="62"/>
-      <c r="I13" s="111">
+      <c r="H13" s="76"/>
+      <c r="I13" s="81">
         <v>46230</v>
       </c>
-      <c r="J13" s="61"/>
-      <c r="K13" s="62"/>
+      <c r="J13" s="75"/>
+      <c r="K13" s="76"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="106"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="106"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="62"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="75"/>
+      <c r="K14" s="76"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="106"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="106"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="62"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="76"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -6837,13 +6771,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="107" t="s">
+      <c r="G17" s="77" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="99"/>
-      <c r="I17" s="99"/>
-      <c r="J17" s="99"/>
-      <c r="K17" s="99"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="66"/>
+      <c r="K17" s="66"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -7857,19 +7791,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="104" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="128" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="128" t="s">
+      <c r="E1" s="70"/>
+      <c r="F1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="72"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
@@ -7881,194 +7815,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="124"/>
-      <c r="B2" s="99"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="86" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="87"/>
-      <c r="F2" s="86" t="s">
+      <c r="E2" s="72"/>
+      <c r="F2" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="87"/>
-      <c r="H2" s="90">
+      <c r="G2" s="72"/>
+      <c r="H2" s="57">
         <v>46231</v>
       </c>
-      <c r="I2" s="92" t="s">
+      <c r="I2" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="113"/>
+      <c r="J2" s="60"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="124"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="114"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="61"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="125"/>
-      <c r="B4" s="126"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="129"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="115"/>
+      <c r="A4" s="105"/>
+      <c r="B4" s="106"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="116" t="s">
+      <c r="A5" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="117" t="s">
+      <c r="B5" s="101"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="102" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="118"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
+      <c r="H5" s="101"/>
+      <c r="I5" s="101"/>
+      <c r="J5" s="103"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="119" t="s">
+      <c r="A6" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="66" t="s">
+      <c r="B6" s="75"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="91" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="120"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="84"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="119" t="s">
+      <c r="A7" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="66" t="s">
+      <c r="B7" s="75"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="91" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="120"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="84"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="119" t="s">
+      <c r="A8" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="66" t="s">
+      <c r="B8" s="75"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="91" t="s">
         <v>76</v>
       </c>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="120"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
+      <c r="J8" s="84"/>
     </row>
     <row r="9" spans="1:10" ht="200.1" customHeight="1">
-      <c r="A9" s="137" t="s">
+      <c r="A9" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="140" t="s">
+      <c r="B9" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="62"/>
-      <c r="D9" s="130" t="s">
+      <c r="C9" s="76"/>
+      <c r="D9" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="120"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="84"/>
     </row>
     <row r="10" spans="1:10" ht="45" customHeight="1">
-      <c r="A10" s="138"/>
-      <c r="B10" s="140" t="s">
+      <c r="A10" s="93"/>
+      <c r="B10" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="130" t="s">
+      <c r="C10" s="76"/>
+      <c r="D10" s="83" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="141"/>
-      <c r="F10" s="141"/>
-      <c r="G10" s="141"/>
-      <c r="H10" s="141"/>
-      <c r="I10" s="141"/>
-      <c r="J10" s="142"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="97"/>
     </row>
     <row r="11" spans="1:10" ht="45" customHeight="1">
-      <c r="A11" s="139"/>
-      <c r="B11" s="140" t="s">
+      <c r="A11" s="94"/>
+      <c r="B11" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="62"/>
-      <c r="D11" s="130" t="s">
+      <c r="C11" s="76"/>
+      <c r="D11" s="83" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="120"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="84"/>
     </row>
     <row r="12" spans="1:10" ht="80.099999999999994" customHeight="1">
-      <c r="A12" s="119" t="s">
+      <c r="A12" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="61"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="130" t="s">
+      <c r="B12" s="75"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="83" t="s">
         <v>98</v>
       </c>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="120"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="84"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="131" t="s">
+      <c r="A13" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="132"/>
-      <c r="C13" s="133"/>
-      <c r="D13" s="134" t="s">
+      <c r="B13" s="86"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="135"/>
-      <c r="F13" s="135"/>
-      <c r="G13" s="135"/>
-      <c r="H13" s="135"/>
-      <c r="I13" s="135"/>
-      <c r="J13" s="136"/>
+      <c r="E13" s="89"/>
+      <c r="F13" s="89"/>
+      <c r="G13" s="89"/>
+      <c r="H13" s="89"/>
+      <c r="I13" s="89"/>
+      <c r="J13" s="90"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9059,6 +8993,18 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -9074,18 +9020,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -9104,19 +9038,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="128" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="128" t="s">
+      <c r="E1" s="70"/>
+      <c r="F1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="72"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -9128,48 +9062,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="124"/>
-      <c r="B2" s="99"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="86" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="87"/>
-      <c r="F2" s="86" t="s">
+      <c r="E2" s="72"/>
+      <c r="F2" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="87"/>
-      <c r="H2" s="90">
+      <c r="G2" s="72"/>
+      <c r="H2" s="57">
         <v>46230</v>
       </c>
-      <c r="I2" s="92" t="s">
+      <c r="I2" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="113"/>
+      <c r="J2" s="60"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="124"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="114"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="61"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="125"/>
-      <c r="B4" s="126"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="129"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="115"/>
+      <c r="A4" s="105"/>
+      <c r="B4" s="106"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="99"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -10526,19 +10460,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="128" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="128" t="s">
+      <c r="E1" s="70"/>
+      <c r="F1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="72"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -10550,48 +10484,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="124"/>
-      <c r="B2" s="99"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="86" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="87"/>
-      <c r="F2" s="86" t="s">
+      <c r="E2" s="72"/>
+      <c r="F2" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="87"/>
-      <c r="H2" s="90">
+      <c r="G2" s="72"/>
+      <c r="H2" s="57">
         <v>46231</v>
       </c>
-      <c r="I2" s="92" t="s">
+      <c r="I2" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="113"/>
+      <c r="J2" s="60"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="124"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="114"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="61"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="124"/>
-      <c r="B4" s="144"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="114"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="61"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="33"/>
@@ -11998,19 +11932,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="125" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="126"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="130" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="74"/>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="131"/>
+      <c r="F1" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="74"/>
+      <c r="G1" s="131"/>
       <c r="H1" s="45" t="s">
         <v>5</v>
       </c>
@@ -12022,202 +11956,202 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="98"/>
-      <c r="B2" s="99"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="86" t="s">
+      <c r="A2" s="128"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="87"/>
-      <c r="F2" s="86" t="s">
+      <c r="E2" s="72"/>
+      <c r="F2" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="87"/>
-      <c r="H2" s="90">
+      <c r="G2" s="72"/>
+      <c r="H2" s="57">
         <v>46232</v>
       </c>
-      <c r="I2" s="92" t="s">
+      <c r="I2" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="93"/>
+      <c r="J2" s="123"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="98"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="94"/>
+      <c r="A3" s="128"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="124"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="98"/>
-      <c r="B4" s="99"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="94"/>
+      <c r="A4" s="128"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="124"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="75" t="s">
+      <c r="B5" s="101"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="133" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="76"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
+      <c r="H5" s="101"/>
+      <c r="I5" s="101"/>
+      <c r="J5" s="134"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="132" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="65"/>
+      <c r="B6" s="75"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="116"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="77"/>
-      <c r="B7" s="78"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="78"/>
-      <c r="J7" s="79"/>
+      <c r="A7" s="135"/>
+      <c r="B7" s="136"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
+      <c r="F7" s="136"/>
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="137"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="80"/>
-      <c r="B8" s="81"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
-      <c r="I8" s="81"/>
-      <c r="J8" s="82"/>
+      <c r="A8" s="138"/>
+      <c r="B8" s="139"/>
+      <c r="C8" s="139"/>
+      <c r="D8" s="139"/>
+      <c r="E8" s="139"/>
+      <c r="F8" s="139"/>
+      <c r="G8" s="139"/>
+      <c r="H8" s="139"/>
+      <c r="I8" s="139"/>
+      <c r="J8" s="140"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="80"/>
-      <c r="B9" s="81"/>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
-      <c r="J9" s="82"/>
+      <c r="A9" s="138"/>
+      <c r="B9" s="139"/>
+      <c r="C9" s="139"/>
+      <c r="D9" s="139"/>
+      <c r="E9" s="139"/>
+      <c r="F9" s="139"/>
+      <c r="G9" s="139"/>
+      <c r="H9" s="139"/>
+      <c r="I9" s="139"/>
+      <c r="J9" s="140"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="80"/>
-      <c r="B10" s="81"/>
-      <c r="C10" s="81"/>
-      <c r="D10" s="81"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="82"/>
+      <c r="A10" s="138"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="140"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="80"/>
-      <c r="B11" s="81"/>
-      <c r="C11" s="81"/>
-      <c r="D11" s="81"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="81"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="82"/>
+      <c r="A11" s="138"/>
+      <c r="B11" s="139"/>
+      <c r="C11" s="139"/>
+      <c r="D11" s="139"/>
+      <c r="E11" s="139"/>
+      <c r="F11" s="139"/>
+      <c r="G11" s="139"/>
+      <c r="H11" s="139"/>
+      <c r="I11" s="139"/>
+      <c r="J11" s="140"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="80"/>
-      <c r="B12" s="81"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="82"/>
+      <c r="A12" s="138"/>
+      <c r="B12" s="139"/>
+      <c r="C12" s="139"/>
+      <c r="D12" s="139"/>
+      <c r="E12" s="139"/>
+      <c r="F12" s="139"/>
+      <c r="G12" s="139"/>
+      <c r="H12" s="139"/>
+      <c r="I12" s="139"/>
+      <c r="J12" s="140"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="80"/>
-      <c r="B13" s="81"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="82"/>
+      <c r="A13" s="138"/>
+      <c r="B13" s="139"/>
+      <c r="C13" s="139"/>
+      <c r="D13" s="139"/>
+      <c r="E13" s="139"/>
+      <c r="F13" s="139"/>
+      <c r="G13" s="139"/>
+      <c r="H13" s="139"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="140"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="83"/>
-      <c r="B14" s="84"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="84"/>
-      <c r="G14" s="84"/>
-      <c r="H14" s="84"/>
-      <c r="I14" s="84"/>
-      <c r="J14" s="85"/>
+      <c r="A14" s="141"/>
+      <c r="B14" s="142"/>
+      <c r="C14" s="142"/>
+      <c r="D14" s="142"/>
+      <c r="E14" s="142"/>
+      <c r="F14" s="142"/>
+      <c r="G14" s="142"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="142"/>
+      <c r="J14" s="143"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="132" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61"/>
-      <c r="J15" s="65"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="75"/>
+      <c r="J15" s="116"/>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="132" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="66" t="s">
+      <c r="B16" s="75"/>
+      <c r="C16" s="76"/>
+      <c r="D16" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="62"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="76"/>
       <c r="I16" s="14" t="s">
         <v>25</v>
       </c>
@@ -12226,11 +12160,11 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="60" t="s">
+      <c r="A17" s="132" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="62"/>
+      <c r="B17" s="75"/>
+      <c r="C17" s="76"/>
       <c r="D17" s="14" t="s">
         <v>27</v>
       </c>
@@ -12243,18 +12177,18 @@
       <c r="G17" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="67" t="s">
+      <c r="H17" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="I17" s="61"/>
-      <c r="J17" s="65"/>
+      <c r="I17" s="75"/>
+      <c r="J17" s="116"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="57" t="s">
+      <c r="A18" s="109" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="58"/>
-      <c r="C18" s="59"/>
+      <c r="B18" s="114"/>
+      <c r="C18" s="115"/>
       <c r="D18" s="15" t="s">
         <v>73</v>
       </c>
@@ -12267,51 +12201,51 @@
       <c r="G18" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="H18" s="66" t="s">
+      <c r="H18" s="91" t="s">
         <v>78</v>
       </c>
-      <c r="I18" s="61"/>
-      <c r="J18" s="65"/>
+      <c r="I18" s="75"/>
+      <c r="J18" s="116"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="57"/>
-      <c r="B19" s="58"/>
-      <c r="C19" s="59"/>
+      <c r="A19" s="109"/>
+      <c r="B19" s="114"/>
+      <c r="C19" s="115"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="15"/>
       <c r="G19" s="15"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="65"/>
+      <c r="H19" s="91"/>
+      <c r="I19" s="75"/>
+      <c r="J19" s="116"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="60" t="s">
+      <c r="A20" s="132" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="61"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="65"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="75"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="75"/>
+      <c r="G20" s="75"/>
+      <c r="H20" s="75"/>
+      <c r="I20" s="75"/>
+      <c r="J20" s="116"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="60" t="s">
+      <c r="A21" s="132" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="61"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="66" t="s">
+      <c r="B21" s="75"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="E21" s="61"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="62"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="75"/>
+      <c r="H21" s="76"/>
       <c r="I21" s="14" t="s">
         <v>25</v>
       </c>
@@ -12320,11 +12254,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="132" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="62"/>
+      <c r="B22" s="75"/>
+      <c r="C22" s="76"/>
       <c r="D22" s="14" t="s">
         <v>27</v>
       </c>
@@ -12337,18 +12271,18 @@
       <c r="G22" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H22" s="67" t="s">
+      <c r="H22" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="I22" s="61"/>
-      <c r="J22" s="65"/>
+      <c r="I22" s="75"/>
+      <c r="J22" s="116"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="57" t="s">
+      <c r="A23" s="109" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="63"/>
-      <c r="C23" s="64"/>
+      <c r="B23" s="110"/>
+      <c r="C23" s="111"/>
       <c r="D23" s="15" t="s">
         <v>82</v>
       </c>
@@ -12361,51 +12295,51 @@
       <c r="G23" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="H23" s="66" t="s">
+      <c r="H23" s="91" t="s">
         <v>84</v>
       </c>
-      <c r="I23" s="68"/>
-      <c r="J23" s="69"/>
+      <c r="I23" s="112"/>
+      <c r="J23" s="113"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="57"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="59"/>
+      <c r="A24" s="109"/>
+      <c r="B24" s="114"/>
+      <c r="C24" s="115"/>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="65"/>
+      <c r="H24" s="91"/>
+      <c r="I24" s="75"/>
+      <c r="J24" s="116"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="60" t="s">
+      <c r="A25" s="132" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="61"/>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="65"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="75"/>
+      <c r="J25" s="116"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="60" t="s">
+      <c r="A26" s="132" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="61"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="66" t="s">
+      <c r="B26" s="75"/>
+      <c r="C26" s="76"/>
+      <c r="D26" s="91" t="s">
         <v>96</v>
       </c>
-      <c r="E26" s="61"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="62"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75"/>
+      <c r="H26" s="76"/>
       <c r="I26" s="14" t="s">
         <v>25</v>
       </c>
@@ -12414,11 +12348,11 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="60" t="s">
+      <c r="A27" s="132" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="61"/>
-      <c r="C27" s="62"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="76"/>
       <c r="D27" s="14" t="s">
         <v>27</v>
       </c>
@@ -12431,18 +12365,18 @@
       <c r="G27" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H27" s="67" t="s">
+      <c r="H27" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="I27" s="61"/>
-      <c r="J27" s="65"/>
+      <c r="I27" s="75"/>
+      <c r="J27" s="116"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="57" t="s">
+      <c r="A28" s="109" t="s">
         <v>85</v>
       </c>
-      <c r="B28" s="63"/>
-      <c r="C28" s="64"/>
+      <c r="B28" s="110"/>
+      <c r="C28" s="111"/>
       <c r="D28" s="15" t="s">
         <v>86</v>
       </c>
@@ -12455,23 +12389,23 @@
       <c r="G28" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="H28" s="66" t="s">
+      <c r="H28" s="91" t="s">
         <v>88</v>
       </c>
-      <c r="I28" s="68"/>
-      <c r="J28" s="69"/>
+      <c r="I28" s="112"/>
+      <c r="J28" s="113"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="100"/>
-      <c r="B29" s="101"/>
-      <c r="C29" s="102"/>
+      <c r="A29" s="117"/>
+      <c r="B29" s="118"/>
+      <c r="C29" s="119"/>
       <c r="D29" s="44"/>
       <c r="E29" s="44"/>
       <c r="F29" s="44"/>
       <c r="G29" s="44"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="104"/>
-      <c r="J29" s="105"/>
+      <c r="H29" s="120"/>
+      <c r="I29" s="121"/>
+      <c r="J29" s="122"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13451,17 +13385,18 @@
     <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="D21:H21"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -13478,18 +13413,17 @@
     <mergeCell ref="H18:J18"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13566,182 +13500,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="104" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="128" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="128" t="s">
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="128" t="s">
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="128" t="s">
+      <c r="P1" s="70"/>
+      <c r="Q1" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="72"/>
-      <c r="S1" s="128" t="s">
+      <c r="R1" s="70"/>
+      <c r="S1" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="118"/>
+      <c r="T1" s="103"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="124"/>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="155"/>
-      <c r="M2" s="155"/>
-      <c r="N2" s="87"/>
-      <c r="O2" s="86"/>
-      <c r="P2" s="87"/>
-      <c r="Q2" s="86"/>
-      <c r="R2" s="87"/>
-      <c r="S2" s="86"/>
-      <c r="T2" s="156"/>
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="71"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="150"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="124"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="99"/>
-      <c r="M3" s="99"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="88"/>
-      <c r="P3" s="89"/>
-      <c r="Q3" s="88"/>
-      <c r="R3" s="89"/>
-      <c r="S3" s="88"/>
-      <c r="T3" s="157"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="67"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="151"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="125"/>
-      <c r="B4" s="126"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="126"/>
-      <c r="I4" s="126"/>
-      <c r="J4" s="127"/>
-      <c r="K4" s="129"/>
-      <c r="L4" s="126"/>
-      <c r="M4" s="126"/>
-      <c r="N4" s="127"/>
-      <c r="O4" s="129"/>
-      <c r="P4" s="127"/>
-      <c r="Q4" s="129"/>
-      <c r="R4" s="127"/>
-      <c r="S4" s="129"/>
-      <c r="T4" s="158"/>
+      <c r="A4" s="105"/>
+      <c r="B4" s="106"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="108"/>
+      <c r="L4" s="106"/>
+      <c r="M4" s="106"/>
+      <c r="N4" s="107"/>
+      <c r="O4" s="108"/>
+      <c r="P4" s="107"/>
+      <c r="Q4" s="108"/>
+      <c r="R4" s="107"/>
+      <c r="S4" s="108"/>
+      <c r="T4" s="152"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="151" t="s">
+      <c r="A5" s="153" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="117" t="s">
+      <c r="B5" s="101"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="71"/>
-      <c r="R5" s="71"/>
-      <c r="S5" s="71"/>
-      <c r="T5" s="118"/>
+      <c r="H5" s="101"/>
+      <c r="I5" s="101"/>
+      <c r="J5" s="101"/>
+      <c r="K5" s="101"/>
+      <c r="L5" s="101"/>
+      <c r="M5" s="101"/>
+      <c r="N5" s="101"/>
+      <c r="O5" s="101"/>
+      <c r="P5" s="101"/>
+      <c r="Q5" s="101"/>
+      <c r="R5" s="101"/>
+      <c r="S5" s="101"/>
+      <c r="T5" s="103"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="152" t="s">
+      <c r="A6" s="154" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="66" t="s">
+      <c r="B6" s="75"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="61"/>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="61"/>
-      <c r="S6" s="61"/>
-      <c r="T6" s="120"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="75"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="75"/>
+      <c r="N6" s="75"/>
+      <c r="O6" s="75"/>
+      <c r="P6" s="75"/>
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75"/>
+      <c r="T6" s="84"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="152" t="s">
+      <c r="A7" s="154" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="66" t="s">
+      <c r="B7" s="75"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="61"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="61"/>
-      <c r="M7" s="61"/>
-      <c r="N7" s="61"/>
-      <c r="O7" s="61"/>
-      <c r="P7" s="61"/>
-      <c r="Q7" s="61"/>
-      <c r="R7" s="61"/>
-      <c r="S7" s="61"/>
-      <c r="T7" s="120"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="75"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="75"/>
+      <c r="N7" s="75"/>
+      <c r="O7" s="75"/>
+      <c r="P7" s="75"/>
+      <c r="Q7" s="75"/>
+      <c r="R7" s="75"/>
+      <c r="S7" s="75"/>
+      <c r="T7" s="84"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -13940,37 +13874,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="152" t="s">
+      <c r="A15" s="154" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="154" t="s">
+      <c r="B15" s="76"/>
+      <c r="C15" s="157" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="62"/>
-      <c r="E15" s="67" t="s">
+      <c r="D15" s="76"/>
+      <c r="E15" s="144" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="62"/>
-      <c r="G15" s="67" t="s">
+      <c r="F15" s="76"/>
+      <c r="G15" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="61"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="67" t="s">
+      <c r="H15" s="75"/>
+      <c r="I15" s="76"/>
+      <c r="J15" s="144" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="62"/>
-      <c r="L15" s="67" t="s">
+      <c r="K15" s="76"/>
+      <c r="L15" s="144" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="61"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="67" t="s">
+      <c r="M15" s="75"/>
+      <c r="N15" s="76"/>
+      <c r="O15" s="144" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="61"/>
-      <c r="Q15" s="62"/>
+      <c r="P15" s="75"/>
+      <c r="Q15" s="76"/>
       <c r="R15" s="14" t="s">
         <v>49</v>
       </c>
@@ -13982,37 +13916,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="145">
+      <c r="A16" s="155">
         <v>1</v>
       </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="146" t="s">
+      <c r="B16" s="76"/>
+      <c r="C16" s="156" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="62"/>
-      <c r="E16" s="146" t="s">
+      <c r="D16" s="76"/>
+      <c r="E16" s="156" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="62"/>
-      <c r="G16" s="153" t="s">
+      <c r="F16" s="76"/>
+      <c r="G16" s="145" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="61"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="153" t="s">
+      <c r="H16" s="75"/>
+      <c r="I16" s="76"/>
+      <c r="J16" s="145" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="62"/>
-      <c r="L16" s="149" t="s">
+      <c r="K16" s="76"/>
+      <c r="L16" s="147" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="61"/>
-      <c r="N16" s="62"/>
-      <c r="O16" s="149" t="s">
+      <c r="M16" s="75"/>
+      <c r="N16" s="76"/>
+      <c r="O16" s="147" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="61"/>
-      <c r="Q16" s="62"/>
+      <c r="P16" s="75"/>
+      <c r="Q16" s="76"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
@@ -14024,37 +13958,37 @@
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="145">
+      <c r="A17" s="155">
         <v>2</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="146" t="s">
+      <c r="B17" s="76"/>
+      <c r="C17" s="156" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="62"/>
-      <c r="E17" s="146" t="s">
+      <c r="D17" s="76"/>
+      <c r="E17" s="156" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="62"/>
-      <c r="G17" s="153" t="s">
+      <c r="F17" s="76"/>
+      <c r="G17" s="145" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="61"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="153" t="s">
+      <c r="H17" s="75"/>
+      <c r="I17" s="76"/>
+      <c r="J17" s="145" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="62"/>
-      <c r="L17" s="149" t="s">
+      <c r="K17" s="76"/>
+      <c r="L17" s="147" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="61"/>
-      <c r="N17" s="62"/>
-      <c r="O17" s="149" t="s">
+      <c r="M17" s="75"/>
+      <c r="N17" s="76"/>
+      <c r="O17" s="147" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="61"/>
-      <c r="Q17" s="62"/>
+      <c r="P17" s="75"/>
+      <c r="Q17" s="76"/>
       <c r="R17" s="28"/>
       <c r="S17" s="28"/>
       <c r="T17" s="29"/>
@@ -14066,23 +14000,23 @@
       <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="145"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="146"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="146"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="153"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="153"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="149"/>
-      <c r="M18" s="61"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="149"/>
-      <c r="P18" s="61"/>
-      <c r="Q18" s="62"/>
+      <c r="A18" s="155"/>
+      <c r="B18" s="76"/>
+      <c r="C18" s="156"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="156"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="145"/>
+      <c r="H18" s="75"/>
+      <c r="I18" s="76"/>
+      <c r="J18" s="145"/>
+      <c r="K18" s="76"/>
+      <c r="L18" s="147"/>
+      <c r="M18" s="75"/>
+      <c r="N18" s="76"/>
+      <c r="O18" s="147"/>
+      <c r="P18" s="75"/>
+      <c r="Q18" s="76"/>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
       <c r="T18" s="29"/>
@@ -14094,23 +14028,23 @@
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="145"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="146"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="146"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="153"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="153"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="149"/>
-      <c r="M19" s="61"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="149"/>
-      <c r="P19" s="61"/>
-      <c r="Q19" s="62"/>
+      <c r="A19" s="155"/>
+      <c r="B19" s="76"/>
+      <c r="C19" s="156"/>
+      <c r="D19" s="76"/>
+      <c r="E19" s="156"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="145"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="76"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="76"/>
+      <c r="L19" s="147"/>
+      <c r="M19" s="75"/>
+      <c r="N19" s="76"/>
+      <c r="O19" s="147"/>
+      <c r="P19" s="75"/>
+      <c r="Q19" s="76"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
       <c r="T19" s="29"/>
@@ -14122,23 +14056,23 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="145"/>
-      <c r="B20" s="62"/>
-      <c r="C20" s="146"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="146"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="153"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="153"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="149"/>
-      <c r="M20" s="61"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="149"/>
-      <c r="P20" s="61"/>
-      <c r="Q20" s="62"/>
+      <c r="A20" s="155"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="156"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="156"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="145"/>
+      <c r="H20" s="75"/>
+      <c r="I20" s="76"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="76"/>
+      <c r="L20" s="147"/>
+      <c r="M20" s="75"/>
+      <c r="N20" s="76"/>
+      <c r="O20" s="147"/>
+      <c r="P20" s="75"/>
+      <c r="Q20" s="76"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
       <c r="T20" s="29"/>
@@ -14150,23 +14084,23 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="145"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="146"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="146"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="153"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="153"/>
-      <c r="K21" s="62"/>
-      <c r="L21" s="149"/>
-      <c r="M21" s="61"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="149"/>
-      <c r="P21" s="61"/>
-      <c r="Q21" s="62"/>
+      <c r="A21" s="155"/>
+      <c r="B21" s="76"/>
+      <c r="C21" s="156"/>
+      <c r="D21" s="76"/>
+      <c r="E21" s="156"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="145"/>
+      <c r="H21" s="75"/>
+      <c r="I21" s="76"/>
+      <c r="J21" s="145"/>
+      <c r="K21" s="76"/>
+      <c r="L21" s="147"/>
+      <c r="M21" s="75"/>
+      <c r="N21" s="76"/>
+      <c r="O21" s="147"/>
+      <c r="P21" s="75"/>
+      <c r="Q21" s="76"/>
       <c r="R21" s="28"/>
       <c r="S21" s="28"/>
       <c r="T21" s="29"/>
@@ -14178,23 +14112,23 @@
       <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="145"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="146"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="146"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="153"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="153"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="149"/>
-      <c r="M22" s="61"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="149"/>
-      <c r="P22" s="61"/>
-      <c r="Q22" s="62"/>
+      <c r="A22" s="155"/>
+      <c r="B22" s="76"/>
+      <c r="C22" s="156"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="156"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="145"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="145"/>
+      <c r="K22" s="76"/>
+      <c r="L22" s="147"/>
+      <c r="M22" s="75"/>
+      <c r="N22" s="76"/>
+      <c r="O22" s="147"/>
+      <c r="P22" s="75"/>
+      <c r="Q22" s="76"/>
       <c r="R22" s="28"/>
       <c r="S22" s="28"/>
       <c r="T22" s="29"/>
@@ -14206,23 +14140,23 @@
       <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="145"/>
-      <c r="B23" s="62"/>
-      <c r="C23" s="146"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="146"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="153"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="153"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="149"/>
-      <c r="M23" s="61"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="149"/>
-      <c r="P23" s="61"/>
-      <c r="Q23" s="62"/>
+      <c r="A23" s="155"/>
+      <c r="B23" s="76"/>
+      <c r="C23" s="156"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="145"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="145"/>
+      <c r="K23" s="76"/>
+      <c r="L23" s="147"/>
+      <c r="M23" s="75"/>
+      <c r="N23" s="76"/>
+      <c r="O23" s="147"/>
+      <c r="P23" s="75"/>
+      <c r="Q23" s="76"/>
       <c r="R23" s="28"/>
       <c r="S23" s="28"/>
       <c r="T23" s="29"/>
@@ -14234,23 +14168,23 @@
       <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="145"/>
-      <c r="B24" s="62"/>
-      <c r="C24" s="146"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="146"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="153"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="153"/>
-      <c r="K24" s="62"/>
-      <c r="L24" s="149"/>
-      <c r="M24" s="61"/>
-      <c r="N24" s="62"/>
-      <c r="O24" s="149"/>
-      <c r="P24" s="61"/>
-      <c r="Q24" s="62"/>
+      <c r="A24" s="155"/>
+      <c r="B24" s="76"/>
+      <c r="C24" s="156"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="156"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="145"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="145"/>
+      <c r="K24" s="76"/>
+      <c r="L24" s="147"/>
+      <c r="M24" s="75"/>
+      <c r="N24" s="76"/>
+      <c r="O24" s="147"/>
+      <c r="P24" s="75"/>
+      <c r="Q24" s="76"/>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
       <c r="T24" s="29"/>
@@ -14262,23 +14196,23 @@
       <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="145"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="146"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="146"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="153"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="153"/>
-      <c r="K25" s="62"/>
-      <c r="L25" s="149"/>
-      <c r="M25" s="61"/>
-      <c r="N25" s="62"/>
-      <c r="O25" s="149"/>
-      <c r="P25" s="61"/>
-      <c r="Q25" s="62"/>
+      <c r="A25" s="155"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="156"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="156"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="145"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="76"/>
+      <c r="J25" s="145"/>
+      <c r="K25" s="76"/>
+      <c r="L25" s="147"/>
+      <c r="M25" s="75"/>
+      <c r="N25" s="76"/>
+      <c r="O25" s="147"/>
+      <c r="P25" s="75"/>
+      <c r="Q25" s="76"/>
       <c r="R25" s="28"/>
       <c r="S25" s="28"/>
       <c r="T25" s="29"/>
@@ -14290,23 +14224,23 @@
       <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="145"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="146"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="146"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="153"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="153"/>
-      <c r="K26" s="62"/>
-      <c r="L26" s="149"/>
-      <c r="M26" s="61"/>
-      <c r="N26" s="62"/>
-      <c r="O26" s="149"/>
-      <c r="P26" s="61"/>
-      <c r="Q26" s="62"/>
+      <c r="A26" s="155"/>
+      <c r="B26" s="76"/>
+      <c r="C26" s="156"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="156"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="145"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="76"/>
+      <c r="J26" s="145"/>
+      <c r="K26" s="76"/>
+      <c r="L26" s="147"/>
+      <c r="M26" s="75"/>
+      <c r="N26" s="76"/>
+      <c r="O26" s="147"/>
+      <c r="P26" s="75"/>
+      <c r="Q26" s="76"/>
       <c r="R26" s="28"/>
       <c r="S26" s="28"/>
       <c r="T26" s="29"/>
@@ -14318,23 +14252,23 @@
       <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="145"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="146"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="146"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="153"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="153"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="149"/>
-      <c r="M27" s="61"/>
-      <c r="N27" s="62"/>
-      <c r="O27" s="149"/>
-      <c r="P27" s="61"/>
-      <c r="Q27" s="62"/>
+      <c r="A27" s="155"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="156"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="156"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="145"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="76"/>
+      <c r="J27" s="145"/>
+      <c r="K27" s="76"/>
+      <c r="L27" s="147"/>
+      <c r="M27" s="75"/>
+      <c r="N27" s="76"/>
+      <c r="O27" s="147"/>
+      <c r="P27" s="75"/>
+      <c r="Q27" s="76"/>
       <c r="R27" s="28"/>
       <c r="S27" s="28"/>
       <c r="T27" s="29"/>
@@ -14346,23 +14280,23 @@
       <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="145"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="146"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="146"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="153"/>
-      <c r="H28" s="61"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="153"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="149"/>
-      <c r="M28" s="61"/>
-      <c r="N28" s="62"/>
-      <c r="O28" s="149"/>
-      <c r="P28" s="61"/>
-      <c r="Q28" s="62"/>
+      <c r="A28" s="155"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="156"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="156"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="145"/>
+      <c r="H28" s="75"/>
+      <c r="I28" s="76"/>
+      <c r="J28" s="145"/>
+      <c r="K28" s="76"/>
+      <c r="L28" s="147"/>
+      <c r="M28" s="75"/>
+      <c r="N28" s="76"/>
+      <c r="O28" s="147"/>
+      <c r="P28" s="75"/>
+      <c r="Q28" s="76"/>
       <c r="R28" s="28"/>
       <c r="S28" s="28"/>
       <c r="T28" s="29"/>
@@ -14374,23 +14308,23 @@
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="145"/>
-      <c r="B29" s="62"/>
-      <c r="C29" s="146"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="146"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="153"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="153"/>
-      <c r="K29" s="62"/>
-      <c r="L29" s="149"/>
-      <c r="M29" s="61"/>
-      <c r="N29" s="62"/>
-      <c r="O29" s="149"/>
-      <c r="P29" s="61"/>
-      <c r="Q29" s="62"/>
+      <c r="A29" s="155"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="156"/>
+      <c r="D29" s="76"/>
+      <c r="E29" s="156"/>
+      <c r="F29" s="76"/>
+      <c r="G29" s="145"/>
+      <c r="H29" s="75"/>
+      <c r="I29" s="76"/>
+      <c r="J29" s="145"/>
+      <c r="K29" s="76"/>
+      <c r="L29" s="147"/>
+      <c r="M29" s="75"/>
+      <c r="N29" s="76"/>
+      <c r="O29" s="147"/>
+      <c r="P29" s="75"/>
+      <c r="Q29" s="76"/>
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
       <c r="T29" s="29"/>
@@ -14402,23 +14336,23 @@
       <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="145"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="146"/>
-      <c r="D30" s="62"/>
-      <c r="E30" s="146"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="153"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="153"/>
-      <c r="K30" s="62"/>
-      <c r="L30" s="149"/>
-      <c r="M30" s="61"/>
-      <c r="N30" s="62"/>
-      <c r="O30" s="149"/>
-      <c r="P30" s="61"/>
-      <c r="Q30" s="62"/>
+      <c r="A30" s="155"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="156"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="156"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="145"/>
+      <c r="H30" s="75"/>
+      <c r="I30" s="76"/>
+      <c r="J30" s="145"/>
+      <c r="K30" s="76"/>
+      <c r="L30" s="147"/>
+      <c r="M30" s="75"/>
+      <c r="N30" s="76"/>
+      <c r="O30" s="147"/>
+      <c r="P30" s="75"/>
+      <c r="Q30" s="76"/>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
       <c r="T30" s="29"/>
@@ -14430,23 +14364,23 @@
       <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="147"/>
-      <c r="B31" s="133"/>
-      <c r="C31" s="148"/>
-      <c r="D31" s="133"/>
-      <c r="E31" s="148"/>
-      <c r="F31" s="133"/>
-      <c r="G31" s="159"/>
-      <c r="H31" s="132"/>
-      <c r="I31" s="133"/>
-      <c r="J31" s="159"/>
-      <c r="K31" s="133"/>
-      <c r="L31" s="150"/>
-      <c r="M31" s="132"/>
-      <c r="N31" s="133"/>
-      <c r="O31" s="150"/>
-      <c r="P31" s="132"/>
-      <c r="Q31" s="133"/>
+      <c r="A31" s="158"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="159"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="159"/>
+      <c r="F31" s="87"/>
+      <c r="G31" s="146"/>
+      <c r="H31" s="86"/>
+      <c r="I31" s="87"/>
+      <c r="J31" s="146"/>
+      <c r="K31" s="87"/>
+      <c r="L31" s="148"/>
+      <c r="M31" s="86"/>
+      <c r="N31" s="87"/>
+      <c r="O31" s="148"/>
+      <c r="P31" s="86"/>
+      <c r="Q31" s="87"/>
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
       <c r="T31" s="32"/>
@@ -15444,62 +15378,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -15524,62 +15458,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
